--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -704,7 +704,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-24T06:00:35    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-25T05:54:27    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.6s</t>
+          <t>1.61s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.04s</t>
+          <t>1.05s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>3.42s</t>
+          <t>3.43s</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.89s</t>
+          <t>0.98s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.46s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.83</v>
+        <v>3.75</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H43" s="20" t="inlineStr"/>
     </row>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="G45" s="21" t="n">
-        <v>10.33</v>
+        <v>10.35</v>
       </c>
       <c r="H45" s="23" t="inlineStr"/>
     </row>
@@ -2870,19 +2870,19 @@
         </is>
       </c>
       <c r="G47" s="21" t="n">
-        <v>21.34</v>
+        <v>21.33</v>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="G48" s="21" t="n">
-        <v>22.07</v>
+        <v>22.08</v>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="G49" s="21" t="n">
-        <v>22.03</v>
+        <v>22.02</v>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3014,19 +3014,19 @@
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="G51" s="21" t="n">
-        <v>22.2</v>
+        <v>22.08</v>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>21.14</v>
+        <v>21.16</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>21.16</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="G56" s="21" t="n">
-        <v>22.11</v>
+        <v>22.05</v>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="G57" s="21" t="n">
-        <v>22.12</v>
+        <v>22.1</v>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3350,19 +3350,19 @@
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>22.35</v>
+        <v>22.31</v>
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H72" s="20" t="inlineStr"/>
     </row>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="20" t="inlineStr"/>
     </row>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="G136" s="18" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H136" s="20" t="inlineStr"/>
     </row>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="G139" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H139" s="20" t="inlineStr"/>
     </row>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H152" s="20" t="inlineStr"/>
     </row>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="G154" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H154" s="20" t="inlineStr"/>
     </row>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="G166" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H166" s="20" t="inlineStr"/>
     </row>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G170" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="20" t="inlineStr"/>
     </row>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="G180" s="18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H180" s="20" t="inlineStr"/>
     </row>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="G182" s="18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H182" s="20" t="inlineStr"/>
     </row>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="G184" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="20" t="inlineStr"/>
     </row>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="G187" s="18" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H187" s="20" t="inlineStr"/>
     </row>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="G189" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H189" s="20" t="inlineStr"/>
     </row>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G192" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="20" t="inlineStr"/>
     </row>
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="G193" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="20" t="inlineStr"/>
     </row>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="G198" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="20" t="inlineStr"/>
     </row>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G205" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H205" s="20" t="inlineStr"/>
     </row>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="G212" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="20" t="inlineStr"/>
     </row>
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="G220" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="20" t="inlineStr"/>
     </row>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="G221" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="20" t="inlineStr"/>
     </row>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="G222" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="20" t="inlineStr"/>
     </row>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="G227" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="20" t="inlineStr"/>
     </row>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="G228" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="20" t="inlineStr"/>
     </row>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="G231" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="20" t="inlineStr"/>
     </row>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G233" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="20" t="inlineStr"/>
     </row>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="G236" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H236" s="20" t="inlineStr"/>
     </row>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="G239" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="20" t="inlineStr"/>
     </row>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="G243" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="20" t="inlineStr"/>
     </row>
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="G244" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" s="20" t="inlineStr"/>
     </row>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="G245" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="20" t="inlineStr"/>
     </row>
@@ -10166,7 +10166,7 @@
         </is>
       </c>
       <c r="G247" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H247" s="20" t="inlineStr"/>
     </row>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="G248" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="20" t="inlineStr"/>
     </row>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G252" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H252" s="20" t="inlineStr"/>
     </row>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="G254" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="20" t="inlineStr"/>
     </row>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="G257" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="20" t="inlineStr"/>
     </row>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="G259" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="20" t="inlineStr"/>
     </row>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="G265" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="20" t="inlineStr"/>
     </row>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="G271" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H271" s="20" t="inlineStr"/>
     </row>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="G277" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="20" t="inlineStr"/>
     </row>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -11426,7 +11426,7 @@
         </is>
       </c>
       <c r="G282" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="20" t="inlineStr"/>
     </row>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="G288" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="20" t="inlineStr"/>
     </row>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="G294" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="20" t="inlineStr"/>
     </row>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="G301" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="20" t="inlineStr"/>
     </row>
@@ -12146,7 +12146,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="G304" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="20" t="inlineStr"/>
     </row>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -12506,7 +12506,7 @@
         </is>
       </c>
       <c r="G312" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="20" t="inlineStr"/>
     </row>
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G315" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="20" t="inlineStr"/>
     </row>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -12902,7 +12902,7 @@
         </is>
       </c>
       <c r="G323" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="20" t="inlineStr"/>
     </row>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="G324" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="20" t="inlineStr"/>
     </row>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="G327" s="18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H327" s="20" t="inlineStr"/>
     </row>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="G329" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H329" s="20" t="inlineStr"/>
     </row>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -13190,7 +13190,7 @@
         </is>
       </c>
       <c r="G331" s="18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="20" t="inlineStr"/>
     </row>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="G343" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="20" t="inlineStr"/>
     </row>
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="G346" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="20" t="inlineStr"/>
     </row>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="G349" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="20" t="inlineStr"/>
     </row>
@@ -13874,7 +13874,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G354" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="20" t="inlineStr"/>
     </row>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="G357" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="20" t="inlineStr"/>
     </row>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="G362" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="20" t="inlineStr"/>
     </row>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -14954,7 +14954,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -15062,7 +15062,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -15242,7 +15242,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="G389" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="20" t="inlineStr"/>
     </row>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="G390" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H390" s="20" t="inlineStr"/>
     </row>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="G391" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H391" s="20" t="inlineStr"/>
     </row>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G395" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H395" s="20" t="inlineStr"/>
     </row>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -15854,7 +15854,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="G414" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="20" t="inlineStr"/>
     </row>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="G425" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="20" t="inlineStr"/>
     </row>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="G428" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="20" t="inlineStr"/>
     </row>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -16934,7 +16934,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G438" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="20" t="inlineStr"/>
     </row>
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="G441" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="20" t="inlineStr"/>
     </row>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="G442" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="20" t="inlineStr"/>
     </row>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -17510,7 +17510,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -17546,7 +17546,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -17690,7 +17690,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="G461" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="20" t="inlineStr"/>
     </row>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="G465" s="18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H465" s="20" t="inlineStr"/>
     </row>
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="G467" s="18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="20" t="inlineStr"/>
     </row>
@@ -18158,7 +18158,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -18230,7 +18230,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -18374,7 +18374,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -18410,7 +18410,7 @@
         </is>
       </c>
       <c r="G476" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="20" t="inlineStr"/>
     </row>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -18482,7 +18482,7 @@
         </is>
       </c>
       <c r="G478" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="20" t="inlineStr"/>
     </row>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="G481" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="20" t="inlineStr"/>
     </row>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="G487" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="20" t="inlineStr"/>
     </row>
@@ -18914,7 +18914,7 @@
         </is>
       </c>
       <c r="G490" s="18" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="20" t="inlineStr"/>
     </row>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="G491" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H491" s="20" t="inlineStr"/>
     </row>
@@ -19022,7 +19022,7 @@
         </is>
       </c>
       <c r="G493" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H493" s="20" t="inlineStr"/>
     </row>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="G496" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="20" t="inlineStr"/>
     </row>
@@ -19202,7 +19202,7 @@
         </is>
       </c>
       <c r="G498" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="20" t="inlineStr"/>
     </row>
@@ -19274,7 +19274,7 @@
         </is>
       </c>
       <c r="G500" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="20" t="inlineStr"/>
     </row>
@@ -19413,7 +19413,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.83</v>
+        <v>3.75</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -19557,7 +19557,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -19593,7 +19593,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -19629,7 +19629,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -19701,7 +19701,7 @@
         </is>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
     </row>
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -19809,7 +19809,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
     </row>
@@ -19917,7 +19917,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -20061,7 +20061,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -20241,7 +20241,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -20277,7 +20277,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -20313,7 +20313,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -20421,7 +20421,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -20457,7 +20457,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -20529,7 +20529,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -20637,7 +20637,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -20709,7 +20709,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -20781,7 +20781,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -20961,7 +20961,7 @@
         </is>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H45" s="20" t="inlineStr"/>
     </row>
@@ -20997,7 +20997,7 @@
         </is>
       </c>
       <c r="G46" s="18" t="n">
-        <v>21.14</v>
+        <v>21.16</v>
       </c>
       <c r="H46" s="20" t="inlineStr"/>
     </row>
@@ -21033,7 +21033,7 @@
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>21.16</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="20" t="inlineStr"/>
     </row>
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="H48" s="20" t="inlineStr"/>
     </row>
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="H49" s="20" t="inlineStr"/>
     </row>
@@ -21141,7 +21141,7 @@
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="H50" s="20" t="inlineStr"/>
     </row>
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H51" s="20" t="inlineStr"/>
     </row>
@@ -21213,7 +21213,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H56" s="20" t="inlineStr"/>
     </row>
@@ -21393,7 +21393,7 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H57" s="20" t="inlineStr"/>
     </row>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H58" s="20" t="inlineStr"/>
     </row>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -21501,7 +21501,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -21573,7 +21573,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -21681,7 +21681,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -21753,7 +21753,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -21789,7 +21789,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -21861,7 +21861,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -21933,7 +21933,7 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="20" t="inlineStr"/>
     </row>
@@ -21969,7 +21969,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -22005,7 +22005,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H77" s="20" t="inlineStr"/>
     </row>
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -22185,7 +22185,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -22329,7 +22329,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -22437,7 +22437,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -22473,7 +22473,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -22545,7 +22545,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -22581,7 +22581,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -22653,7 +22653,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -22725,7 +22725,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -22761,7 +22761,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -22797,7 +22797,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -22869,7 +22869,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -22941,7 +22941,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -22977,7 +22977,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -23049,7 +23049,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -23157,7 +23157,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -23193,7 +23193,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -23301,7 +23301,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -23337,7 +23337,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -23445,7 +23445,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -23481,7 +23481,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -23517,7 +23517,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -23553,7 +23553,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -23589,7 +23589,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -23661,7 +23661,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -23697,7 +23697,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -23733,7 +23733,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -23769,7 +23769,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -23877,7 +23877,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -23949,7 +23949,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -24021,7 +24021,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -24057,7 +24057,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -24273,7 +24273,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -24417,7 +24417,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="G143" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H143" s="20" t="inlineStr"/>
     </row>
@@ -24525,7 +24525,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -24669,7 +24669,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -25029,7 +25029,7 @@
         </is>
       </c>
       <c r="G158" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H158" s="20" t="inlineStr"/>
     </row>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="G162" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H162" s="20" t="inlineStr"/>
     </row>
@@ -25245,7 +25245,7 @@
         </is>
       </c>
       <c r="G164" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="20" t="inlineStr"/>
     </row>
@@ -25353,7 +25353,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -25389,7 +25389,7 @@
         </is>
       </c>
       <c r="G168" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H168" s="20" t="inlineStr"/>
     </row>
@@ -25425,7 +25425,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -25497,7 +25497,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -25569,7 +25569,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -25641,7 +25641,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="G176" s="18" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H176" s="20" t="inlineStr"/>
     </row>
@@ -25713,7 +25713,7 @@
         </is>
       </c>
       <c r="G177" s="18" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="H177" s="20" t="inlineStr"/>
     </row>
@@ -25749,7 +25749,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="G181" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H181" s="20" t="inlineStr"/>
     </row>
@@ -25893,7 +25893,7 @@
         </is>
       </c>
       <c r="G182" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="20" t="inlineStr"/>
     </row>
@@ -25929,7 +25929,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -26001,7 +26001,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -26073,7 +26073,7 @@
         </is>
       </c>
       <c r="G187" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H187" s="20" t="inlineStr"/>
     </row>
@@ -26109,7 +26109,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -26181,7 +26181,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -26325,7 +26325,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -26577,7 +26577,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -26649,7 +26649,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -26829,7 +26829,7 @@
         </is>
       </c>
       <c r="G208" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H208" s="20" t="inlineStr"/>
     </row>
@@ -26865,7 +26865,7 @@
         </is>
       </c>
       <c r="G209" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="20" t="inlineStr"/>
     </row>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="G210" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="20" t="inlineStr"/>
     </row>
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="G211" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="20" t="inlineStr"/>
     </row>
@@ -27117,7 +27117,7 @@
         </is>
       </c>
       <c r="G216" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="20" t="inlineStr"/>
     </row>
@@ -27153,7 +27153,7 @@
         </is>
       </c>
       <c r="G217" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="20" t="inlineStr"/>
     </row>
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -27261,7 +27261,7 @@
         </is>
       </c>
       <c r="G220" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="20" t="inlineStr"/>
     </row>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="G222" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="20" t="inlineStr"/>
     </row>
@@ -27441,7 +27441,7 @@
         </is>
       </c>
       <c r="G225" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="20" t="inlineStr"/>
     </row>
@@ -27549,7 +27549,7 @@
         </is>
       </c>
       <c r="G228" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="20" t="inlineStr"/>
     </row>
@@ -27621,7 +27621,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -27693,7 +27693,7 @@
         </is>
       </c>
       <c r="G232" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="20" t="inlineStr"/>
     </row>
@@ -27729,7 +27729,7 @@
         </is>
       </c>
       <c r="G233" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H233" s="20" t="inlineStr"/>
     </row>
@@ -27765,7 +27765,7 @@
         </is>
       </c>
       <c r="G234" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="20" t="inlineStr"/>
     </row>
@@ -27837,7 +27837,7 @@
         </is>
       </c>
       <c r="G236" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H236" s="20" t="inlineStr"/>
     </row>
@@ -27873,7 +27873,7 @@
         </is>
       </c>
       <c r="G237" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="20" t="inlineStr"/>
     </row>
@@ -28017,7 +28017,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -28053,7 +28053,7 @@
         </is>
       </c>
       <c r="G242" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="20" t="inlineStr"/>
     </row>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="G243" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="20" t="inlineStr"/>
     </row>
@@ -28161,7 +28161,7 @@
         </is>
       </c>
       <c r="G245" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="20" t="inlineStr"/>
     </row>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="G246" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="20" t="inlineStr"/>
     </row>
@@ -28269,7 +28269,7 @@
         </is>
       </c>
       <c r="G248" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="20" t="inlineStr"/>
     </row>
@@ -28341,7 +28341,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -28449,7 +28449,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="G254" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H254" s="20" t="inlineStr"/>
     </row>
@@ -28521,7 +28521,7 @@
         </is>
       </c>
       <c r="G255" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H255" s="20" t="inlineStr"/>
     </row>
@@ -28593,7 +28593,7 @@
         </is>
       </c>
       <c r="G257" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H257" s="20" t="inlineStr"/>
     </row>
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="G258" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H258" s="20" t="inlineStr"/>
     </row>
@@ -28701,7 +28701,7 @@
         </is>
       </c>
       <c r="G260" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H260" s="20" t="inlineStr"/>
     </row>
@@ -28737,7 +28737,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -28773,7 +28773,7 @@
         </is>
       </c>
       <c r="G262" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H262" s="20" t="inlineStr"/>
     </row>
@@ -28845,7 +28845,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -28989,7 +28989,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -29025,7 +29025,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -29097,7 +29097,7 @@
         </is>
       </c>
       <c r="G271" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" s="20" t="inlineStr"/>
     </row>
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -29313,7 +29313,7 @@
         </is>
       </c>
       <c r="G277" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="20" t="inlineStr"/>
     </row>
@@ -29349,7 +29349,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -29493,7 +29493,7 @@
         </is>
       </c>
       <c r="G282" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="20" t="inlineStr"/>
     </row>
@@ -29529,7 +29529,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -29709,7 +29709,7 @@
         </is>
       </c>
       <c r="G288" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="20" t="inlineStr"/>
     </row>
@@ -29781,7 +29781,7 @@
         </is>
       </c>
       <c r="G290" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="20" t="inlineStr"/>
     </row>
@@ -29817,7 +29817,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="G292" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="20" t="inlineStr"/>
     </row>
@@ -29889,7 +29889,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -29997,7 +29997,7 @@
         </is>
       </c>
       <c r="G296" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="20" t="inlineStr"/>
     </row>
@@ -30069,7 +30069,7 @@
         </is>
       </c>
       <c r="G298" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="20" t="inlineStr"/>
     </row>
@@ -30105,7 +30105,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -30177,7 +30177,7 @@
         </is>
       </c>
       <c r="G301" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="20" t="inlineStr"/>
     </row>
@@ -30213,7 +30213,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -30249,7 +30249,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -30285,7 +30285,7 @@
         </is>
       </c>
       <c r="G304" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="20" t="inlineStr"/>
     </row>
@@ -30357,7 +30357,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -30393,7 +30393,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -30501,7 +30501,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -30573,7 +30573,7 @@
         </is>
       </c>
       <c r="G312" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H312" s="20" t="inlineStr"/>
     </row>
@@ -30609,7 +30609,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -30645,7 +30645,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -30717,7 +30717,7 @@
         </is>
       </c>
       <c r="G316" s="18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H316" s="20" t="inlineStr"/>
     </row>
@@ -30753,7 +30753,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -30789,7 +30789,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -30861,7 +30861,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="G326" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H326" s="20" t="inlineStr"/>
     </row>
@@ -31149,7 +31149,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -31293,7 +31293,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -31401,7 +31401,7 @@
         </is>
       </c>
       <c r="G335" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="20" t="inlineStr"/>
     </row>
@@ -31473,7 +31473,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -31509,7 +31509,7 @@
         </is>
       </c>
       <c r="G338" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="20" t="inlineStr"/>
     </row>
@@ -31545,7 +31545,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -31689,7 +31689,7 @@
         </is>
       </c>
       <c r="G343" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="20" t="inlineStr"/>
     </row>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="G344" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="20" t="inlineStr"/>
     </row>
@@ -31797,7 +31797,7 @@
         </is>
       </c>
       <c r="G346" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="20" t="inlineStr"/>
     </row>
@@ -31833,7 +31833,7 @@
         </is>
       </c>
       <c r="G347" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="20" t="inlineStr"/>
     </row>
@@ -31941,7 +31941,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -31977,7 +31977,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="G353" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H353" s="20" t="inlineStr"/>
     </row>
@@ -32229,7 +32229,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -32265,7 +32265,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -32301,7 +32301,7 @@
         </is>
       </c>
       <c r="G360" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="20" t="inlineStr"/>
     </row>
@@ -32409,7 +32409,7 @@
         </is>
       </c>
       <c r="G363" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="20" t="inlineStr"/>
     </row>
@@ -32445,7 +32445,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -32481,7 +32481,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -32517,7 +32517,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -32625,7 +32625,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -32661,7 +32661,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -32733,7 +32733,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -32769,7 +32769,7 @@
         </is>
       </c>
       <c r="G373" s="18" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H373" s="20" t="inlineStr"/>
     </row>
@@ -32877,7 +32877,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -32913,7 +32913,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -32949,7 +32949,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -33093,7 +33093,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -33165,7 +33165,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -33201,7 +33201,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -33453,7 +33453,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -33525,7 +33525,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -33597,7 +33597,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -33669,7 +33669,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -33741,7 +33741,7 @@
         </is>
       </c>
       <c r="G400" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="20" t="inlineStr"/>
     </row>
@@ -33777,7 +33777,7 @@
         </is>
       </c>
       <c r="G401" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="20" t="inlineStr"/>
     </row>
@@ -33849,7 +33849,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="G406" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="20" t="inlineStr"/>
     </row>
@@ -34065,7 +34065,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -34101,7 +34101,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -34137,7 +34137,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="G414" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="20" t="inlineStr"/>
     </row>
@@ -34281,7 +34281,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -34317,7 +34317,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -34353,7 +34353,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -34605,7 +34605,7 @@
         </is>
       </c>
       <c r="G424" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H424" s="20" t="inlineStr"/>
     </row>
@@ -34641,7 +34641,7 @@
         </is>
       </c>
       <c r="G425" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H425" s="20" t="inlineStr"/>
     </row>
@@ -34677,7 +34677,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -34713,7 +34713,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="G430" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H430" s="20" t="inlineStr"/>
     </row>
@@ -34857,7 +34857,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -35073,7 +35073,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -35109,7 +35109,7 @@
         </is>
       </c>
       <c r="G438" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H438" s="20" t="inlineStr"/>
     </row>
@@ -35145,7 +35145,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -35181,7 +35181,7 @@
         </is>
       </c>
       <c r="G440" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="20" t="inlineStr"/>
     </row>
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="G441" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="20" t="inlineStr"/>
     </row>
@@ -35325,7 +35325,7 @@
         </is>
       </c>
       <c r="G444" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="20" t="inlineStr"/>
     </row>
@@ -35361,7 +35361,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -35397,7 +35397,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -35505,7 +35505,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -35541,7 +35541,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -35577,7 +35577,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -35613,7 +35613,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -35649,7 +35649,7 @@
         </is>
       </c>
       <c r="G453" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H453" s="20" t="inlineStr"/>
     </row>
@@ -35685,7 +35685,7 @@
         </is>
       </c>
       <c r="G454" s="18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H454" s="20" t="inlineStr"/>
     </row>
@@ -35721,7 +35721,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -35757,7 +35757,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -35829,7 +35829,7 @@
         </is>
       </c>
       <c r="G458" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H458" s="20" t="inlineStr"/>
     </row>
@@ -35901,7 +35901,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -36009,7 +36009,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -36045,7 +36045,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -36081,7 +36081,7 @@
         </is>
       </c>
       <c r="G465" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H465" s="20" t="inlineStr"/>
     </row>
@@ -36117,7 +36117,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -36153,7 +36153,7 @@
         </is>
       </c>
       <c r="G467" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H467" s="20" t="inlineStr"/>
     </row>
@@ -36189,7 +36189,7 @@
         </is>
       </c>
       <c r="G468" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H468" s="20" t="inlineStr"/>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="G470" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="20" t="inlineStr"/>
     </row>
@@ -36297,7 +36297,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -36333,7 +36333,7 @@
         </is>
       </c>
       <c r="G472" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="20" t="inlineStr"/>
     </row>
@@ -36369,7 +36369,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -36477,7 +36477,7 @@
         </is>
       </c>
       <c r="G476" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="20" t="inlineStr"/>
     </row>
@@ -36585,7 +36585,7 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
@@ -36621,7 +36621,7 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
@@ -36693,7 +36693,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -36801,7 +36801,7 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
@@ -36873,7 +36873,7 @@
         </is>
       </c>
       <c r="G487" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="20" t="inlineStr"/>
     </row>
@@ -36945,7 +36945,7 @@
         </is>
       </c>
       <c r="G489" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="20" t="inlineStr"/>
     </row>
@@ -37084,7 +37084,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>10.33</v>
+        <v>10.35</v>
       </c>
       <c r="H4" s="23" t="inlineStr"/>
     </row>
@@ -37200,19 +37200,19 @@
         </is>
       </c>
       <c r="G5" s="21" t="n">
-        <v>21.34</v>
+        <v>21.33</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37248,19 +37248,19 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>22.07</v>
+        <v>22.08</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37296,19 +37296,19 @@
         </is>
       </c>
       <c r="G7" s="21" t="n">
-        <v>22.03</v>
+        <v>22.02</v>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37344,19 +37344,19 @@
         </is>
       </c>
       <c r="G8" s="21" t="n">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37392,19 +37392,19 @@
         </is>
       </c>
       <c r="G9" s="21" t="n">
-        <v>22.2</v>
+        <v>22.08</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37440,19 +37440,19 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>22.11</v>
+        <v>22.05</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37488,19 +37488,19 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>22.12</v>
+        <v>22.1</v>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37536,19 +37536,19 @@
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>22.35</v>
+        <v>22.31</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55b5bd7ab41a &lt;unknown&gt;
-#1 0x55b5bd183689 &lt;unknown&gt;
-#2 0x55b5bd1d8cff &lt;unknown&gt;
-#3 0x55b5bd1d8f51 &lt;unknown&gt;
-#4 0x55b5bd224144 &lt;unknown&gt;
-#5 0x55b5bd221329 &lt;unknown&gt;
-#6 0x55b5b</t>
+#0 0x557efabc344a &lt;unknown&gt;
+#1 0x557efa59b8c9 &lt;unknown&gt;
+#2 0x557efa5f0f32 &lt;unknown&gt;
+#3 0x557efa5f1181 &lt;unknown&gt;
+#4 0x557efa63c374 &lt;unknown&gt;
+#5 0x557efa63955d &lt;unknown&gt;
+#6 0x557ef</t>
         </is>
       </c>
     </row>
@@ -37965,7 +37965,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>1.6s</t>
+          <t>1.61s</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$490</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$489</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -704,7 +704,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-25T05:54:27    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-26T06:11:50    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -748,22 +748,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>488</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.61s</t>
+          <t>1.67s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>3.43s</t>
+          <t>3.44s</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.98s</t>
+          <t>0.89s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1074,19 +1074,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.84s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>3.75</v>
+        <v>0.36</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>1.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H43" s="20" t="inlineStr"/>
     </row>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="G45" s="21" t="n">
-        <v>10.35</v>
+        <v>10.34</v>
       </c>
       <c r="H45" s="23" t="inlineStr"/>
     </row>
@@ -2870,19 +2870,19 @@
         </is>
       </c>
       <c r="G47" s="21" t="n">
-        <v>21.33</v>
+        <v>21.39</v>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="G48" s="21" t="n">
-        <v>22.08</v>
+        <v>22.05</v>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="G49" s="21" t="n">
-        <v>22.02</v>
+        <v>22.07</v>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3014,19 +3014,19 @@
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>22.11</v>
+        <v>22.15</v>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="G51" s="21" t="n">
-        <v>22.08</v>
+        <v>22.18</v>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>21.16</v>
+        <v>21.18</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>21.12</v>
+        <v>21.21</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="G56" s="21" t="n">
-        <v>22.05</v>
+        <v>22.12</v>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="G57" s="21" t="n">
-        <v>22.1</v>
+        <v>22.15</v>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3350,19 +3350,19 @@
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>22.31</v>
+        <v>22.45</v>
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="20" t="inlineStr"/>
     </row>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="G136" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H136" s="20" t="inlineStr"/>
     </row>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="G139" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H139" s="20" t="inlineStr"/>
     </row>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="G143" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="20" t="inlineStr"/>
     </row>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G153" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H153" s="20" t="inlineStr"/>
     </row>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="G154" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="20" t="inlineStr"/>
     </row>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="G157" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H157" s="20" t="inlineStr"/>
     </row>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="G158" s="18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H158" s="20" t="inlineStr"/>
     </row>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="G162" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H162" s="20" t="inlineStr"/>
     </row>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H164" s="20" t="inlineStr"/>
     </row>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="G166" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H166" s="20" t="inlineStr"/>
     </row>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G170" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="20" t="inlineStr"/>
     </row>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="G172" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H172" s="20" t="inlineStr"/>
     </row>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="G174" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="20" t="inlineStr"/>
     </row>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="G180" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="20" t="inlineStr"/>
     </row>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="G182" s="18" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="H182" s="20" t="inlineStr"/>
     </row>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="G184" s="18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H184" s="20" t="inlineStr"/>
     </row>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="G187" s="18" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="H187" s="20" t="inlineStr"/>
     </row>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="G189" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="20" t="inlineStr"/>
     </row>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="G191" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="20" t="inlineStr"/>
     </row>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G192" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H192" s="20" t="inlineStr"/>
     </row>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="G197" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H197" s="20" t="inlineStr"/>
     </row>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="G202" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="20" t="inlineStr"/>
     </row>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="G204" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H204" s="20" t="inlineStr"/>
     </row>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="G208" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="20" t="inlineStr"/>
     </row>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="G209" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="20" t="inlineStr"/>
     </row>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G211" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="20" t="inlineStr"/>
     </row>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="G212" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="20" t="inlineStr"/>
     </row>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="G213" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="20" t="inlineStr"/>
     </row>
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="G215" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="20" t="inlineStr"/>
     </row>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="G216" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="20" t="inlineStr"/>
     </row>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="G217" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="20" t="inlineStr"/>
     </row>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="G218" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="20" t="inlineStr"/>
     </row>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="G221" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="20" t="inlineStr"/>
     </row>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="G224" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H224" s="20" t="inlineStr"/>
     </row>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="G225" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="20" t="inlineStr"/>
     </row>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="G226" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="20" t="inlineStr"/>
     </row>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="G228" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="20" t="inlineStr"/>
     </row>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="G229" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="20" t="inlineStr"/>
     </row>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="G232" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="20" t="inlineStr"/>
     </row>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G233" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H233" s="20" t="inlineStr"/>
     </row>
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="G234" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="20" t="inlineStr"/>
     </row>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G235" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="20" t="inlineStr"/>
     </row>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="G237" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H237" s="20" t="inlineStr"/>
     </row>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="G238" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="20" t="inlineStr"/>
     </row>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="G240" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="20" t="inlineStr"/>
     </row>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="G242" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="20" t="inlineStr"/>
     </row>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="G243" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="20" t="inlineStr"/>
     </row>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G246" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="20" t="inlineStr"/>
     </row>
@@ -10166,7 +10166,7 @@
         </is>
       </c>
       <c r="G247" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="20" t="inlineStr"/>
     </row>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="G248" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="20" t="inlineStr"/>
     </row>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="G249" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="20" t="inlineStr"/>
     </row>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="G251" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H251" s="20" t="inlineStr"/>
     </row>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G252" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="20" t="inlineStr"/>
     </row>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="G258" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="20" t="inlineStr"/>
     </row>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="G259" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="20" t="inlineStr"/>
     </row>
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="G260" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="20" t="inlineStr"/>
     </row>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="G271" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H271" s="20" t="inlineStr"/>
     </row>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G276" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="20" t="inlineStr"/>
     </row>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="G277" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="20" t="inlineStr"/>
     </row>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -12074,7 +12074,7 @@
         </is>
       </c>
       <c r="G300" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H300" s="20" t="inlineStr"/>
     </row>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="G301" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="20" t="inlineStr"/>
     </row>
@@ -12146,7 +12146,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="G304" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="20" t="inlineStr"/>
     </row>
@@ -12254,7 +12254,7 @@
         </is>
       </c>
       <c r="G305" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H305" s="20" t="inlineStr"/>
     </row>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="G311" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="20" t="inlineStr"/>
     </row>
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="G322" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H322" s="20" t="inlineStr"/>
     </row>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="G324" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="20" t="inlineStr"/>
     </row>
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="G327" s="18" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="20" t="inlineStr"/>
     </row>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="G329" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H329" s="20" t="inlineStr"/>
     </row>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -13190,7 +13190,7 @@
         </is>
       </c>
       <c r="G331" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="20" t="inlineStr"/>
     </row>
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="G333" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="20" t="inlineStr"/>
     </row>
@@ -13334,7 +13334,7 @@
         </is>
       </c>
       <c r="G335" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="20" t="inlineStr"/>
     </row>
@@ -13370,7 +13370,7 @@
         </is>
       </c>
       <c r="G336" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H336" s="20" t="inlineStr"/>
     </row>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="G343" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="20" t="inlineStr"/>
     </row>
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="G346" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="20" t="inlineStr"/>
     </row>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -13874,7 +13874,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="G352" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H352" s="20" t="inlineStr"/>
     </row>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -14198,7 +14198,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="G362" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="20" t="inlineStr"/>
     </row>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -14486,7 +14486,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -14702,7 +14702,7 @@
         </is>
       </c>
       <c r="G373" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="20" t="inlineStr"/>
     </row>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -14954,7 +14954,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -15062,7 +15062,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="G386" s="18" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H386" s="20" t="inlineStr"/>
     </row>
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -15242,7 +15242,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="G390" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="20" t="inlineStr"/>
     </row>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="G391" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="20" t="inlineStr"/>
     </row>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G395" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="20" t="inlineStr"/>
     </row>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G397" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="20" t="inlineStr"/>
     </row>
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="G402" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H402" s="20" t="inlineStr"/>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -15854,7 +15854,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="G406" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="20" t="inlineStr"/>
     </row>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="G408" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H408" s="20" t="inlineStr"/>
     </row>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -16142,7 +16142,7 @@
         </is>
       </c>
       <c r="G413" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="20" t="inlineStr"/>
     </row>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="G414" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="20" t="inlineStr"/>
     </row>
@@ -16214,7 +16214,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -16322,7 +16322,7 @@
         </is>
       </c>
       <c r="G418" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="20" t="inlineStr"/>
     </row>
@@ -16358,7 +16358,7 @@
         </is>
       </c>
       <c r="G419" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="20" t="inlineStr"/>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="G425" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="20" t="inlineStr"/>
     </row>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="G428" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H428" s="20" t="inlineStr"/>
     </row>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="G429" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H429" s="20" t="inlineStr"/>
     </row>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -16826,7 +16826,7 @@
         </is>
       </c>
       <c r="G432" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="20" t="inlineStr"/>
     </row>
@@ -16862,7 +16862,7 @@
         </is>
       </c>
       <c r="G433" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="20" t="inlineStr"/>
     </row>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="G434" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="20" t="inlineStr"/>
     </row>
@@ -16934,7 +16934,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -17114,7 +17114,7 @@
         </is>
       </c>
       <c r="G440" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="20" t="inlineStr"/>
     </row>
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="G441" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="20" t="inlineStr"/>
     </row>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="G442" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="20" t="inlineStr"/>
     </row>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="G447" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="20" t="inlineStr"/>
     </row>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -17510,7 +17510,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -17690,7 +17690,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -17762,7 +17762,7 @@
         </is>
       </c>
       <c r="G458" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="20" t="inlineStr"/>
     </row>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="G467" s="18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H467" s="20" t="inlineStr"/>
     </row>
@@ -18122,7 +18122,7 @@
         </is>
       </c>
       <c r="G468" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H468" s="20" t="inlineStr"/>
     </row>
@@ -18158,7 +18158,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="G470" s="18" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H470" s="20" t="inlineStr"/>
     </row>
@@ -18230,7 +18230,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -18302,7 +18302,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -18374,7 +18374,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
@@ -18770,7 +18770,7 @@
         </is>
       </c>
       <c r="G486" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H486" s="20" t="inlineStr"/>
     </row>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="G487" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="20" t="inlineStr"/>
     </row>
@@ -18842,7 +18842,7 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
@@ -18914,45 +18914,54 @@
         </is>
       </c>
       <c r="G490" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="20" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
-      <c r="A491" s="18" t="inlineStr">
+      <c r="A491" s="21" t="inlineStr">
         <is>
           <t>TC_PERF_030</t>
         </is>
       </c>
-      <c r="B491" s="18" t="inlineStr">
+      <c r="B491" s="21" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C491" s="18" t="inlineStr">
+      <c r="C491" s="21" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D491" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E491" s="19" t="inlineStr">
+      <c r="D491" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E491" s="22" t="inlineStr">
         <is>
           <t>Performance smoke test #30</t>
         </is>
       </c>
-      <c r="F491" s="18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G491" s="18" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H491" s="20" t="inlineStr"/>
+      <c r="F491" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G491" s="21" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="H491" s="23" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.004
+  (Session info: chrome=150.0.7871.128)
+Stacktrace:
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f34646e35a &lt;unkno</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="18" t="inlineStr">
@@ -19022,7 +19031,7 @@
         </is>
       </c>
       <c r="G493" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H493" s="20" t="inlineStr"/>
     </row>
@@ -19058,7 +19067,7 @@
         </is>
       </c>
       <c r="G494" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="20" t="inlineStr"/>
     </row>
@@ -19094,7 +19103,7 @@
         </is>
       </c>
       <c r="G495" s="18" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H495" s="20" t="inlineStr"/>
     </row>
@@ -19130,7 +19139,7 @@
         </is>
       </c>
       <c r="G496" s="18" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H496" s="20" t="inlineStr"/>
     </row>
@@ -19166,7 +19175,7 @@
         </is>
       </c>
       <c r="G497" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="20" t="inlineStr"/>
     </row>
@@ -19202,7 +19211,7 @@
         </is>
       </c>
       <c r="G498" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H498" s="20" t="inlineStr"/>
     </row>
@@ -19274,7 +19283,7 @@
         </is>
       </c>
       <c r="G500" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H500" s="20" t="inlineStr"/>
     </row>
@@ -19326,7 +19335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H490"/>
+  <dimension ref="A1:H489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19413,7 +19422,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>3.75</v>
+        <v>0.36</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -19449,7 +19458,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -19485,7 +19494,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -19521,7 +19530,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>1.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -19557,7 +19566,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -19593,7 +19602,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -19629,7 +19638,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -19665,7 +19674,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -19701,7 +19710,7 @@
         </is>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
     </row>
@@ -19737,7 +19746,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -19773,7 +19782,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -19809,7 +19818,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -19845,7 +19854,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -19881,7 +19890,7 @@
         </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
     </row>
@@ -19917,7 +19926,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -19953,7 +19962,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -19989,7 +19998,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -20025,7 +20034,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -20169,7 +20178,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -20205,7 +20214,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -20241,7 +20250,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -20277,7 +20286,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -20313,7 +20322,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -20385,7 +20394,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -20421,7 +20430,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -20457,7 +20466,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -20493,7 +20502,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -20529,7 +20538,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -20565,7 +20574,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -20601,7 +20610,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -20637,7 +20646,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -20673,7 +20682,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -20745,7 +20754,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -20781,7 +20790,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -20817,7 +20826,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -20925,7 +20934,7 @@
         </is>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H44" s="20" t="inlineStr"/>
     </row>
@@ -20961,7 +20970,7 @@
         </is>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H45" s="20" t="inlineStr"/>
     </row>
@@ -20997,7 +21006,7 @@
         </is>
       </c>
       <c r="G46" s="18" t="n">
-        <v>21.16</v>
+        <v>21.18</v>
       </c>
       <c r="H46" s="20" t="inlineStr"/>
     </row>
@@ -21033,7 +21042,7 @@
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>21.12</v>
+        <v>21.21</v>
       </c>
       <c r="H47" s="20" t="inlineStr"/>
     </row>
@@ -21069,7 +21078,7 @@
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H48" s="20" t="inlineStr"/>
     </row>
@@ -21105,7 +21114,7 @@
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H49" s="20" t="inlineStr"/>
     </row>
@@ -21141,7 +21150,7 @@
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="H50" s="20" t="inlineStr"/>
     </row>
@@ -21177,7 +21186,7 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H51" s="20" t="inlineStr"/>
     </row>
@@ -21213,7 +21222,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -21249,7 +21258,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -21285,7 +21294,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -21321,7 +21330,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -21357,7 +21366,7 @@
         </is>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H56" s="20" t="inlineStr"/>
     </row>
@@ -21393,7 +21402,7 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H57" s="20" t="inlineStr"/>
     </row>
@@ -21429,7 +21438,7 @@
         </is>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H58" s="20" t="inlineStr"/>
     </row>
@@ -21465,7 +21474,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -21501,7 +21510,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -21609,7 +21618,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -21645,7 +21654,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -21681,7 +21690,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -21753,7 +21762,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -21789,7 +21798,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -21861,7 +21870,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -21897,7 +21906,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -21969,7 +21978,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -22005,7 +22014,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -22041,7 +22050,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -22077,7 +22086,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -22149,7 +22158,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -22221,7 +22230,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -22257,7 +22266,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -22293,7 +22302,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -22329,7 +22338,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -22365,7 +22374,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -22401,7 +22410,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -22437,7 +22446,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -22473,7 +22482,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -22509,7 +22518,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -22581,7 +22590,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -22617,7 +22626,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -22689,7 +22698,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -22761,7 +22770,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -22797,7 +22806,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -22833,7 +22842,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -22869,7 +22878,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -22905,7 +22914,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -22941,7 +22950,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -23013,7 +23022,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -23049,7 +23058,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -23157,7 +23166,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -23229,7 +23238,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -23265,7 +23274,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -23301,7 +23310,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -23337,7 +23346,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -23373,7 +23382,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -23409,7 +23418,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -23445,7 +23454,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -23481,7 +23490,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -23517,7 +23526,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -23553,7 +23562,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -23589,7 +23598,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -23625,7 +23634,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -23661,7 +23670,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -23697,7 +23706,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -23733,7 +23742,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -23769,7 +23778,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -23805,7 +23814,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -23841,7 +23850,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -23877,7 +23886,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -23913,7 +23922,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -23949,7 +23958,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -23985,7 +23994,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -24021,7 +24030,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -24057,7 +24066,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -24093,7 +24102,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -24129,7 +24138,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -24165,7 +24174,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -24201,7 +24210,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -24273,7 +24282,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -24309,7 +24318,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -24345,7 +24354,7 @@
         </is>
       </c>
       <c r="G139" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H139" s="20" t="inlineStr"/>
     </row>
@@ -24381,7 +24390,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -24453,7 +24462,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -24489,7 +24498,7 @@
         </is>
       </c>
       <c r="G143" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H143" s="20" t="inlineStr"/>
     </row>
@@ -24525,7 +24534,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -24561,7 +24570,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -24597,7 +24606,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -24633,7 +24642,7 @@
         </is>
       </c>
       <c r="G147" s="18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H147" s="20" t="inlineStr"/>
     </row>
@@ -24669,7 +24678,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -24705,7 +24714,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -24741,7 +24750,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -24777,7 +24786,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -24849,7 +24858,7 @@
         </is>
       </c>
       <c r="G153" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H153" s="20" t="inlineStr"/>
     </row>
@@ -24921,7 +24930,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -24957,7 +24966,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -25029,7 +25038,7 @@
         </is>
       </c>
       <c r="G158" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H158" s="20" t="inlineStr"/>
     </row>
@@ -25065,7 +25074,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -25101,7 +25110,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -25137,7 +25146,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -25173,7 +25182,7 @@
         </is>
       </c>
       <c r="G162" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="20" t="inlineStr"/>
     </row>
@@ -25209,7 +25218,7 @@
         </is>
       </c>
       <c r="G163" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="20" t="inlineStr"/>
     </row>
@@ -25245,7 +25254,7 @@
         </is>
       </c>
       <c r="G164" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="20" t="inlineStr"/>
     </row>
@@ -25353,7 +25362,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -25389,7 +25398,7 @@
         </is>
       </c>
       <c r="G168" s="18" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H168" s="20" t="inlineStr"/>
     </row>
@@ -25425,7 +25434,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -25497,7 +25506,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -25533,7 +25542,7 @@
         </is>
       </c>
       <c r="G172" s="18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H172" s="20" t="inlineStr"/>
     </row>
@@ -25569,7 +25578,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -25605,7 +25614,7 @@
         </is>
       </c>
       <c r="G174" s="18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H174" s="20" t="inlineStr"/>
     </row>
@@ -25641,7 +25650,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -25677,7 +25686,7 @@
         </is>
       </c>
       <c r="G176" s="18" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="H176" s="20" t="inlineStr"/>
     </row>
@@ -25749,7 +25758,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -25785,7 +25794,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -25821,7 +25830,7 @@
         </is>
       </c>
       <c r="G180" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H180" s="20" t="inlineStr"/>
     </row>
@@ -25857,7 +25866,7 @@
         </is>
       </c>
       <c r="G181" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H181" s="20" t="inlineStr"/>
     </row>
@@ -25929,7 +25938,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -26001,7 +26010,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -26037,7 +26046,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -26109,7 +26118,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -26181,7 +26190,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -26217,7 +26226,7 @@
         </is>
       </c>
       <c r="G191" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H191" s="20" t="inlineStr"/>
     </row>
@@ -26289,7 +26298,7 @@
         </is>
       </c>
       <c r="G193" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H193" s="20" t="inlineStr"/>
     </row>
@@ -26397,7 +26406,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -26433,7 +26442,7 @@
         </is>
       </c>
       <c r="G197" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="20" t="inlineStr"/>
     </row>
@@ -26469,7 +26478,7 @@
         </is>
       </c>
       <c r="G198" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="20" t="inlineStr"/>
     </row>
@@ -26541,7 +26550,7 @@
         </is>
       </c>
       <c r="G200" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="20" t="inlineStr"/>
     </row>
@@ -26577,7 +26586,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -26613,7 +26622,7 @@
         </is>
       </c>
       <c r="G202" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="20" t="inlineStr"/>
     </row>
@@ -26649,7 +26658,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -26685,7 +26694,7 @@
         </is>
       </c>
       <c r="G204" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="20" t="inlineStr"/>
     </row>
@@ -26721,7 +26730,7 @@
         </is>
       </c>
       <c r="G205" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="20" t="inlineStr"/>
     </row>
@@ -26757,7 +26766,7 @@
         </is>
       </c>
       <c r="G206" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="20" t="inlineStr"/>
     </row>
@@ -26793,7 +26802,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -26829,7 +26838,7 @@
         </is>
       </c>
       <c r="G208" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="20" t="inlineStr"/>
     </row>
@@ -26901,7 +26910,7 @@
         </is>
       </c>
       <c r="G210" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="20" t="inlineStr"/>
     </row>
@@ -27009,7 +27018,7 @@
         </is>
       </c>
       <c r="G213" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H213" s="20" t="inlineStr"/>
     </row>
@@ -27045,7 +27054,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -27081,7 +27090,7 @@
         </is>
       </c>
       <c r="G215" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="20" t="inlineStr"/>
     </row>
@@ -27153,7 +27162,7 @@
         </is>
       </c>
       <c r="G217" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="20" t="inlineStr"/>
     </row>
@@ -27189,7 +27198,7 @@
         </is>
       </c>
       <c r="G218" s="18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="20" t="inlineStr"/>
     </row>
@@ -27225,7 +27234,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -27297,7 +27306,7 @@
         </is>
       </c>
       <c r="G221" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="20" t="inlineStr"/>
     </row>
@@ -27333,7 +27342,7 @@
         </is>
       </c>
       <c r="G222" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H222" s="20" t="inlineStr"/>
     </row>
@@ -27369,7 +27378,7 @@
         </is>
       </c>
       <c r="G223" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="20" t="inlineStr"/>
     </row>
@@ -27405,7 +27414,7 @@
         </is>
       </c>
       <c r="G224" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="20" t="inlineStr"/>
     </row>
@@ -27477,7 +27486,7 @@
         </is>
       </c>
       <c r="G226" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H226" s="20" t="inlineStr"/>
     </row>
@@ -27513,7 +27522,7 @@
         </is>
       </c>
       <c r="G227" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="20" t="inlineStr"/>
     </row>
@@ -27585,7 +27594,7 @@
         </is>
       </c>
       <c r="G229" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="20" t="inlineStr"/>
     </row>
@@ -27621,7 +27630,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -27657,7 +27666,7 @@
         </is>
       </c>
       <c r="G231" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="20" t="inlineStr"/>
     </row>
@@ -27693,7 +27702,7 @@
         </is>
       </c>
       <c r="G232" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="20" t="inlineStr"/>
     </row>
@@ -27801,7 +27810,7 @@
         </is>
       </c>
       <c r="G235" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="20" t="inlineStr"/>
     </row>
@@ -27837,7 +27846,7 @@
         </is>
       </c>
       <c r="G236" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H236" s="20" t="inlineStr"/>
     </row>
@@ -27873,7 +27882,7 @@
         </is>
       </c>
       <c r="G237" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="20" t="inlineStr"/>
     </row>
@@ -27909,7 +27918,7 @@
         </is>
       </c>
       <c r="G238" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="20" t="inlineStr"/>
     </row>
@@ -27945,7 +27954,7 @@
         </is>
       </c>
       <c r="G239" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="20" t="inlineStr"/>
     </row>
@@ -27981,7 +27990,7 @@
         </is>
       </c>
       <c r="G240" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="20" t="inlineStr"/>
     </row>
@@ -28017,7 +28026,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -28161,7 +28170,7 @@
         </is>
       </c>
       <c r="G245" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="20" t="inlineStr"/>
     </row>
@@ -28233,7 +28242,7 @@
         </is>
       </c>
       <c r="G247" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="20" t="inlineStr"/>
     </row>
@@ -28269,7 +28278,7 @@
         </is>
       </c>
       <c r="G248" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="20" t="inlineStr"/>
     </row>
@@ -28305,7 +28314,7 @@
         </is>
       </c>
       <c r="G249" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="20" t="inlineStr"/>
     </row>
@@ -28341,7 +28350,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -28449,7 +28458,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -28521,7 +28530,7 @@
         </is>
       </c>
       <c r="G255" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H255" s="20" t="inlineStr"/>
     </row>
@@ -28557,7 +28566,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -28629,7 +28638,7 @@
         </is>
       </c>
       <c r="G258" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H258" s="20" t="inlineStr"/>
     </row>
@@ -28701,7 +28710,7 @@
         </is>
       </c>
       <c r="G260" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H260" s="20" t="inlineStr"/>
     </row>
@@ -28737,7 +28746,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -28881,7 +28890,7 @@
         </is>
       </c>
       <c r="G265" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="20" t="inlineStr"/>
     </row>
@@ -28917,7 +28926,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -28953,7 +28962,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -28989,7 +28998,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -29025,7 +29034,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -29133,7 +29142,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -29169,7 +29178,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -29241,7 +29250,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -29349,7 +29358,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -29421,7 +29430,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -29565,7 +29574,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -29637,7 +29646,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -29745,7 +29754,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -29781,7 +29790,7 @@
         </is>
       </c>
       <c r="G290" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="20" t="inlineStr"/>
     </row>
@@ -29817,7 +29826,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -29889,7 +29898,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -29925,7 +29934,7 @@
         </is>
       </c>
       <c r="G294" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H294" s="20" t="inlineStr"/>
     </row>
@@ -29961,7 +29970,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -29997,7 +30006,7 @@
         </is>
       </c>
       <c r="G296" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="20" t="inlineStr"/>
     </row>
@@ -30033,7 +30042,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -30069,7 +30078,7 @@
         </is>
       </c>
       <c r="G298" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="20" t="inlineStr"/>
     </row>
@@ -30141,7 +30150,7 @@
         </is>
       </c>
       <c r="G300" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="20" t="inlineStr"/>
     </row>
@@ -30213,7 +30222,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -30249,7 +30258,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -30357,7 +30366,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -30393,7 +30402,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -30429,7 +30438,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -30465,7 +30474,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -30501,7 +30510,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -30537,7 +30546,7 @@
         </is>
       </c>
       <c r="G311" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H311" s="20" t="inlineStr"/>
     </row>
@@ -30609,7 +30618,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -30717,7 +30726,7 @@
         </is>
       </c>
       <c r="G316" s="18" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H316" s="20" t="inlineStr"/>
     </row>
@@ -30753,7 +30762,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -30789,7 +30798,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -30825,7 +30834,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -30861,7 +30870,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -30897,7 +30906,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -30933,7 +30942,7 @@
         </is>
       </c>
       <c r="G322" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="20" t="inlineStr"/>
     </row>
@@ -31005,7 +31014,7 @@
         </is>
       </c>
       <c r="G324" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H324" s="20" t="inlineStr"/>
     </row>
@@ -31041,7 +31050,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -31077,7 +31086,7 @@
         </is>
       </c>
       <c r="G326" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H326" s="20" t="inlineStr"/>
     </row>
@@ -31149,7 +31158,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -31221,7 +31230,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -31293,7 +31302,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -31401,7 +31410,7 @@
         </is>
       </c>
       <c r="G335" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="20" t="inlineStr"/>
     </row>
@@ -31473,7 +31482,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -31545,7 +31554,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -31581,7 +31590,7 @@
         </is>
       </c>
       <c r="G340" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H340" s="20" t="inlineStr"/>
     </row>
@@ -31617,7 +31626,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -31833,7 +31842,7 @@
         </is>
       </c>
       <c r="G347" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="20" t="inlineStr"/>
     </row>
@@ -31869,7 +31878,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -31941,7 +31950,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -31977,7 +31986,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -32049,7 +32058,7 @@
         </is>
       </c>
       <c r="G353" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="20" t="inlineStr"/>
     </row>
@@ -32085,7 +32094,7 @@
         </is>
       </c>
       <c r="G354" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H354" s="20" t="inlineStr"/>
     </row>
@@ -32121,7 +32130,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -32157,7 +32166,7 @@
         </is>
       </c>
       <c r="G356" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="20" t="inlineStr"/>
     </row>
@@ -32193,7 +32202,7 @@
         </is>
       </c>
       <c r="G357" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="20" t="inlineStr"/>
     </row>
@@ -32229,7 +32238,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -32373,7 +32382,7 @@
         </is>
       </c>
       <c r="G362" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="20" t="inlineStr"/>
     </row>
@@ -32409,7 +32418,7 @@
         </is>
       </c>
       <c r="G363" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H363" s="20" t="inlineStr"/>
     </row>
@@ -32445,7 +32454,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -32517,7 +32526,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -32553,7 +32562,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -32589,7 +32598,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -32625,7 +32634,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -32661,7 +32670,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -32697,7 +32706,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -32733,7 +32742,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -32769,7 +32778,7 @@
         </is>
       </c>
       <c r="G373" s="18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H373" s="20" t="inlineStr"/>
     </row>
@@ -32805,7 +32814,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -32841,7 +32850,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -32877,7 +32886,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -32913,7 +32922,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -32985,7 +32994,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -33021,7 +33030,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -33057,7 +33066,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -33093,7 +33102,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -33129,7 +33138,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -33165,7 +33174,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -33201,7 +33210,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -33237,7 +33246,7 @@
         </is>
       </c>
       <c r="G386" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H386" s="20" t="inlineStr"/>
     </row>
@@ -33273,7 +33282,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -33309,7 +33318,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -33417,7 +33426,7 @@
         </is>
       </c>
       <c r="G391" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="20" t="inlineStr"/>
     </row>
@@ -33453,7 +33462,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -33489,7 +33498,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -33525,7 +33534,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -33561,7 +33570,7 @@
         </is>
       </c>
       <c r="G395" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="20" t="inlineStr"/>
     </row>
@@ -33597,7 +33606,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -33633,7 +33642,7 @@
         </is>
       </c>
       <c r="G397" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H397" s="20" t="inlineStr"/>
     </row>
@@ -33669,7 +33678,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -33705,7 +33714,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -33741,7 +33750,7 @@
         </is>
       </c>
       <c r="G400" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="20" t="inlineStr"/>
     </row>
@@ -33813,7 +33822,7 @@
         </is>
       </c>
       <c r="G402" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H402" s="20" t="inlineStr"/>
     </row>
@@ -33849,7 +33858,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -33885,7 +33894,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -33921,7 +33930,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -33993,7 +34002,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -34029,7 +34038,7 @@
         </is>
       </c>
       <c r="G408" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="20" t="inlineStr"/>
     </row>
@@ -34065,7 +34074,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -34101,7 +34110,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -34137,7 +34146,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -34173,7 +34182,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -34245,7 +34254,7 @@
         </is>
       </c>
       <c r="G414" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="20" t="inlineStr"/>
     </row>
@@ -34281,7 +34290,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -34317,7 +34326,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -34353,7 +34362,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -34389,7 +34398,7 @@
         </is>
       </c>
       <c r="G418" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H418" s="20" t="inlineStr"/>
     </row>
@@ -34461,7 +34470,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -34497,7 +34506,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -34533,7 +34542,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -34569,7 +34578,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -34605,7 +34614,7 @@
         </is>
       </c>
       <c r="G424" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H424" s="20" t="inlineStr"/>
     </row>
@@ -34641,7 +34650,7 @@
         </is>
       </c>
       <c r="G425" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H425" s="20" t="inlineStr"/>
     </row>
@@ -34677,7 +34686,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -34785,7 +34794,7 @@
         </is>
       </c>
       <c r="G429" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="20" t="inlineStr"/>
     </row>
@@ -34821,7 +34830,7 @@
         </is>
       </c>
       <c r="G430" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="20" t="inlineStr"/>
     </row>
@@ -34857,7 +34866,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -35001,7 +35010,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -35037,7 +35046,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -35073,7 +35082,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -35109,7 +35118,7 @@
         </is>
       </c>
       <c r="G438" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="20" t="inlineStr"/>
     </row>
@@ -35145,7 +35154,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -35181,7 +35190,7 @@
         </is>
       </c>
       <c r="G440" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="20" t="inlineStr"/>
     </row>
@@ -35361,7 +35370,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -35397,7 +35406,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -35433,7 +35442,7 @@
         </is>
       </c>
       <c r="G447" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="20" t="inlineStr"/>
     </row>
@@ -35469,7 +35478,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -35505,7 +35514,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -35577,7 +35586,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -35613,7 +35622,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -35649,7 +35658,7 @@
         </is>
       </c>
       <c r="G453" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H453" s="20" t="inlineStr"/>
     </row>
@@ -35721,7 +35730,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -35757,7 +35766,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -35793,7 +35802,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -35829,7 +35838,7 @@
         </is>
       </c>
       <c r="G458" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H458" s="20" t="inlineStr"/>
     </row>
@@ -35865,7 +35874,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -35901,7 +35910,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -35973,7 +35982,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -36009,7 +36018,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -36045,7 +36054,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -36117,7 +36126,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -36225,7 +36234,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -36297,7 +36306,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -36333,7 +36342,7 @@
         </is>
       </c>
       <c r="G472" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="20" t="inlineStr"/>
     </row>
@@ -36369,7 +36378,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -36405,7 +36414,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -36441,7 +36450,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -36477,7 +36486,7 @@
         </is>
       </c>
       <c r="G476" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="20" t="inlineStr"/>
     </row>
@@ -36513,7 +36522,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -36585,14 +36594,14 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B480" s="18" t="inlineStr">
@@ -36612,7 +36621,7 @@
       </c>
       <c r="E480" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F480" s="18" t="inlineStr">
@@ -36621,14 +36630,14 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B481" s="18" t="inlineStr">
@@ -36648,7 +36657,7 @@
       </c>
       <c r="E481" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F481" s="18" t="inlineStr">
@@ -36657,14 +36666,14 @@
         </is>
       </c>
       <c r="G481" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="20" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B482" s="18" t="inlineStr">
@@ -36684,7 +36693,7 @@
       </c>
       <c r="E482" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F482" s="18" t="inlineStr">
@@ -36693,14 +36702,14 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B483" s="18" t="inlineStr">
@@ -36720,7 +36729,7 @@
       </c>
       <c r="E483" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F483" s="18" t="inlineStr">
@@ -36729,14 +36738,14 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B484" s="18" t="inlineStr">
@@ -36756,7 +36765,7 @@
       </c>
       <c r="E484" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F484" s="18" t="inlineStr">
@@ -36765,14 +36774,14 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B485" s="18" t="inlineStr">
@@ -36792,7 +36801,7 @@
       </c>
       <c r="E485" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F485" s="18" t="inlineStr">
@@ -36808,7 +36817,7 @@
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B486" s="18" t="inlineStr">
@@ -36828,7 +36837,7 @@
       </c>
       <c r="E486" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F486" s="18" t="inlineStr">
@@ -36837,14 +36846,14 @@
         </is>
       </c>
       <c r="G486" s="18" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="20" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B487" s="18" t="inlineStr">
@@ -36864,7 +36873,7 @@
       </c>
       <c r="E487" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F487" s="18" t="inlineStr">
@@ -36880,7 +36889,7 @@
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B488" s="18" t="inlineStr">
@@ -36900,7 +36909,7 @@
       </c>
       <c r="E488" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F488" s="18" t="inlineStr">
@@ -36909,14 +36918,14 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_040</t>
         </is>
       </c>
       <c r="B489" s="18" t="inlineStr">
@@ -36936,7 +36945,7 @@
       </c>
       <c r="E489" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #40</t>
         </is>
       </c>
       <c r="F489" s="18" t="inlineStr">
@@ -36949,44 +36958,8 @@
       </c>
       <c r="H489" s="20" t="inlineStr"/>
     </row>
-    <row r="490" ht="16" customHeight="1">
-      <c r="A490" s="18" t="inlineStr">
-        <is>
-          <t>TC_PERF_040</t>
-        </is>
-      </c>
-      <c r="B490" s="18" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C490" s="18" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D490" s="18" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E490" s="19" t="inlineStr">
-        <is>
-          <t>Performance smoke test #40</t>
-        </is>
-      </c>
-      <c r="F490" s="18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G490" s="18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H490" s="20" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H490"/>
+  <autoFilter ref="A1:H489"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36997,7 +36970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37084,7 +37057,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
@@ -37124,7 +37097,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
@@ -37164,7 +37137,7 @@
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>10.35</v>
+        <v>10.34</v>
       </c>
       <c r="H4" s="23" t="inlineStr"/>
     </row>
@@ -37200,19 +37173,19 @@
         </is>
       </c>
       <c r="G5" s="21" t="n">
-        <v>21.33</v>
+        <v>21.39</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37248,19 +37221,19 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>22.08</v>
+        <v>22.05</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37296,19 +37269,19 @@
         </is>
       </c>
       <c r="G7" s="21" t="n">
-        <v>22.02</v>
+        <v>22.07</v>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37344,19 +37317,19 @@
         </is>
       </c>
       <c r="G8" s="21" t="n">
-        <v>22.11</v>
+        <v>22.15</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37392,19 +37365,19 @@
         </is>
       </c>
       <c r="G9" s="21" t="n">
-        <v>22.08</v>
+        <v>22.18</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37440,19 +37413,19 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>22.05</v>
+        <v>22.12</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37488,19 +37461,19 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>22.1</v>
+        <v>22.15</v>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
         </is>
       </c>
     </row>
@@ -37536,24 +37509,69 @@
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>22.31</v>
+        <v>22.45</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x557efabc344a &lt;unknown&gt;
-#1 0x557efa59b8c9 &lt;unknown&gt;
-#2 0x557efa5f0f32 &lt;unknown&gt;
-#3 0x557efa5f1181 &lt;unknown&gt;
-#4 0x557efa63c374 &lt;unknown&gt;
-#5 0x557efa63955d &lt;unknown&gt;
-#6 0x557ef</t>
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f3464dbf32 &lt;unknown&gt;
+#3 0x55f3464dc181 &lt;unknown&gt;
+#4 0x55f346527374 &lt;unknown&gt;
+#5 0x55f34652455d &lt;unknown&gt;
+#6 0x55f34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>TC_PERF_030</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Performance smoke test #30</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.004
+  (Session info: chrome=150.0.7871.128)
+Stacktrace:
+#0 0x55f346aae44a &lt;unknown&gt;
+#1 0x55f3464868c9 &lt;unknown&gt;
+#2 0x55f34646e35a &lt;unkno</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37758,14 +37776,14 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
     </row>
@@ -37923,7 +37941,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
@@ -37944,7 +37962,7 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="29" t="inlineStr">
         <is>
@@ -37965,7 +37983,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>1.61s</t>
+          <t>1.67s</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$489</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -704,7 +704,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-26T06:11:50    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-27T06:39:40    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -748,22 +748,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>489</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.67s</t>
+          <t>1.6s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.05s</t>
+          <t>1.04s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>3.44s</t>
+          <t>3.42s</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.89s</t>
+          <t>0.88s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.17s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1074,19 +1074,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.36</v>
+        <v>0.84</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="H43" s="20" t="inlineStr"/>
     </row>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="20" t="inlineStr"/>
     </row>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="G45" s="21" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="H45" s="23" t="inlineStr"/>
     </row>
@@ -2870,19 +2870,19 @@
         </is>
       </c>
       <c r="G47" s="21" t="n">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="G48" s="21" t="n">
-        <v>22.05</v>
+        <v>21.95</v>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="G49" s="21" t="n">
-        <v>22.07</v>
+        <v>22.01</v>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3014,19 +3014,19 @@
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>22.15</v>
+        <v>22.07</v>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="G51" s="21" t="n">
-        <v>22.18</v>
+        <v>22.09</v>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>21.18</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>21.21</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="G56" s="21" t="n">
-        <v>22.12</v>
+        <v>22.07</v>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="G57" s="21" t="n">
-        <v>22.15</v>
+        <v>22.1</v>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3350,19 +3350,19 @@
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>22.45</v>
+        <v>22.34</v>
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H72" s="20" t="inlineStr"/>
     </row>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H77" s="20" t="inlineStr"/>
     </row>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H104" s="20" t="inlineStr"/>
     </row>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="G143" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="20" t="inlineStr"/>
     </row>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="G147" s="18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H147" s="20" t="inlineStr"/>
     </row>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="20" t="inlineStr"/>
     </row>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G153" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="20" t="inlineStr"/>
     </row>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="G157" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="20" t="inlineStr"/>
     </row>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="G158" s="18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="20" t="inlineStr"/>
     </row>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="G162" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="20" t="inlineStr"/>
     </row>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="G163" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H163" s="20" t="inlineStr"/>
     </row>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G164" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="20" t="inlineStr"/>
     </row>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="G165" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H165" s="20" t="inlineStr"/>
     </row>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="G166" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H166" s="20" t="inlineStr"/>
     </row>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="G168" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H168" s="20" t="inlineStr"/>
     </row>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="G172" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="20" t="inlineStr"/>
     </row>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="G176" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H176" s="20" t="inlineStr"/>
     </row>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="G182" s="18" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="H182" s="20" t="inlineStr"/>
     </row>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="G184" s="18" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H184" s="20" t="inlineStr"/>
     </row>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="G187" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="20" t="inlineStr"/>
     </row>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>12.07</v>
+        <v>12.1</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="G191" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="20" t="inlineStr"/>
     </row>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G192" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="20" t="inlineStr"/>
     </row>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="G195" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="20" t="inlineStr"/>
     </row>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="G197" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="20" t="inlineStr"/>
     </row>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="G198" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="20" t="inlineStr"/>
     </row>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="G200" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="20" t="inlineStr"/>
     </row>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="G202" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="20" t="inlineStr"/>
     </row>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="G204" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="20" t="inlineStr"/>
     </row>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G205" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="20" t="inlineStr"/>
     </row>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="G206" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="20" t="inlineStr"/>
     </row>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="G209" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="20" t="inlineStr"/>
     </row>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="G210" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="20" t="inlineStr"/>
     </row>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G211" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="20" t="inlineStr"/>
     </row>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="G212" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="20" t="inlineStr"/>
     </row>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="G213" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="20" t="inlineStr"/>
     </row>
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="G215" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="20" t="inlineStr"/>
     </row>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="G216" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="20" t="inlineStr"/>
     </row>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="G217" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="20" t="inlineStr"/>
     </row>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="G218" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="20" t="inlineStr"/>
     </row>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="G220" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="20" t="inlineStr"/>
     </row>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="G222" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="20" t="inlineStr"/>
     </row>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="G223" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="20" t="inlineStr"/>
     </row>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="G224" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="20" t="inlineStr"/>
     </row>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="G226" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="20" t="inlineStr"/>
     </row>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="G227" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H227" s="20" t="inlineStr"/>
     </row>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="G229" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="20" t="inlineStr"/>
     </row>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="G231" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="20" t="inlineStr"/>
     </row>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="G232" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="20" t="inlineStr"/>
     </row>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G233" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="20" t="inlineStr"/>
     </row>
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="G234" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="20" t="inlineStr"/>
     </row>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="G236" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="20" t="inlineStr"/>
     </row>
@@ -9806,7 +9806,7 @@
         </is>
       </c>
       <c r="G237" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="20" t="inlineStr"/>
     </row>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="G239" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="20" t="inlineStr"/>
     </row>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="G240" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H240" s="20" t="inlineStr"/>
     </row>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="G242" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H242" s="20" t="inlineStr"/>
     </row>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="G243" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="20" t="inlineStr"/>
     </row>
@@ -10058,7 +10058,7 @@
         </is>
       </c>
       <c r="G244" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="20" t="inlineStr"/>
     </row>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="G245" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="20" t="inlineStr"/>
     </row>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G246" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="20" t="inlineStr"/>
     </row>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="G248" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="20" t="inlineStr"/>
     </row>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="G249" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H249" s="20" t="inlineStr"/>
     </row>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="G251" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H251" s="20" t="inlineStr"/>
     </row>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="G255" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H255" s="20" t="inlineStr"/>
     </row>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="G257" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="20" t="inlineStr"/>
     </row>
@@ -10562,7 +10562,7 @@
         </is>
       </c>
       <c r="G258" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="20" t="inlineStr"/>
     </row>
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="G260" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H260" s="20" t="inlineStr"/>
     </row>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -10706,7 +10706,7 @@
         </is>
       </c>
       <c r="G262" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="20" t="inlineStr"/>
     </row>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="G263" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="20" t="inlineStr"/>
     </row>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="G265" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H265" s="20" t="inlineStr"/>
     </row>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="G270" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H270" s="20" t="inlineStr"/>
     </row>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G274" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="20" t="inlineStr"/>
     </row>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="G277" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="20" t="inlineStr"/>
     </row>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G287" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H287" s="20" t="inlineStr"/>
     </row>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="G290" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="20" t="inlineStr"/>
     </row>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -12074,7 +12074,7 @@
         </is>
       </c>
       <c r="G300" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H300" s="20" t="inlineStr"/>
     </row>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="G301" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="20" t="inlineStr"/>
     </row>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="G304" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H304" s="20" t="inlineStr"/>
     </row>
@@ -12254,7 +12254,7 @@
         </is>
       </c>
       <c r="G305" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="20" t="inlineStr"/>
     </row>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -12326,7 +12326,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -12506,7 +12506,7 @@
         </is>
       </c>
       <c r="G312" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="20" t="inlineStr"/>
     </row>
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="G316" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="20" t="inlineStr"/>
     </row>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="G322" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="20" t="inlineStr"/>
     </row>
@@ -12902,7 +12902,7 @@
         </is>
       </c>
       <c r="G323" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H323" s="20" t="inlineStr"/>
     </row>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="G324" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="20" t="inlineStr"/>
     </row>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="G327" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="20" t="inlineStr"/>
     </row>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="G329" s="18" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="H329" s="20" t="inlineStr"/>
     </row>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -13370,7 +13370,7 @@
         </is>
       </c>
       <c r="G336" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="20" t="inlineStr"/>
     </row>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -13586,7 +13586,7 @@
         </is>
       </c>
       <c r="G342" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="20" t="inlineStr"/>
     </row>
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="G344" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H344" s="20" t="inlineStr"/>
     </row>
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="G347" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H347" s="20" t="inlineStr"/>
     </row>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -13874,7 +13874,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="G352" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="20" t="inlineStr"/>
     </row>
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="G353" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="20" t="inlineStr"/>
     </row>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G356" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="20" t="inlineStr"/>
     </row>
@@ -14198,7 +14198,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="G360" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="20" t="inlineStr"/>
     </row>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="G362" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="20" t="inlineStr"/>
     </row>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -14486,7 +14486,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -14954,7 +14954,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -15062,7 +15062,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="G386" s="18" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H386" s="20" t="inlineStr"/>
     </row>
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -15242,7 +15242,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="G389" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H389" s="20" t="inlineStr"/>
     </row>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="G390" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="20" t="inlineStr"/>
     </row>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G395" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="20" t="inlineStr"/>
     </row>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G397" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="20" t="inlineStr"/>
     </row>
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -15674,7 +15674,7 @@
         </is>
       </c>
       <c r="G400" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="20" t="inlineStr"/>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="G408" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="20" t="inlineStr"/>
     </row>
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -16142,7 +16142,7 @@
         </is>
       </c>
       <c r="G413" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="20" t="inlineStr"/>
     </row>
@@ -16214,7 +16214,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -16322,7 +16322,7 @@
         </is>
       </c>
       <c r="G418" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="20" t="inlineStr"/>
     </row>
@@ -16394,7 +16394,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="G428" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="20" t="inlineStr"/>
     </row>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="G429" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="20" t="inlineStr"/>
     </row>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="G430" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H430" s="20" t="inlineStr"/>
     </row>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -16826,7 +16826,7 @@
         </is>
       </c>
       <c r="G432" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="20" t="inlineStr"/>
     </row>
@@ -16862,7 +16862,7 @@
         </is>
       </c>
       <c r="G433" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="20" t="inlineStr"/>
     </row>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="G434" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="20" t="inlineStr"/>
     </row>
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="G442" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="20" t="inlineStr"/>
     </row>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="G443" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="20" t="inlineStr"/>
     </row>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="G447" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="20" t="inlineStr"/>
     </row>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -17690,7 +17690,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -17762,7 +17762,7 @@
         </is>
       </c>
       <c r="G458" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="20" t="inlineStr"/>
     </row>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="G465" s="18" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="20" t="inlineStr"/>
     </row>
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -18122,7 +18122,7 @@
         </is>
       </c>
       <c r="G468" s="18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="20" t="inlineStr"/>
     </row>
@@ -18158,7 +18158,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="G470" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="20" t="inlineStr"/>
     </row>
@@ -18230,7 +18230,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -18266,7 +18266,7 @@
         </is>
       </c>
       <c r="G472" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="20" t="inlineStr"/>
     </row>
@@ -18302,7 +18302,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -18374,7 +18374,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -18410,7 +18410,7 @@
         </is>
       </c>
       <c r="G476" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="20" t="inlineStr"/>
     </row>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="G481" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H481" s="20" t="inlineStr"/>
     </row>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
@@ -18770,7 +18770,7 @@
         </is>
       </c>
       <c r="G486" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="20" t="inlineStr"/>
     </row>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
       <c r="G487" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="20" t="inlineStr"/>
     </row>
@@ -18842,7 +18842,7 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
@@ -18914,54 +18914,45 @@
         </is>
       </c>
       <c r="G490" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="20" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
-      <c r="A491" s="21" t="inlineStr">
+      <c r="A491" s="18" t="inlineStr">
         <is>
           <t>TC_PERF_030</t>
         </is>
       </c>
-      <c r="B491" s="21" t="inlineStr">
+      <c r="B491" s="18" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C491" s="21" t="inlineStr">
+      <c r="C491" s="18" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D491" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E491" s="22" t="inlineStr">
+      <c r="D491" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E491" s="19" t="inlineStr">
         <is>
           <t>Performance smoke test #30</t>
         </is>
       </c>
-      <c r="F491" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G491" s="21" t="n">
-        <v>30.19</v>
-      </c>
-      <c r="H491" s="23" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.004
-  (Session info: chrome=150.0.7871.128)
-Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f34646e35a &lt;unkno</t>
-        </is>
-      </c>
+      <c r="F491" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G491" s="18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H491" s="20" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="18" t="inlineStr">
@@ -19031,7 +19022,7 @@
         </is>
       </c>
       <c r="G493" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="20" t="inlineStr"/>
     </row>
@@ -19103,7 +19094,7 @@
         </is>
       </c>
       <c r="G495" s="18" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="20" t="inlineStr"/>
     </row>
@@ -19139,7 +19130,7 @@
         </is>
       </c>
       <c r="G496" s="18" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="20" t="inlineStr"/>
     </row>
@@ -19175,7 +19166,7 @@
         </is>
       </c>
       <c r="G497" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="20" t="inlineStr"/>
     </row>
@@ -19211,7 +19202,7 @@
         </is>
       </c>
       <c r="G498" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="20" t="inlineStr"/>
     </row>
@@ -19283,7 +19274,7 @@
         </is>
       </c>
       <c r="G500" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="20" t="inlineStr"/>
     </row>
@@ -19319,7 +19310,7 @@
         </is>
       </c>
       <c r="G501" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="20" t="inlineStr"/>
     </row>
@@ -19335,7 +19326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H489"/>
+  <dimension ref="A1:H490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19422,7 +19413,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.36</v>
+        <v>0.84</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -19458,7 +19449,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -19494,7 +19485,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -19530,7 +19521,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -19566,7 +19557,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -19602,7 +19593,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -19638,7 +19629,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -19674,7 +19665,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -19710,7 +19701,7 @@
         </is>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
     </row>
@@ -19746,7 +19737,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -19782,7 +19773,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -19818,7 +19809,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -19854,7 +19845,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -19890,7 +19881,7 @@
         </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
     </row>
@@ -19926,7 +19917,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -19962,7 +19953,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -19998,7 +19989,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -20070,7 +20061,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -20106,7 +20097,7 @@
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
@@ -20142,7 +20133,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -20178,7 +20169,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -20214,7 +20205,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -20250,7 +20241,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -20286,7 +20277,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -20322,7 +20313,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -20358,7 +20349,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -20430,7 +20421,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -20466,7 +20457,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -20502,7 +20493,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -20538,7 +20529,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -20574,7 +20565,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -20610,7 +20601,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -20646,7 +20637,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -20682,7 +20673,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -20754,7 +20745,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -20790,7 +20781,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -20826,7 +20817,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -20862,7 +20853,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -20934,7 +20925,7 @@
         </is>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="20" t="inlineStr"/>
     </row>
@@ -20970,7 +20961,7 @@
         </is>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="20" t="inlineStr"/>
     </row>
@@ -21006,7 +20997,7 @@
         </is>
       </c>
       <c r="G46" s="18" t="n">
-        <v>21.18</v>
+        <v>21.13</v>
       </c>
       <c r="H46" s="20" t="inlineStr"/>
     </row>
@@ -21042,7 +21033,7 @@
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>21.21</v>
+        <v>21.12</v>
       </c>
       <c r="H47" s="20" t="inlineStr"/>
     </row>
@@ -21078,7 +21069,7 @@
         </is>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="H48" s="20" t="inlineStr"/>
     </row>
@@ -21114,7 +21105,7 @@
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H49" s="20" t="inlineStr"/>
     </row>
@@ -21150,7 +21141,7 @@
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="H50" s="20" t="inlineStr"/>
     </row>
@@ -21186,7 +21177,7 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H51" s="20" t="inlineStr"/>
     </row>
@@ -21222,7 +21213,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -21258,7 +21249,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -21294,7 +21285,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -21330,7 +21321,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -21366,7 +21357,7 @@
         </is>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H56" s="20" t="inlineStr"/>
     </row>
@@ -21402,7 +21393,7 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H57" s="20" t="inlineStr"/>
     </row>
@@ -21474,7 +21465,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -21510,7 +21501,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -21546,7 +21537,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -21582,7 +21573,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -21618,7 +21609,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -21654,7 +21645,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -21690,7 +21681,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -21726,7 +21717,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -21762,7 +21753,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -21798,7 +21789,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -21834,7 +21825,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -21870,7 +21861,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -21906,7 +21897,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -21942,7 +21933,7 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H72" s="20" t="inlineStr"/>
     </row>
@@ -21978,7 +21969,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -22014,7 +22005,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -22050,7 +22041,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -22086,7 +22077,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -22122,7 +22113,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="20" t="inlineStr"/>
     </row>
@@ -22158,7 +22149,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -22230,7 +22221,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -22266,7 +22257,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -22302,7 +22293,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -22338,7 +22329,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -22374,7 +22365,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -22410,7 +22401,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -22446,7 +22437,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -22482,7 +22473,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -22518,7 +22509,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -22554,7 +22545,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -22590,7 +22581,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -22626,7 +22617,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -22662,7 +22653,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -22698,7 +22689,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -22734,7 +22725,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -22770,7 +22761,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -22806,7 +22797,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -22842,7 +22833,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -22878,7 +22869,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -22914,7 +22905,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -22950,7 +22941,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -22986,7 +22977,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -23022,7 +23013,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -23058,7 +23049,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -23094,7 +23085,7 @@
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H104" s="20" t="inlineStr"/>
     </row>
@@ -23130,7 +23121,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -23166,7 +23157,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -23202,7 +23193,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -23238,7 +23229,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -23274,7 +23265,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -23310,7 +23301,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -23382,7 +23373,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -23418,7 +23409,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -23454,7 +23445,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -23490,7 +23481,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -23526,7 +23517,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -23598,7 +23589,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -23706,7 +23697,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -23742,7 +23733,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -23778,7 +23769,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -23922,7 +23913,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -23994,7 +23985,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -24030,7 +24021,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -24066,7 +24057,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -24102,7 +24093,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -24138,7 +24129,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -24210,7 +24201,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -24246,7 +24237,7 @@
         </is>
       </c>
       <c r="G136" s="18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H136" s="20" t="inlineStr"/>
     </row>
@@ -24282,7 +24273,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -24318,7 +24309,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -24354,7 +24345,7 @@
         </is>
       </c>
       <c r="G139" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H139" s="20" t="inlineStr"/>
     </row>
@@ -24390,7 +24381,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -24426,7 +24417,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -24462,7 +24453,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -24534,7 +24525,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -24570,7 +24561,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -24606,7 +24597,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -24642,7 +24633,7 @@
         </is>
       </c>
       <c r="G147" s="18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="20" t="inlineStr"/>
     </row>
@@ -24678,7 +24669,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -24714,7 +24705,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -24750,7 +24741,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -24786,7 +24777,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -24822,7 +24813,7 @@
         </is>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H152" s="20" t="inlineStr"/>
     </row>
@@ -24858,7 +24849,7 @@
         </is>
       </c>
       <c r="G153" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="20" t="inlineStr"/>
     </row>
@@ -24894,7 +24885,7 @@
         </is>
       </c>
       <c r="G154" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H154" s="20" t="inlineStr"/>
     </row>
@@ -24930,7 +24921,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -24966,7 +24957,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -25002,7 +24993,7 @@
         </is>
       </c>
       <c r="G157" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H157" s="20" t="inlineStr"/>
     </row>
@@ -25038,7 +25029,7 @@
         </is>
       </c>
       <c r="G158" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="20" t="inlineStr"/>
     </row>
@@ -25110,7 +25101,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -25146,7 +25137,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -25290,7 +25281,7 @@
         </is>
       </c>
       <c r="G165" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H165" s="20" t="inlineStr"/>
     </row>
@@ -25362,7 +25353,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -25398,7 +25389,7 @@
         </is>
       </c>
       <c r="G168" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="20" t="inlineStr"/>
     </row>
@@ -25506,7 +25497,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -25542,7 +25533,7 @@
         </is>
       </c>
       <c r="G172" s="18" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="H172" s="20" t="inlineStr"/>
     </row>
@@ -25578,7 +25569,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -25614,7 +25605,7 @@
         </is>
       </c>
       <c r="G174" s="18" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H174" s="20" t="inlineStr"/>
     </row>
@@ -25650,7 +25641,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -25686,7 +25677,7 @@
         </is>
       </c>
       <c r="G176" s="18" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H176" s="20" t="inlineStr"/>
     </row>
@@ -25722,7 +25713,7 @@
         </is>
       </c>
       <c r="G177" s="18" t="n">
-        <v>12.07</v>
+        <v>12.1</v>
       </c>
       <c r="H177" s="20" t="inlineStr"/>
     </row>
@@ -25830,7 +25821,7 @@
         </is>
       </c>
       <c r="G180" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H180" s="20" t="inlineStr"/>
     </row>
@@ -25866,7 +25857,7 @@
         </is>
       </c>
       <c r="G181" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H181" s="20" t="inlineStr"/>
     </row>
@@ -25938,7 +25929,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -25974,7 +25965,7 @@
         </is>
       </c>
       <c r="G184" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H184" s="20" t="inlineStr"/>
     </row>
@@ -26010,7 +26001,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -26046,7 +26037,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -26082,7 +26073,7 @@
         </is>
       </c>
       <c r="G187" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H187" s="20" t="inlineStr"/>
     </row>
@@ -26118,7 +26109,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -26154,7 +26145,7 @@
         </is>
       </c>
       <c r="G189" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H189" s="20" t="inlineStr"/>
     </row>
@@ -26190,7 +26181,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -26226,7 +26217,7 @@
         </is>
       </c>
       <c r="G191" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H191" s="20" t="inlineStr"/>
     </row>
@@ -26262,7 +26253,7 @@
         </is>
       </c>
       <c r="G192" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H192" s="20" t="inlineStr"/>
     </row>
@@ -26298,7 +26289,7 @@
         </is>
       </c>
       <c r="G193" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H193" s="20" t="inlineStr"/>
     </row>
@@ -26334,7 +26325,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -26370,7 +26361,7 @@
         </is>
       </c>
       <c r="G195" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H195" s="20" t="inlineStr"/>
     </row>
@@ -26406,7 +26397,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -26478,7 +26469,7 @@
         </is>
       </c>
       <c r="G198" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="20" t="inlineStr"/>
     </row>
@@ -26514,7 +26505,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -26550,7 +26541,7 @@
         </is>
       </c>
       <c r="G200" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="20" t="inlineStr"/>
     </row>
@@ -26586,7 +26577,7 @@
         </is>
       </c>
       <c r="G201" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="20" t="inlineStr"/>
     </row>
@@ -26622,7 +26613,7 @@
         </is>
       </c>
       <c r="G202" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="20" t="inlineStr"/>
     </row>
@@ -26658,7 +26649,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -26694,7 +26685,7 @@
         </is>
       </c>
       <c r="G204" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H204" s="20" t="inlineStr"/>
     </row>
@@ -26730,7 +26721,7 @@
         </is>
       </c>
       <c r="G205" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="20" t="inlineStr"/>
     </row>
@@ -26766,7 +26757,7 @@
         </is>
       </c>
       <c r="G206" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="20" t="inlineStr"/>
     </row>
@@ -26802,7 +26793,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -26874,7 +26865,7 @@
         </is>
       </c>
       <c r="G209" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="20" t="inlineStr"/>
     </row>
@@ -26946,7 +26937,7 @@
         </is>
       </c>
       <c r="G211" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="20" t="inlineStr"/>
     </row>
@@ -26982,7 +26973,7 @@
         </is>
       </c>
       <c r="G212" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="20" t="inlineStr"/>
     </row>
@@ -27018,7 +27009,7 @@
         </is>
       </c>
       <c r="G213" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="20" t="inlineStr"/>
     </row>
@@ -27090,7 +27081,7 @@
         </is>
       </c>
       <c r="G215" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="20" t="inlineStr"/>
     </row>
@@ -27126,7 +27117,7 @@
         </is>
       </c>
       <c r="G216" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="20" t="inlineStr"/>
     </row>
@@ -27198,7 +27189,7 @@
         </is>
       </c>
       <c r="G218" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="20" t="inlineStr"/>
     </row>
@@ -27234,7 +27225,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -27270,7 +27261,7 @@
         </is>
       </c>
       <c r="G220" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="20" t="inlineStr"/>
     </row>
@@ -27306,7 +27297,7 @@
         </is>
       </c>
       <c r="G221" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="20" t="inlineStr"/>
     </row>
@@ -27342,7 +27333,7 @@
         </is>
       </c>
       <c r="G222" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="20" t="inlineStr"/>
     </row>
@@ -27378,7 +27369,7 @@
         </is>
       </c>
       <c r="G223" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="20" t="inlineStr"/>
     </row>
@@ -27450,7 +27441,7 @@
         </is>
       </c>
       <c r="G225" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="20" t="inlineStr"/>
     </row>
@@ -27486,7 +27477,7 @@
         </is>
       </c>
       <c r="G226" s="18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="20" t="inlineStr"/>
     </row>
@@ -27558,7 +27549,7 @@
         </is>
       </c>
       <c r="G228" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H228" s="20" t="inlineStr"/>
     </row>
@@ -27594,7 +27585,7 @@
         </is>
       </c>
       <c r="G229" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H229" s="20" t="inlineStr"/>
     </row>
@@ -27630,7 +27621,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -27666,7 +27657,7 @@
         </is>
       </c>
       <c r="G231" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H231" s="20" t="inlineStr"/>
     </row>
@@ -27702,7 +27693,7 @@
         </is>
       </c>
       <c r="G232" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H232" s="20" t="inlineStr"/>
     </row>
@@ -27738,7 +27729,7 @@
         </is>
       </c>
       <c r="G233" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="20" t="inlineStr"/>
     </row>
@@ -27774,7 +27765,7 @@
         </is>
       </c>
       <c r="G234" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="20" t="inlineStr"/>
     </row>
@@ -27810,7 +27801,7 @@
         </is>
       </c>
       <c r="G235" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H235" s="20" t="inlineStr"/>
     </row>
@@ -27882,7 +27873,7 @@
         </is>
       </c>
       <c r="G237" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="20" t="inlineStr"/>
     </row>
@@ -27918,7 +27909,7 @@
         </is>
       </c>
       <c r="G238" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="20" t="inlineStr"/>
     </row>
@@ -27954,7 +27945,7 @@
         </is>
       </c>
       <c r="G239" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H239" s="20" t="inlineStr"/>
     </row>
@@ -27990,7 +27981,7 @@
         </is>
       </c>
       <c r="G240" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="20" t="inlineStr"/>
     </row>
@@ -28134,7 +28125,7 @@
         </is>
       </c>
       <c r="G244" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="20" t="inlineStr"/>
     </row>
@@ -28170,7 +28161,7 @@
         </is>
       </c>
       <c r="G245" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="20" t="inlineStr"/>
     </row>
@@ -28206,7 +28197,7 @@
         </is>
       </c>
       <c r="G246" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="20" t="inlineStr"/>
     </row>
@@ -28242,7 +28233,7 @@
         </is>
       </c>
       <c r="G247" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="20" t="inlineStr"/>
     </row>
@@ -28314,7 +28305,7 @@
         </is>
       </c>
       <c r="G249" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H249" s="20" t="inlineStr"/>
     </row>
@@ -28350,7 +28341,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -28386,7 +28377,7 @@
         </is>
       </c>
       <c r="G251" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H251" s="20" t="inlineStr"/>
     </row>
@@ -28422,7 +28413,7 @@
         </is>
       </c>
       <c r="G252" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H252" s="20" t="inlineStr"/>
     </row>
@@ -28458,7 +28449,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -28494,7 +28485,7 @@
         </is>
       </c>
       <c r="G254" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H254" s="20" t="inlineStr"/>
     </row>
@@ -28530,7 +28521,7 @@
         </is>
       </c>
       <c r="G255" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H255" s="20" t="inlineStr"/>
     </row>
@@ -28566,7 +28557,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -28674,7 +28665,7 @@
         </is>
       </c>
       <c r="G259" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H259" s="20" t="inlineStr"/>
     </row>
@@ -28746,7 +28737,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -28782,7 +28773,7 @@
         </is>
       </c>
       <c r="G262" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="20" t="inlineStr"/>
     </row>
@@ -28818,7 +28809,7 @@
         </is>
       </c>
       <c r="G263" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="20" t="inlineStr"/>
     </row>
@@ -28854,7 +28845,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -28926,7 +28917,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -28962,7 +28953,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -28998,7 +28989,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -29142,7 +29133,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -29178,7 +29169,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -29250,7 +29241,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -29286,7 +29277,7 @@
         </is>
       </c>
       <c r="G276" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H276" s="20" t="inlineStr"/>
     </row>
@@ -29358,7 +29349,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -29394,7 +29385,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -29430,7 +29421,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -29502,7 +29493,7 @@
         </is>
       </c>
       <c r="G282" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="20" t="inlineStr"/>
     </row>
@@ -29574,7 +29565,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -29646,7 +29637,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -29718,7 +29709,7 @@
         </is>
       </c>
       <c r="G288" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H288" s="20" t="inlineStr"/>
     </row>
@@ -29754,7 +29745,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -29790,7 +29781,7 @@
         </is>
       </c>
       <c r="G290" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="20" t="inlineStr"/>
     </row>
@@ -29862,7 +29853,7 @@
         </is>
       </c>
       <c r="G292" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H292" s="20" t="inlineStr"/>
     </row>
@@ -29898,7 +29889,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -29934,7 +29925,7 @@
         </is>
       </c>
       <c r="G294" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="20" t="inlineStr"/>
     </row>
@@ -29970,7 +29961,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -30006,7 +29997,7 @@
         </is>
       </c>
       <c r="G296" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="20" t="inlineStr"/>
     </row>
@@ -30042,7 +30033,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -30078,7 +30069,7 @@
         </is>
       </c>
       <c r="G298" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="20" t="inlineStr"/>
     </row>
@@ -30114,7 +30105,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -30186,7 +30177,7 @@
         </is>
       </c>
       <c r="G301" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="20" t="inlineStr"/>
     </row>
@@ -30222,7 +30213,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -30258,7 +30249,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -30330,7 +30321,7 @@
         </is>
       </c>
       <c r="G305" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="20" t="inlineStr"/>
     </row>
@@ -30402,7 +30393,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -30438,7 +30429,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -30474,7 +30465,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -30510,7 +30501,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -30546,7 +30537,7 @@
         </is>
       </c>
       <c r="G311" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H311" s="20" t="inlineStr"/>
     </row>
@@ -30582,7 +30573,7 @@
         </is>
       </c>
       <c r="G312" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H312" s="20" t="inlineStr"/>
     </row>
@@ -30618,7 +30609,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -30654,7 +30645,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -30726,7 +30717,7 @@
         </is>
       </c>
       <c r="G316" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H316" s="20" t="inlineStr"/>
     </row>
@@ -30762,7 +30753,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -30798,7 +30789,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -30834,7 +30825,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -30906,7 +30897,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -31050,7 +31041,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -31086,7 +31077,7 @@
         </is>
       </c>
       <c r="G326" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H326" s="20" t="inlineStr"/>
     </row>
@@ -31230,7 +31221,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -31266,7 +31257,7 @@
         </is>
       </c>
       <c r="G331" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H331" s="20" t="inlineStr"/>
     </row>
@@ -31338,7 +31329,7 @@
         </is>
       </c>
       <c r="G333" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H333" s="20" t="inlineStr"/>
     </row>
@@ -31446,7 +31437,7 @@
         </is>
       </c>
       <c r="G336" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H336" s="20" t="inlineStr"/>
     </row>
@@ -31482,7 +31473,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -31554,7 +31545,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -31590,7 +31581,7 @@
         </is>
       </c>
       <c r="G340" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="20" t="inlineStr"/>
     </row>
@@ -31626,7 +31617,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -31662,7 +31653,7 @@
         </is>
       </c>
       <c r="G342" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="20" t="inlineStr"/>
     </row>
@@ -31734,7 +31725,7 @@
         </is>
       </c>
       <c r="G344" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="20" t="inlineStr"/>
     </row>
@@ -31770,7 +31761,7 @@
         </is>
       </c>
       <c r="G345" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="20" t="inlineStr"/>
     </row>
@@ -31878,7 +31869,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -31914,7 +31905,7 @@
         </is>
       </c>
       <c r="G349" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H349" s="20" t="inlineStr"/>
     </row>
@@ -31950,7 +31941,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -31986,7 +31977,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -32058,7 +32049,7 @@
         </is>
       </c>
       <c r="G353" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="20" t="inlineStr"/>
     </row>
@@ -32094,7 +32085,7 @@
         </is>
       </c>
       <c r="G354" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="20" t="inlineStr"/>
     </row>
@@ -32130,7 +32121,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -32166,7 +32157,7 @@
         </is>
       </c>
       <c r="G356" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="20" t="inlineStr"/>
     </row>
@@ -32202,7 +32193,7 @@
         </is>
       </c>
       <c r="G357" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H357" s="20" t="inlineStr"/>
     </row>
@@ -32238,7 +32229,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -32274,7 +32265,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -32310,7 +32301,7 @@
         </is>
       </c>
       <c r="G360" s="18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H360" s="20" t="inlineStr"/>
     </row>
@@ -32346,7 +32337,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -32418,7 +32409,7 @@
         </is>
       </c>
       <c r="G363" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="20" t="inlineStr"/>
     </row>
@@ -32454,7 +32445,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -32490,7 +32481,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -32526,7 +32517,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -32562,7 +32553,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -32598,7 +32589,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -32634,7 +32625,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -32706,7 +32697,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -32742,7 +32733,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -32778,7 +32769,7 @@
         </is>
       </c>
       <c r="G373" s="18" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H373" s="20" t="inlineStr"/>
     </row>
@@ -32814,7 +32805,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -32850,7 +32841,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -32886,7 +32877,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -32922,7 +32913,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -32958,7 +32949,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -32994,7 +32985,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -33066,7 +33057,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -33102,7 +33093,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -33138,7 +33129,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -33174,7 +33165,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -33210,7 +33201,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -33246,7 +33237,7 @@
         </is>
       </c>
       <c r="G386" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H386" s="20" t="inlineStr"/>
     </row>
@@ -33282,7 +33273,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -33318,7 +33309,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -33354,7 +33345,7 @@
         </is>
       </c>
       <c r="G389" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="20" t="inlineStr"/>
     </row>
@@ -33462,7 +33453,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -33498,7 +33489,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -33606,7 +33597,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -33642,7 +33633,7 @@
         </is>
       </c>
       <c r="G397" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="20" t="inlineStr"/>
     </row>
@@ -33678,7 +33669,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -33714,7 +33705,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -33750,7 +33741,7 @@
         </is>
       </c>
       <c r="G400" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="20" t="inlineStr"/>
     </row>
@@ -33786,7 +33777,7 @@
         </is>
       </c>
       <c r="G401" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="20" t="inlineStr"/>
     </row>
@@ -33822,7 +33813,7 @@
         </is>
       </c>
       <c r="G402" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="20" t="inlineStr"/>
     </row>
@@ -33894,7 +33885,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -33930,7 +33921,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -33966,7 +33957,7 @@
         </is>
       </c>
       <c r="G406" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H406" s="20" t="inlineStr"/>
     </row>
@@ -34002,7 +33993,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -34074,7 +34065,7 @@
         </is>
       </c>
       <c r="G409" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="20" t="inlineStr"/>
     </row>
@@ -34110,7 +34101,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -34146,7 +34137,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -34182,7 +34173,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -34290,7 +34281,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -34326,7 +34317,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -34362,7 +34353,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -34398,7 +34389,7 @@
         </is>
       </c>
       <c r="G418" s="18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H418" s="20" t="inlineStr"/>
     </row>
@@ -34434,7 +34425,7 @@
         </is>
       </c>
       <c r="G419" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H419" s="20" t="inlineStr"/>
     </row>
@@ -34470,7 +34461,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -34506,7 +34497,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -34542,7 +34533,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -34578,7 +34569,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -34758,7 +34749,7 @@
         </is>
       </c>
       <c r="G428" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="20" t="inlineStr"/>
     </row>
@@ -34866,7 +34857,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -34902,7 +34893,7 @@
         </is>
       </c>
       <c r="G432" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="20" t="inlineStr"/>
     </row>
@@ -34974,7 +34965,7 @@
         </is>
       </c>
       <c r="G434" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="20" t="inlineStr"/>
     </row>
@@ -35010,7 +35001,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -35046,7 +35037,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -35082,7 +35073,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -35154,7 +35145,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -35334,7 +35325,7 @@
         </is>
       </c>
       <c r="G444" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="20" t="inlineStr"/>
     </row>
@@ -35370,7 +35361,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -35406,7 +35397,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -35442,7 +35433,7 @@
         </is>
       </c>
       <c r="G447" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="20" t="inlineStr"/>
     </row>
@@ -35478,7 +35469,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -35514,7 +35505,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -35586,7 +35577,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -35622,7 +35613,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -35658,7 +35649,7 @@
         </is>
       </c>
       <c r="G453" s="18" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H453" s="20" t="inlineStr"/>
     </row>
@@ -35694,7 +35685,7 @@
         </is>
       </c>
       <c r="G454" s="18" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H454" s="20" t="inlineStr"/>
     </row>
@@ -35730,7 +35721,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -35802,7 +35793,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -35838,7 +35829,7 @@
         </is>
       </c>
       <c r="G458" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H458" s="20" t="inlineStr"/>
     </row>
@@ -35874,7 +35865,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -35910,7 +35901,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -35946,7 +35937,7 @@
         </is>
       </c>
       <c r="G461" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H461" s="20" t="inlineStr"/>
     </row>
@@ -35982,7 +35973,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -36018,7 +36009,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -36054,7 +36045,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -36090,7 +36081,7 @@
         </is>
       </c>
       <c r="G465" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H465" s="20" t="inlineStr"/>
     </row>
@@ -36126,7 +36117,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -36198,7 +36189,7 @@
         </is>
       </c>
       <c r="G468" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H468" s="20" t="inlineStr"/>
     </row>
@@ -36234,7 +36225,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -36270,7 +36261,7 @@
         </is>
       </c>
       <c r="G470" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H470" s="20" t="inlineStr"/>
     </row>
@@ -36306,7 +36297,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -36342,7 +36333,7 @@
         </is>
       </c>
       <c r="G472" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="20" t="inlineStr"/>
     </row>
@@ -36378,7 +36369,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -36414,7 +36405,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -36450,7 +36441,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -36486,7 +36477,7 @@
         </is>
       </c>
       <c r="G476" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="20" t="inlineStr"/>
     </row>
@@ -36522,7 +36513,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -36594,14 +36585,14 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
     <row r="480" ht="16" customHeight="1">
       <c r="A480" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B480" s="18" t="inlineStr">
@@ -36621,7 +36612,7 @@
       </c>
       <c r="E480" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F480" s="18" t="inlineStr">
@@ -36630,14 +36621,14 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
     <row r="481" ht="16" customHeight="1">
       <c r="A481" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B481" s="18" t="inlineStr">
@@ -36657,7 +36648,7 @@
       </c>
       <c r="E481" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F481" s="18" t="inlineStr">
@@ -36666,14 +36657,14 @@
         </is>
       </c>
       <c r="G481" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="20" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B482" s="18" t="inlineStr">
@@ -36693,7 +36684,7 @@
       </c>
       <c r="E482" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F482" s="18" t="inlineStr">
@@ -36702,14 +36693,14 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B483" s="18" t="inlineStr">
@@ -36729,7 +36720,7 @@
       </c>
       <c r="E483" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F483" s="18" t="inlineStr">
@@ -36738,14 +36729,14 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B484" s="18" t="inlineStr">
@@ -36765,7 +36756,7 @@
       </c>
       <c r="E484" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F484" s="18" t="inlineStr">
@@ -36774,14 +36765,14 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B485" s="18" t="inlineStr">
@@ -36801,7 +36792,7 @@
       </c>
       <c r="E485" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F485" s="18" t="inlineStr">
@@ -36810,14 +36801,14 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B486" s="18" t="inlineStr">
@@ -36837,7 +36828,7 @@
       </c>
       <c r="E486" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F486" s="18" t="inlineStr">
@@ -36846,14 +36837,14 @@
         </is>
       </c>
       <c r="G486" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="20" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B487" s="18" t="inlineStr">
@@ -36873,7 +36864,7 @@
       </c>
       <c r="E487" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F487" s="18" t="inlineStr">
@@ -36889,7 +36880,7 @@
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B488" s="18" t="inlineStr">
@@ -36909,7 +36900,7 @@
       </c>
       <c r="E488" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F488" s="18" t="inlineStr">
@@ -36918,14 +36909,14 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="18" t="inlineStr">
         <is>
-          <t>TC_PERF_040</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B489" s="18" t="inlineStr">
@@ -36945,7 +36936,7 @@
       </c>
       <c r="E489" s="19" t="inlineStr">
         <is>
-          <t>Performance smoke test #40</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F489" s="18" t="inlineStr">
@@ -36958,8 +36949,44 @@
       </c>
       <c r="H489" s="20" t="inlineStr"/>
     </row>
+    <row r="490" ht="16" customHeight="1">
+      <c r="A490" s="18" t="inlineStr">
+        <is>
+          <t>TC_PERF_040</t>
+        </is>
+      </c>
+      <c r="B490" s="18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C490" s="18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D490" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E490" s="19" t="inlineStr">
+        <is>
+          <t>Performance smoke test #40</t>
+        </is>
+      </c>
+      <c r="F490" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G490" s="18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H490" s="20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H489"/>
+  <autoFilter ref="A1:H490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36970,7 +36997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37057,7 +37084,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
@@ -37097,7 +37124,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
@@ -37137,7 +37164,7 @@
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="H4" s="23" t="inlineStr"/>
     </row>
@@ -37173,19 +37200,19 @@
         </is>
       </c>
       <c r="G5" s="21" t="n">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37221,19 +37248,19 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>22.05</v>
+        <v>21.95</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37269,19 +37296,19 @@
         </is>
       </c>
       <c r="G7" s="21" t="n">
-        <v>22.07</v>
+        <v>22.01</v>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37317,19 +37344,19 @@
         </is>
       </c>
       <c r="G8" s="21" t="n">
-        <v>22.15</v>
+        <v>22.07</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37365,19 +37392,19 @@
         </is>
       </c>
       <c r="G9" s="21" t="n">
-        <v>22.18</v>
+        <v>22.09</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37413,19 +37440,19 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>22.12</v>
+        <v>22.07</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37461,19 +37488,19 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>22.15</v>
+        <v>22.1</v>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
@@ -37509,69 +37536,24 @@
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>22.45</v>
+        <v>22.34</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f3464dbf32 &lt;unknown&gt;
-#3 0x55f3464dc181 &lt;unknown&gt;
-#4 0x55f346527374 &lt;unknown&gt;
-#5 0x55f34652455d &lt;unknown&gt;
-#6 0x55f34</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>TC_PERF_030</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Performance smoke test #30</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>30.19</v>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.004
-  (Session info: chrome=150.0.7871.128)
-Stacktrace:
-#0 0x55f346aae44a &lt;unknown&gt;
-#1 0x55f3464868c9 &lt;unknown&gt;
-#2 0x55f34646e35a &lt;unkno</t>
+#0 0x56221503644a &lt;unknown&gt;
+#1 0x562214a0e8c9 &lt;unknown&gt;
+#2 0x562214a63f32 &lt;unknown&gt;
+#3 0x562214a64181 &lt;unknown&gt;
+#4 0x562214aaf374 &lt;unknown&gt;
+#5 0x562214aac55d &lt;unknown&gt;
+#6 0x56221</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37776,14 +37758,14 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -37941,7 +37923,7 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
@@ -37962,7 +37944,7 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="29" t="inlineStr">
         <is>
@@ -37983,7 +37965,7 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>1.67s</t>
+          <t>1.6s</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -704,7 +704,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-27T06:39:40    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-28T05:57:11    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.88s</t>
+          <t>0.86s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.17s</t>
+          <t>2.19s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.84</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="G15" s="21" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
     </row>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H39" s="20" t="inlineStr"/>
     </row>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H43" s="20" t="inlineStr"/>
     </row>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="20" t="inlineStr"/>
     </row>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="G45" s="21" t="n">
-        <v>10.27</v>
+        <v>10.34</v>
       </c>
       <c r="H45" s="23" t="inlineStr"/>
     </row>
@@ -2870,19 +2870,19 @@
         </is>
       </c>
       <c r="G47" s="21" t="n">
-        <v>21.31</v>
+        <v>21.29</v>
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="G48" s="21" t="n">
-        <v>21.95</v>
+        <v>22.05</v>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="G49" s="21" t="n">
-        <v>22.01</v>
+        <v>21.96</v>
       </c>
       <c r="H49" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3014,19 +3014,19 @@
         </is>
       </c>
       <c r="G50" s="21" t="n">
-        <v>22.07</v>
+        <v>22.05</v>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3062,19 +3062,19 @@
         </is>
       </c>
       <c r="G51" s="21" t="n">
-        <v>22.09</v>
+        <v>22.1</v>
       </c>
       <c r="H51" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>21.13</v>
+        <v>21.15</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>21.12</v>
+        <v>21.1</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="G56" s="21" t="n">
-        <v>22.07</v>
+        <v>22.05</v>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
         </is>
       </c>
       <c r="G57" s="21" t="n">
-        <v>22.1</v>
+        <v>22.05</v>
       </c>
       <c r="H57" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3350,19 +3350,19 @@
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="G61" s="18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="H61" s="20" t="inlineStr"/>
     </row>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="20" t="inlineStr"/>
     </row>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H92" s="20" t="inlineStr"/>
     </row>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H104" s="20" t="inlineStr"/>
     </row>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="G111" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H111" s="20" t="inlineStr"/>
     </row>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="G136" s="18" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H136" s="20" t="inlineStr"/>
     </row>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="G137" s="18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="20" t="inlineStr"/>
     </row>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G138" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="20" t="inlineStr"/>
     </row>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="G139" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H139" s="20" t="inlineStr"/>
     </row>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="G142" s="18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H142" s="20" t="inlineStr"/>
     </row>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="G143" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="20" t="inlineStr"/>
     </row>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="G144" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="20" t="inlineStr"/>
     </row>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="G147" s="18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="20" t="inlineStr"/>
     </row>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="20" t="inlineStr"/>
     </row>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="G157" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="20" t="inlineStr"/>
     </row>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="G161" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="20" t="inlineStr"/>
     </row>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="G162" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="20" t="inlineStr"/>
     </row>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="G163" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="20" t="inlineStr"/>
     </row>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="G165" s="18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="20" t="inlineStr"/>
     </row>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="G166" s="18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H166" s="20" t="inlineStr"/>
     </row>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="G168" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="20" t="inlineStr"/>
     </row>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G170" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="20" t="inlineStr"/>
     </row>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="G176" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="20" t="inlineStr"/>
     </row>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="G178" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="20" t="inlineStr"/>
     </row>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="G180" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="20" t="inlineStr"/>
     </row>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="G182" s="18" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="H182" s="20" t="inlineStr"/>
     </row>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="G184" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H184" s="20" t="inlineStr"/>
     </row>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="G186" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="20" t="inlineStr"/>
     </row>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>12.1</v>
+        <v>12.07</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="G190" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="20" t="inlineStr"/>
     </row>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G194" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H194" s="20" t="inlineStr"/>
     </row>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="G196" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="20" t="inlineStr"/>
     </row>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="G208" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="20" t="inlineStr"/>
     </row>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="G210" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="20" t="inlineStr"/>
     </row>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="G211" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="20" t="inlineStr"/>
     </row>
@@ -8978,7 +8978,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="G217" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="20" t="inlineStr"/>
     </row>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="G218" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="20" t="inlineStr"/>
     </row>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="G225" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="20" t="inlineStr"/>
     </row>
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="G230" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H230" s="20" t="inlineStr"/>
     </row>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G235" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H235" s="20" t="inlineStr"/>
     </row>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="G240" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="20" t="inlineStr"/>
     </row>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="G242" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="20" t="inlineStr"/>
     </row>
@@ -10166,7 +10166,7 @@
         </is>
       </c>
       <c r="G247" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="20" t="inlineStr"/>
     </row>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="G250" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="20" t="inlineStr"/>
     </row>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="G252" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="20" t="inlineStr"/>
     </row>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="G254" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="20" t="inlineStr"/>
     </row>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="G263" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="20" t="inlineStr"/>
     </row>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="G265" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="20" t="inlineStr"/>
     </row>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -10922,7 +10922,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="G270" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="20" t="inlineStr"/>
     </row>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="G271" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H271" s="20" t="inlineStr"/>
     </row>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G276" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="20" t="inlineStr"/>
     </row>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="G277" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="20" t="inlineStr"/>
     </row>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="G278" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="20" t="inlineStr"/>
     </row>
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="G281" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="20" t="inlineStr"/>
     </row>
@@ -11426,7 +11426,7 @@
         </is>
       </c>
       <c r="G282" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="20" t="inlineStr"/>
     </row>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G287" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="20" t="inlineStr"/>
     </row>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="G290" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="20" t="inlineStr"/>
     </row>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="G292" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="20" t="inlineStr"/>
     </row>
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="G293" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="20" t="inlineStr"/>
     </row>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="G294" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="20" t="inlineStr"/>
     </row>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="G296" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="20" t="inlineStr"/>
     </row>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="G298" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H298" s="20" t="inlineStr"/>
     </row>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -12074,7 +12074,7 @@
         </is>
       </c>
       <c r="G300" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="20" t="inlineStr"/>
     </row>
@@ -12146,7 +12146,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G315" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="20" t="inlineStr"/>
     </row>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="G319" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="20" t="inlineStr"/>
     </row>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="G322" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="20" t="inlineStr"/>
     </row>
@@ -12902,7 +12902,7 @@
         </is>
       </c>
       <c r="G323" s="18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H323" s="20" t="inlineStr"/>
     </row>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="G324" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H324" s="20" t="inlineStr"/>
     </row>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="G326" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="20" t="inlineStr"/>
     </row>
@@ -13046,7 +13046,7 @@
         </is>
       </c>
       <c r="G327" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="20" t="inlineStr"/>
     </row>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="G329" s="18" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="H329" s="20" t="inlineStr"/>
     </row>
@@ -13190,7 +13190,7 @@
         </is>
       </c>
       <c r="G331" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="20" t="inlineStr"/>
     </row>
@@ -13226,7 +13226,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="G333" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="20" t="inlineStr"/>
     </row>
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="G334" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="20" t="inlineStr"/>
     </row>
@@ -13370,7 +13370,7 @@
         </is>
       </c>
       <c r="G336" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="20" t="inlineStr"/>
     </row>
@@ -13442,7 +13442,7 @@
         </is>
       </c>
       <c r="G338" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="20" t="inlineStr"/>
     </row>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="G339" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="20" t="inlineStr"/>
     </row>
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="G340" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="20" t="inlineStr"/>
     </row>
@@ -13550,7 +13550,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="G343" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="20" t="inlineStr"/>
     </row>
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="G344" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="20" t="inlineStr"/>
     </row>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="G345" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="20" t="inlineStr"/>
     </row>
@@ -13730,7 +13730,7 @@
         </is>
       </c>
       <c r="G346" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="20" t="inlineStr"/>
     </row>
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="G347" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="20" t="inlineStr"/>
     </row>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="G349" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="20" t="inlineStr"/>
     </row>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="G352" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="20" t="inlineStr"/>
     </row>
@@ -13982,7 +13982,7 @@
         </is>
       </c>
       <c r="G353" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="20" t="inlineStr"/>
     </row>
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G354" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="20" t="inlineStr"/>
     </row>
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G356" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="20" t="inlineStr"/>
     </row>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="G357" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="20" t="inlineStr"/>
     </row>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -14198,7 +14198,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="G360" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="20" t="inlineStr"/>
     </row>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="G362" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="20" t="inlineStr"/>
     </row>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -14486,7 +14486,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="G369" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="20" t="inlineStr"/>
     </row>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -14666,7 +14666,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -14738,7 +14738,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -14918,7 +14918,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -15062,7 +15062,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -15134,7 +15134,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="G386" s="18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H386" s="20" t="inlineStr"/>
     </row>
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -15242,7 +15242,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="G389" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="20" t="inlineStr"/>
     </row>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="G390" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="20" t="inlineStr"/>
     </row>
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="G391" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="20" t="inlineStr"/>
     </row>
@@ -15386,7 +15386,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G395" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="20" t="inlineStr"/>
     </row>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="G398" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="20" t="inlineStr"/>
     </row>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="G401" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="20" t="inlineStr"/>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -15854,7 +15854,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="G408" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="20" t="inlineStr"/>
     </row>
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="G410" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="20" t="inlineStr"/>
     </row>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -16142,7 +16142,7 @@
         </is>
       </c>
       <c r="G413" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="20" t="inlineStr"/>
     </row>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="G414" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="20" t="inlineStr"/>
     </row>
@@ -16214,7 +16214,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="G417" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="20" t="inlineStr"/>
     </row>
@@ -16322,7 +16322,7 @@
         </is>
       </c>
       <c r="G418" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="20" t="inlineStr"/>
     </row>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -16610,7 +16610,7 @@
         </is>
       </c>
       <c r="G426" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="20" t="inlineStr"/>
     </row>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="G430" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="20" t="inlineStr"/>
     </row>
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -16826,7 +16826,7 @@
         </is>
       </c>
       <c r="G432" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="20" t="inlineStr"/>
     </row>
@@ -16862,7 +16862,7 @@
         </is>
       </c>
       <c r="G433" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="20" t="inlineStr"/>
     </row>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="G434" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="20" t="inlineStr"/>
     </row>
@@ -16934,7 +16934,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G438" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="20" t="inlineStr"/>
     </row>
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -17114,7 +17114,7 @@
         </is>
       </c>
       <c r="G440" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="20" t="inlineStr"/>
     </row>
@@ -17150,7 +17150,7 @@
         </is>
       </c>
       <c r="G441" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="20" t="inlineStr"/>
     </row>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="G442" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="20" t="inlineStr"/>
     </row>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="G443" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="20" t="inlineStr"/>
     </row>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="G444" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="20" t="inlineStr"/>
     </row>
@@ -17294,7 +17294,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="G447" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="20" t="inlineStr"/>
     </row>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -17510,7 +17510,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -17546,7 +17546,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -17582,7 +17582,7 @@
         </is>
       </c>
       <c r="G453" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H453" s="20" t="inlineStr"/>
     </row>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -17690,7 +17690,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="G457" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="20" t="inlineStr"/>
     </row>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="G459" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="20" t="inlineStr"/>
     </row>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="G460" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="20" t="inlineStr"/>
     </row>
@@ -17870,7 +17870,7 @@
         </is>
       </c>
       <c r="G461" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="20" t="inlineStr"/>
     </row>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="G465" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H465" s="20" t="inlineStr"/>
     </row>
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -18086,7 +18086,7 @@
         </is>
       </c>
       <c r="G467" s="18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="H467" s="20" t="inlineStr"/>
     </row>
@@ -18302,7 +18302,7 @@
         </is>
       </c>
       <c r="G473" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="20" t="inlineStr"/>
     </row>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -18374,7 +18374,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -18554,7 +18554,7 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="G481" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="20" t="inlineStr"/>
     </row>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
@@ -18770,7 +18770,7 @@
         </is>
       </c>
       <c r="G486" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="20" t="inlineStr"/>
     </row>
@@ -18842,7 +18842,7 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
@@ -18914,7 +18914,7 @@
         </is>
       </c>
       <c r="G490" s="18" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H490" s="20" t="inlineStr"/>
     </row>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="G491" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="20" t="inlineStr"/>
     </row>
@@ -19022,7 +19022,7 @@
         </is>
       </c>
       <c r="G493" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="20" t="inlineStr"/>
     </row>
@@ -19058,7 +19058,7 @@
         </is>
       </c>
       <c r="G494" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="20" t="inlineStr"/>
     </row>
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="G495" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="20" t="inlineStr"/>
     </row>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="G496" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="20" t="inlineStr"/>
     </row>
@@ -19202,7 +19202,7 @@
         </is>
       </c>
       <c r="G498" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H498" s="20" t="inlineStr"/>
     </row>
@@ -19238,7 +19238,7 @@
         </is>
       </c>
       <c r="G499" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H499" s="20" t="inlineStr"/>
     </row>
@@ -19274,7 +19274,7 @@
         </is>
       </c>
       <c r="G500" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H500" s="20" t="inlineStr"/>
     </row>
@@ -19413,7 +19413,7 @@
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0.84</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="20" t="inlineStr"/>
     </row>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H3" s="20" t="inlineStr"/>
     </row>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="H4" s="20" t="inlineStr"/>
     </row>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="H5" s="20" t="inlineStr"/>
     </row>
@@ -19557,7 +19557,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="20" t="inlineStr"/>
     </row>
@@ -19593,7 +19593,7 @@
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
     </row>
@@ -19629,7 +19629,7 @@
         </is>
       </c>
       <c r="G8" s="18" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="H9" s="20" t="inlineStr"/>
     </row>
@@ -19701,7 +19701,7 @@
         </is>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
     </row>
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
     </row>
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
@@ -19809,7 +19809,7 @@
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
     </row>
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
     </row>
@@ -19917,7 +19917,7 @@
         </is>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
     </row>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
     </row>
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
     </row>
@@ -20025,7 +20025,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
     </row>
@@ -20061,7 +20061,7 @@
         </is>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
     </row>
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
     </row>
@@ -20133,7 +20133,7 @@
         </is>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
     </row>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
     </row>
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
     </row>
@@ -20241,7 +20241,7 @@
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
     </row>
@@ -20313,7 +20313,7 @@
         </is>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
     </row>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
     </row>
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
     </row>
@@ -20421,7 +20421,7 @@
         </is>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
     </row>
@@ -20457,7 +20457,7 @@
         </is>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
     </row>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
     </row>
@@ -20529,7 +20529,7 @@
         </is>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
     </row>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
     </row>
@@ -20601,7 +20601,7 @@
         </is>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
     </row>
@@ -20637,7 +20637,7 @@
         </is>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
     </row>
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
     </row>
@@ -20709,7 +20709,7 @@
         </is>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H38" s="20" t="inlineStr"/>
     </row>
@@ -20781,7 +20781,7 @@
         </is>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="20" t="inlineStr"/>
     </row>
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H41" s="20" t="inlineStr"/>
     </row>
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="20" t="inlineStr"/>
     </row>
@@ -20925,7 +20925,7 @@
         </is>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="20" t="inlineStr"/>
     </row>
@@ -20961,7 +20961,7 @@
         </is>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H45" s="20" t="inlineStr"/>
     </row>
@@ -20997,7 +20997,7 @@
         </is>
       </c>
       <c r="G46" s="18" t="n">
-        <v>21.13</v>
+        <v>21.15</v>
       </c>
       <c r="H46" s="20" t="inlineStr"/>
     </row>
@@ -21033,7 +21033,7 @@
         </is>
       </c>
       <c r="G47" s="18" t="n">
-        <v>21.12</v>
+        <v>21.1</v>
       </c>
       <c r="H47" s="20" t="inlineStr"/>
     </row>
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="20" t="inlineStr"/>
     </row>
@@ -21141,7 +21141,7 @@
         </is>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="H50" s="20" t="inlineStr"/>
     </row>
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H51" s="20" t="inlineStr"/>
     </row>
@@ -21213,7 +21213,7 @@
         </is>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H52" s="20" t="inlineStr"/>
     </row>
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H53" s="20" t="inlineStr"/>
     </row>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H54" s="20" t="inlineStr"/>
     </row>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H55" s="20" t="inlineStr"/>
     </row>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H56" s="20" t="inlineStr"/>
     </row>
@@ -21393,7 +21393,7 @@
         </is>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H57" s="20" t="inlineStr"/>
     </row>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H58" s="20" t="inlineStr"/>
     </row>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H59" s="20" t="inlineStr"/>
     </row>
@@ -21501,7 +21501,7 @@
         </is>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H60" s="20" t="inlineStr"/>
     </row>
@@ -21573,7 +21573,7 @@
         </is>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="20" t="inlineStr"/>
     </row>
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H63" s="20" t="inlineStr"/>
     </row>
@@ -21645,7 +21645,7 @@
         </is>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H64" s="20" t="inlineStr"/>
     </row>
@@ -21681,7 +21681,7 @@
         </is>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H65" s="20" t="inlineStr"/>
     </row>
@@ -21717,7 +21717,7 @@
         </is>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="20" t="inlineStr"/>
     </row>
@@ -21753,7 +21753,7 @@
         </is>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H67" s="20" t="inlineStr"/>
     </row>
@@ -21789,7 +21789,7 @@
         </is>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H68" s="20" t="inlineStr"/>
     </row>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H69" s="20" t="inlineStr"/>
     </row>
@@ -21861,7 +21861,7 @@
         </is>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H70" s="20" t="inlineStr"/>
     </row>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="20" t="inlineStr"/>
     </row>
@@ -21933,7 +21933,7 @@
         </is>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H72" s="20" t="inlineStr"/>
     </row>
@@ -21969,7 +21969,7 @@
         </is>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
     </row>
@@ -22005,7 +22005,7 @@
         </is>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
     </row>
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H75" s="20" t="inlineStr"/>
     </row>
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H76" s="20" t="inlineStr"/>
     </row>
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="20" t="inlineStr"/>
     </row>
@@ -22185,7 +22185,7 @@
         </is>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="20" t="inlineStr"/>
     </row>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H80" s="20" t="inlineStr"/>
     </row>
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="20" t="inlineStr"/>
     </row>
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="20" t="inlineStr"/>
     </row>
@@ -22329,7 +22329,7 @@
         </is>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="20" t="inlineStr"/>
     </row>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H84" s="20" t="inlineStr"/>
     </row>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H85" s="20" t="inlineStr"/>
     </row>
@@ -22437,7 +22437,7 @@
         </is>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H86" s="20" t="inlineStr"/>
     </row>
@@ -22473,7 +22473,7 @@
         </is>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="20" t="inlineStr"/>
     </row>
@@ -22509,7 +22509,7 @@
         </is>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H88" s="20" t="inlineStr"/>
     </row>
@@ -22545,7 +22545,7 @@
         </is>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="20" t="inlineStr"/>
     </row>
@@ -22581,7 +22581,7 @@
         </is>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="20" t="inlineStr"/>
     </row>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="H91" s="20" t="inlineStr"/>
     </row>
@@ -22689,7 +22689,7 @@
         </is>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H93" s="20" t="inlineStr"/>
     </row>
@@ -22725,7 +22725,7 @@
         </is>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H94" s="20" t="inlineStr"/>
     </row>
@@ -22761,7 +22761,7 @@
         </is>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="20" t="inlineStr"/>
     </row>
@@ -22797,7 +22797,7 @@
         </is>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H96" s="20" t="inlineStr"/>
     </row>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H97" s="20" t="inlineStr"/>
     </row>
@@ -22869,7 +22869,7 @@
         </is>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="20" t="inlineStr"/>
     </row>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="20" t="inlineStr"/>
     </row>
@@ -22941,7 +22941,7 @@
         </is>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H100" s="20" t="inlineStr"/>
     </row>
@@ -22977,7 +22977,7 @@
         </is>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H101" s="20" t="inlineStr"/>
     </row>
@@ -23013,7 +23013,7 @@
         </is>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H102" s="20" t="inlineStr"/>
     </row>
@@ -23049,7 +23049,7 @@
         </is>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H103" s="20" t="inlineStr"/>
     </row>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="G104" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="20" t="inlineStr"/>
     </row>
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="20" t="inlineStr"/>
     </row>
@@ -23157,7 +23157,7 @@
         </is>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H106" s="20" t="inlineStr"/>
     </row>
@@ -23193,7 +23193,7 @@
         </is>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="20" t="inlineStr"/>
     </row>
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="G108" s="18" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H108" s="20" t="inlineStr"/>
     </row>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="G109" s="18" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="20" t="inlineStr"/>
     </row>
@@ -23301,7 +23301,7 @@
         </is>
       </c>
       <c r="G110" s="18" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="20" t="inlineStr"/>
     </row>
@@ -23373,7 +23373,7 @@
         </is>
       </c>
       <c r="G112" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H112" s="20" t="inlineStr"/>
     </row>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="G113" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H113" s="20" t="inlineStr"/>
     </row>
@@ -23445,7 +23445,7 @@
         </is>
       </c>
       <c r="G114" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H114" s="20" t="inlineStr"/>
     </row>
@@ -23481,7 +23481,7 @@
         </is>
       </c>
       <c r="G115" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H115" s="20" t="inlineStr"/>
     </row>
@@ -23517,7 +23517,7 @@
         </is>
       </c>
       <c r="G116" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H116" s="20" t="inlineStr"/>
     </row>
@@ -23553,7 +23553,7 @@
         </is>
       </c>
       <c r="G117" s="18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H117" s="20" t="inlineStr"/>
     </row>
@@ -23589,7 +23589,7 @@
         </is>
       </c>
       <c r="G118" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
     </row>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="G119" s="18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
     </row>
@@ -23661,7 +23661,7 @@
         </is>
       </c>
       <c r="G120" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H120" s="20" t="inlineStr"/>
     </row>
@@ -23697,7 +23697,7 @@
         </is>
       </c>
       <c r="G121" s="18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H121" s="20" t="inlineStr"/>
     </row>
@@ -23733,7 +23733,7 @@
         </is>
       </c>
       <c r="G122" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H122" s="20" t="inlineStr"/>
     </row>
@@ -23769,7 +23769,7 @@
         </is>
       </c>
       <c r="G123" s="18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H123" s="20" t="inlineStr"/>
     </row>
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="G124" s="18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H124" s="20" t="inlineStr"/>
     </row>
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="G125" s="18" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H125" s="20" t="inlineStr"/>
     </row>
@@ -23877,7 +23877,7 @@
         </is>
       </c>
       <c r="G126" s="18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H126" s="20" t="inlineStr"/>
     </row>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="G127" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H127" s="20" t="inlineStr"/>
     </row>
@@ -23949,7 +23949,7 @@
         </is>
       </c>
       <c r="G128" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H128" s="20" t="inlineStr"/>
     </row>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="G129" s="18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="20" t="inlineStr"/>
     </row>
@@ -24021,7 +24021,7 @@
         </is>
       </c>
       <c r="G130" s="18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="20" t="inlineStr"/>
     </row>
@@ -24057,7 +24057,7 @@
         </is>
       </c>
       <c r="G131" s="18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H131" s="20" t="inlineStr"/>
     </row>
@@ -24093,7 +24093,7 @@
         </is>
       </c>
       <c r="G132" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H132" s="20" t="inlineStr"/>
     </row>
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="G133" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H133" s="20" t="inlineStr"/>
     </row>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="G134" s="18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H134" s="20" t="inlineStr"/>
     </row>
@@ -24201,7 +24201,7 @@
         </is>
       </c>
       <c r="G135" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H135" s="20" t="inlineStr"/>
     </row>
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="G136" s="18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H136" s="20" t="inlineStr"/>
     </row>
@@ -24381,7 +24381,7 @@
         </is>
       </c>
       <c r="G140" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H140" s="20" t="inlineStr"/>
     </row>
@@ -24417,7 +24417,7 @@
         </is>
       </c>
       <c r="G141" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H141" s="20" t="inlineStr"/>
     </row>
@@ -24561,7 +24561,7 @@
         </is>
       </c>
       <c r="G145" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H145" s="20" t="inlineStr"/>
     </row>
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="G146" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="20" t="inlineStr"/>
     </row>
@@ -24669,7 +24669,7 @@
         </is>
       </c>
       <c r="G148" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="20" t="inlineStr"/>
     </row>
@@ -24705,7 +24705,7 @@
         </is>
       </c>
       <c r="G149" s="18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H149" s="20" t="inlineStr"/>
     </row>
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="G150" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="20" t="inlineStr"/>
     </row>
@@ -24777,7 +24777,7 @@
         </is>
       </c>
       <c r="G151" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="20" t="inlineStr"/>
     </row>
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="20" t="inlineStr"/>
     </row>
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="G154" s="18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="20" t="inlineStr"/>
     </row>
@@ -24921,7 +24921,7 @@
         </is>
       </c>
       <c r="G155" s="18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H155" s="20" t="inlineStr"/>
     </row>
@@ -24957,7 +24957,7 @@
         </is>
       </c>
       <c r="G156" s="18" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="20" t="inlineStr"/>
     </row>
@@ -24993,7 +24993,7 @@
         </is>
       </c>
       <c r="G157" s="18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="20" t="inlineStr"/>
     </row>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="G159" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="20" t="inlineStr"/>
     </row>
@@ -25101,7 +25101,7 @@
         </is>
       </c>
       <c r="G160" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="20" t="inlineStr"/>
     </row>
@@ -25281,7 +25281,7 @@
         </is>
       </c>
       <c r="G165" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="20" t="inlineStr"/>
     </row>
@@ -25353,7 +25353,7 @@
         </is>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="20" t="inlineStr"/>
     </row>
@@ -25425,7 +25425,7 @@
         </is>
       </c>
       <c r="G169" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="20" t="inlineStr"/>
     </row>
@@ -25497,7 +25497,7 @@
         </is>
       </c>
       <c r="G171" s="18" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="H171" s="20" t="inlineStr"/>
     </row>
@@ -25533,7 +25533,7 @@
         </is>
       </c>
       <c r="G172" s="18" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="H172" s="20" t="inlineStr"/>
     </row>
@@ -25569,7 +25569,7 @@
         </is>
       </c>
       <c r="G173" s="18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H173" s="20" t="inlineStr"/>
     </row>
@@ -25605,7 +25605,7 @@
         </is>
       </c>
       <c r="G174" s="18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="H174" s="20" t="inlineStr"/>
     </row>
@@ -25641,7 +25641,7 @@
         </is>
       </c>
       <c r="G175" s="18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H175" s="20" t="inlineStr"/>
     </row>
@@ -25713,7 +25713,7 @@
         </is>
       </c>
       <c r="G177" s="18" t="n">
-        <v>12.1</v>
+        <v>12.07</v>
       </c>
       <c r="H177" s="20" t="inlineStr"/>
     </row>
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="G179" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H179" s="20" t="inlineStr"/>
     </row>
@@ -25929,7 +25929,7 @@
         </is>
       </c>
       <c r="G183" s="18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H183" s="20" t="inlineStr"/>
     </row>
@@ -26001,7 +26001,7 @@
         </is>
       </c>
       <c r="G185" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H185" s="20" t="inlineStr"/>
     </row>
@@ -26109,7 +26109,7 @@
         </is>
       </c>
       <c r="G188" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H188" s="20" t="inlineStr"/>
     </row>
@@ -26253,7 +26253,7 @@
         </is>
       </c>
       <c r="G192" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H192" s="20" t="inlineStr"/>
     </row>
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="G197" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="20" t="inlineStr"/>
     </row>
@@ -26505,7 +26505,7 @@
         </is>
       </c>
       <c r="G199" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="20" t="inlineStr"/>
     </row>
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="G200" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="20" t="inlineStr"/>
     </row>
@@ -26649,7 +26649,7 @@
         </is>
       </c>
       <c r="G203" s="18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H203" s="20" t="inlineStr"/>
     </row>
@@ -26757,7 +26757,7 @@
         </is>
       </c>
       <c r="G206" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="20" t="inlineStr"/>
     </row>
@@ -26793,7 +26793,7 @@
         </is>
       </c>
       <c r="G207" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="20" t="inlineStr"/>
     </row>
@@ -27045,7 +27045,7 @@
         </is>
       </c>
       <c r="G214" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="20" t="inlineStr"/>
     </row>
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="G219" s="18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H219" s="20" t="inlineStr"/>
     </row>
@@ -27405,7 +27405,7 @@
         </is>
       </c>
       <c r="G224" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="20" t="inlineStr"/>
     </row>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="G229" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="20" t="inlineStr"/>
     </row>
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="G231" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="20" t="inlineStr"/>
     </row>
@@ -27837,7 +27837,7 @@
         </is>
       </c>
       <c r="G236" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="20" t="inlineStr"/>
     </row>
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="G239" s="18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="20" t="inlineStr"/>
     </row>
@@ -28017,7 +28017,7 @@
         </is>
       </c>
       <c r="G241" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="20" t="inlineStr"/>
     </row>
@@ -28053,7 +28053,7 @@
         </is>
       </c>
       <c r="G242" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="20" t="inlineStr"/>
     </row>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="G243" s="18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="20" t="inlineStr"/>
     </row>
@@ -28413,7 +28413,7 @@
         </is>
       </c>
       <c r="G252" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H252" s="20" t="inlineStr"/>
     </row>
@@ -28449,7 +28449,7 @@
         </is>
       </c>
       <c r="G253" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H253" s="20" t="inlineStr"/>
     </row>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="G254" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H254" s="20" t="inlineStr"/>
     </row>
@@ -28521,7 +28521,7 @@
         </is>
       </c>
       <c r="G255" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H255" s="20" t="inlineStr"/>
     </row>
@@ -28557,7 +28557,7 @@
         </is>
       </c>
       <c r="G256" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H256" s="20" t="inlineStr"/>
     </row>
@@ -28593,7 +28593,7 @@
         </is>
       </c>
       <c r="G257" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H257" s="20" t="inlineStr"/>
     </row>
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="G258" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H258" s="20" t="inlineStr"/>
     </row>
@@ -28665,7 +28665,7 @@
         </is>
       </c>
       <c r="G259" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H259" s="20" t="inlineStr"/>
     </row>
@@ -28701,7 +28701,7 @@
         </is>
       </c>
       <c r="G260" s="18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H260" s="20" t="inlineStr"/>
     </row>
@@ -28737,7 +28737,7 @@
         </is>
       </c>
       <c r="G261" s="18" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H261" s="20" t="inlineStr"/>
     </row>
@@ -28773,7 +28773,7 @@
         </is>
       </c>
       <c r="G262" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="20" t="inlineStr"/>
     </row>
@@ -28845,7 +28845,7 @@
         </is>
       </c>
       <c r="G264" s="18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="20" t="inlineStr"/>
     </row>
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="G265" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="20" t="inlineStr"/>
     </row>
@@ -28917,7 +28917,7 @@
         </is>
       </c>
       <c r="G266" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H266" s="20" t="inlineStr"/>
     </row>
@@ -28953,7 +28953,7 @@
         </is>
       </c>
       <c r="G267" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H267" s="20" t="inlineStr"/>
     </row>
@@ -28989,7 +28989,7 @@
         </is>
       </c>
       <c r="G268" s="18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H268" s="20" t="inlineStr"/>
     </row>
@@ -29025,7 +29025,7 @@
         </is>
       </c>
       <c r="G269" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H269" s="20" t="inlineStr"/>
     </row>
@@ -29061,7 +29061,7 @@
         </is>
       </c>
       <c r="G270" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H270" s="20" t="inlineStr"/>
     </row>
@@ -29097,7 +29097,7 @@
         </is>
       </c>
       <c r="G271" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H271" s="20" t="inlineStr"/>
     </row>
@@ -29133,7 +29133,7 @@
         </is>
       </c>
       <c r="G272" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H272" s="20" t="inlineStr"/>
     </row>
@@ -29169,7 +29169,7 @@
         </is>
       </c>
       <c r="G273" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H273" s="20" t="inlineStr"/>
     </row>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="G275" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H275" s="20" t="inlineStr"/>
     </row>
@@ -29277,7 +29277,7 @@
         </is>
       </c>
       <c r="G276" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H276" s="20" t="inlineStr"/>
     </row>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="G279" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H279" s="20" t="inlineStr"/>
     </row>
@@ -29421,7 +29421,7 @@
         </is>
       </c>
       <c r="G280" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="20" t="inlineStr"/>
     </row>
@@ -29457,7 +29457,7 @@
         </is>
       </c>
       <c r="G281" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="20" t="inlineStr"/>
     </row>
@@ -29493,7 +29493,7 @@
         </is>
       </c>
       <c r="G282" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="20" t="inlineStr"/>
     </row>
@@ -29529,7 +29529,7 @@
         </is>
       </c>
       <c r="G283" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="20" t="inlineStr"/>
     </row>
@@ -29565,7 +29565,7 @@
         </is>
       </c>
       <c r="G284" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="20" t="inlineStr"/>
     </row>
@@ -29601,7 +29601,7 @@
         </is>
       </c>
       <c r="G285" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H285" s="20" t="inlineStr"/>
     </row>
@@ -29637,7 +29637,7 @@
         </is>
       </c>
       <c r="G286" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H286" s="20" t="inlineStr"/>
     </row>
@@ -29673,7 +29673,7 @@
         </is>
       </c>
       <c r="G287" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H287" s="20" t="inlineStr"/>
     </row>
@@ -29709,7 +29709,7 @@
         </is>
       </c>
       <c r="G288" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="20" t="inlineStr"/>
     </row>
@@ -29745,7 +29745,7 @@
         </is>
       </c>
       <c r="G289" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="20" t="inlineStr"/>
     </row>
@@ -29817,7 +29817,7 @@
         </is>
       </c>
       <c r="G291" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="20" t="inlineStr"/>
     </row>
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="G292" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="20" t="inlineStr"/>
     </row>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="G295" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="20" t="inlineStr"/>
     </row>
@@ -30033,7 +30033,7 @@
         </is>
       </c>
       <c r="G297" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H297" s="20" t="inlineStr"/>
     </row>
@@ -30069,7 +30069,7 @@
         </is>
       </c>
       <c r="G298" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="20" t="inlineStr"/>
     </row>
@@ -30105,7 +30105,7 @@
         </is>
       </c>
       <c r="G299" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="20" t="inlineStr"/>
     </row>
@@ -30213,7 +30213,7 @@
         </is>
       </c>
       <c r="G302" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="20" t="inlineStr"/>
     </row>
@@ -30249,7 +30249,7 @@
         </is>
       </c>
       <c r="G303" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="20" t="inlineStr"/>
     </row>
@@ -30285,7 +30285,7 @@
         </is>
       </c>
       <c r="G304" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="20" t="inlineStr"/>
     </row>
@@ -30357,7 +30357,7 @@
         </is>
       </c>
       <c r="G306" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="20" t="inlineStr"/>
     </row>
@@ -30393,7 +30393,7 @@
         </is>
       </c>
       <c r="G307" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="20" t="inlineStr"/>
     </row>
@@ -30429,7 +30429,7 @@
         </is>
       </c>
       <c r="G308" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="20" t="inlineStr"/>
     </row>
@@ -30465,7 +30465,7 @@
         </is>
       </c>
       <c r="G309" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="20" t="inlineStr"/>
     </row>
@@ -30501,7 +30501,7 @@
         </is>
       </c>
       <c r="G310" s="18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="20" t="inlineStr"/>
     </row>
@@ -30537,7 +30537,7 @@
         </is>
       </c>
       <c r="G311" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H311" s="20" t="inlineStr"/>
     </row>
@@ -30573,7 +30573,7 @@
         </is>
       </c>
       <c r="G312" s="18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H312" s="20" t="inlineStr"/>
     </row>
@@ -30609,7 +30609,7 @@
         </is>
       </c>
       <c r="G313" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H313" s="20" t="inlineStr"/>
     </row>
@@ -30645,7 +30645,7 @@
         </is>
       </c>
       <c r="G314" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H314" s="20" t="inlineStr"/>
     </row>
@@ -30681,7 +30681,7 @@
         </is>
       </c>
       <c r="G315" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H315" s="20" t="inlineStr"/>
     </row>
@@ -30717,7 +30717,7 @@
         </is>
       </c>
       <c r="G316" s="18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H316" s="20" t="inlineStr"/>
     </row>
@@ -30753,7 +30753,7 @@
         </is>
       </c>
       <c r="G317" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H317" s="20" t="inlineStr"/>
     </row>
@@ -30789,7 +30789,7 @@
         </is>
       </c>
       <c r="G318" s="18" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="H318" s="20" t="inlineStr"/>
     </row>
@@ -30861,7 +30861,7 @@
         </is>
       </c>
       <c r="G320" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H320" s="20" t="inlineStr"/>
     </row>
@@ -30897,7 +30897,7 @@
         </is>
       </c>
       <c r="G321" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H321" s="20" t="inlineStr"/>
     </row>
@@ -30933,7 +30933,7 @@
         </is>
       </c>
       <c r="G322" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="20" t="inlineStr"/>
     </row>
@@ -30969,7 +30969,7 @@
         </is>
       </c>
       <c r="G323" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H323" s="20" t="inlineStr"/>
     </row>
@@ -31041,7 +31041,7 @@
         </is>
       </c>
       <c r="G325" s="18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H325" s="20" t="inlineStr"/>
     </row>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="G327" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H327" s="20" t="inlineStr"/>
     </row>
@@ -31149,7 +31149,7 @@
         </is>
       </c>
       <c r="G328" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H328" s="20" t="inlineStr"/>
     </row>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="G329" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H329" s="20" t="inlineStr"/>
     </row>
@@ -31221,7 +31221,7 @@
         </is>
       </c>
       <c r="G330" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H330" s="20" t="inlineStr"/>
     </row>
@@ -31293,7 +31293,7 @@
         </is>
       </c>
       <c r="G332" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H332" s="20" t="inlineStr"/>
     </row>
@@ -31329,7 +31329,7 @@
         </is>
       </c>
       <c r="G333" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H333" s="20" t="inlineStr"/>
     </row>
@@ -31365,7 +31365,7 @@
         </is>
       </c>
       <c r="G334" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="20" t="inlineStr"/>
     </row>
@@ -31401,7 +31401,7 @@
         </is>
       </c>
       <c r="G335" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="20" t="inlineStr"/>
     </row>
@@ -31437,7 +31437,7 @@
         </is>
       </c>
       <c r="G336" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H336" s="20" t="inlineStr"/>
     </row>
@@ -31473,7 +31473,7 @@
         </is>
       </c>
       <c r="G337" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="20" t="inlineStr"/>
     </row>
@@ -31509,7 +31509,7 @@
         </is>
       </c>
       <c r="G338" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="20" t="inlineStr"/>
     </row>
@@ -31581,7 +31581,7 @@
         </is>
       </c>
       <c r="G340" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="20" t="inlineStr"/>
     </row>
@@ -31617,7 +31617,7 @@
         </is>
       </c>
       <c r="G341" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="20" t="inlineStr"/>
     </row>
@@ -31653,7 +31653,7 @@
         </is>
       </c>
       <c r="G342" s="18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="20" t="inlineStr"/>
     </row>
@@ -31689,7 +31689,7 @@
         </is>
       </c>
       <c r="G343" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H343" s="20" t="inlineStr"/>
     </row>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="G344" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="20" t="inlineStr"/>
     </row>
@@ -31761,7 +31761,7 @@
         </is>
       </c>
       <c r="G345" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="20" t="inlineStr"/>
     </row>
@@ -31797,7 +31797,7 @@
         </is>
       </c>
       <c r="G346" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="20" t="inlineStr"/>
     </row>
@@ -31833,7 +31833,7 @@
         </is>
       </c>
       <c r="G347" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="20" t="inlineStr"/>
     </row>
@@ -31869,7 +31869,7 @@
         </is>
       </c>
       <c r="G348" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H348" s="20" t="inlineStr"/>
     </row>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="G349" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="20" t="inlineStr"/>
     </row>
@@ -31941,7 +31941,7 @@
         </is>
       </c>
       <c r="G350" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="20" t="inlineStr"/>
     </row>
@@ -31977,7 +31977,7 @@
         </is>
       </c>
       <c r="G351" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="20" t="inlineStr"/>
     </row>
@@ -32085,7 +32085,7 @@
         </is>
       </c>
       <c r="G354" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="20" t="inlineStr"/>
     </row>
@@ -32121,7 +32121,7 @@
         </is>
       </c>
       <c r="G355" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="20" t="inlineStr"/>
     </row>
@@ -32157,7 +32157,7 @@
         </is>
       </c>
       <c r="G356" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="20" t="inlineStr"/>
     </row>
@@ -32193,7 +32193,7 @@
         </is>
       </c>
       <c r="G357" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="20" t="inlineStr"/>
     </row>
@@ -32229,7 +32229,7 @@
         </is>
       </c>
       <c r="G358" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="20" t="inlineStr"/>
     </row>
@@ -32265,7 +32265,7 @@
         </is>
       </c>
       <c r="G359" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="20" t="inlineStr"/>
     </row>
@@ -32301,7 +32301,7 @@
         </is>
       </c>
       <c r="G360" s="18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="20" t="inlineStr"/>
     </row>
@@ -32337,7 +32337,7 @@
         </is>
       </c>
       <c r="G361" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="20" t="inlineStr"/>
     </row>
@@ -32409,7 +32409,7 @@
         </is>
       </c>
       <c r="G363" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="20" t="inlineStr"/>
     </row>
@@ -32445,7 +32445,7 @@
         </is>
       </c>
       <c r="G364" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="20" t="inlineStr"/>
     </row>
@@ -32481,7 +32481,7 @@
         </is>
       </c>
       <c r="G365" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="20" t="inlineStr"/>
     </row>
@@ -32517,7 +32517,7 @@
         </is>
       </c>
       <c r="G366" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="20" t="inlineStr"/>
     </row>
@@ -32553,7 +32553,7 @@
         </is>
       </c>
       <c r="G367" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="20" t="inlineStr"/>
     </row>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="G368" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="20" t="inlineStr"/>
     </row>
@@ -32661,7 +32661,7 @@
         </is>
       </c>
       <c r="G370" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="20" t="inlineStr"/>
     </row>
@@ -32697,7 +32697,7 @@
         </is>
       </c>
       <c r="G371" s="18" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="H371" s="20" t="inlineStr"/>
     </row>
@@ -32733,7 +32733,7 @@
         </is>
       </c>
       <c r="G372" s="18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H372" s="20" t="inlineStr"/>
     </row>
@@ -32769,7 +32769,7 @@
         </is>
       </c>
       <c r="G373" s="18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H373" s="20" t="inlineStr"/>
     </row>
@@ -32805,7 +32805,7 @@
         </is>
       </c>
       <c r="G374" s="18" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H374" s="20" t="inlineStr"/>
     </row>
@@ -32841,7 +32841,7 @@
         </is>
       </c>
       <c r="G375" s="18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H375" s="20" t="inlineStr"/>
     </row>
@@ -32877,7 +32877,7 @@
         </is>
       </c>
       <c r="G376" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H376" s="20" t="inlineStr"/>
     </row>
@@ -32913,7 +32913,7 @@
         </is>
       </c>
       <c r="G377" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H377" s="20" t="inlineStr"/>
     </row>
@@ -32949,7 +32949,7 @@
         </is>
       </c>
       <c r="G378" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H378" s="20" t="inlineStr"/>
     </row>
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="G379" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H379" s="20" t="inlineStr"/>
     </row>
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="G380" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H380" s="20" t="inlineStr"/>
     </row>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="G381" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H381" s="20" t="inlineStr"/>
     </row>
@@ -33093,7 +33093,7 @@
         </is>
       </c>
       <c r="G382" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H382" s="20" t="inlineStr"/>
     </row>
@@ -33129,7 +33129,7 @@
         </is>
       </c>
       <c r="G383" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H383" s="20" t="inlineStr"/>
     </row>
@@ -33165,7 +33165,7 @@
         </is>
       </c>
       <c r="G384" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H384" s="20" t="inlineStr"/>
     </row>
@@ -33201,7 +33201,7 @@
         </is>
       </c>
       <c r="G385" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H385" s="20" t="inlineStr"/>
     </row>
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="G387" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="20" t="inlineStr"/>
     </row>
@@ -33309,7 +33309,7 @@
         </is>
       </c>
       <c r="G388" s="18" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="20" t="inlineStr"/>
     </row>
@@ -33381,7 +33381,7 @@
         </is>
       </c>
       <c r="G390" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="20" t="inlineStr"/>
     </row>
@@ -33453,7 +33453,7 @@
         </is>
       </c>
       <c r="G392" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="20" t="inlineStr"/>
     </row>
@@ -33489,7 +33489,7 @@
         </is>
       </c>
       <c r="G393" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="20" t="inlineStr"/>
     </row>
@@ -33525,7 +33525,7 @@
         </is>
       </c>
       <c r="G394" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="20" t="inlineStr"/>
     </row>
@@ -33597,7 +33597,7 @@
         </is>
       </c>
       <c r="G396" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="20" t="inlineStr"/>
     </row>
@@ -33633,7 +33633,7 @@
         </is>
       </c>
       <c r="G397" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="20" t="inlineStr"/>
     </row>
@@ -33705,7 +33705,7 @@
         </is>
       </c>
       <c r="G399" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="20" t="inlineStr"/>
     </row>
@@ -33777,7 +33777,7 @@
         </is>
       </c>
       <c r="G401" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="20" t="inlineStr"/>
     </row>
@@ -33813,7 +33813,7 @@
         </is>
       </c>
       <c r="G402" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H402" s="20" t="inlineStr"/>
     </row>
@@ -33849,7 +33849,7 @@
         </is>
       </c>
       <c r="G403" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="20" t="inlineStr"/>
     </row>
@@ -33885,7 +33885,7 @@
         </is>
       </c>
       <c r="G404" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="20" t="inlineStr"/>
     </row>
@@ -33921,7 +33921,7 @@
         </is>
       </c>
       <c r="G405" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="20" t="inlineStr"/>
     </row>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="G406" s="18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="20" t="inlineStr"/>
     </row>
@@ -33993,7 +33993,7 @@
         </is>
       </c>
       <c r="G407" s="18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="20" t="inlineStr"/>
     </row>
@@ -34137,7 +34137,7 @@
         </is>
       </c>
       <c r="G411" s="18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H411" s="20" t="inlineStr"/>
     </row>
@@ -34173,7 +34173,7 @@
         </is>
       </c>
       <c r="G412" s="18" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H412" s="20" t="inlineStr"/>
     </row>
@@ -34281,7 +34281,7 @@
         </is>
       </c>
       <c r="G415" s="18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="20" t="inlineStr"/>
     </row>
@@ -34317,7 +34317,7 @@
         </is>
       </c>
       <c r="G416" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H416" s="20" t="inlineStr"/>
     </row>
@@ -34425,7 +34425,7 @@
         </is>
       </c>
       <c r="G419" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H419" s="20" t="inlineStr"/>
     </row>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="G420" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H420" s="20" t="inlineStr"/>
     </row>
@@ -34497,7 +34497,7 @@
         </is>
       </c>
       <c r="G421" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H421" s="20" t="inlineStr"/>
     </row>
@@ -34533,7 +34533,7 @@
         </is>
       </c>
       <c r="G422" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H422" s="20" t="inlineStr"/>
     </row>
@@ -34569,7 +34569,7 @@
         </is>
       </c>
       <c r="G423" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H423" s="20" t="inlineStr"/>
     </row>
@@ -34605,7 +34605,7 @@
         </is>
       </c>
       <c r="G424" s="18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H424" s="20" t="inlineStr"/>
     </row>
@@ -34641,7 +34641,7 @@
         </is>
       </c>
       <c r="G425" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H425" s="20" t="inlineStr"/>
     </row>
@@ -34713,7 +34713,7 @@
         </is>
       </c>
       <c r="G427" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="20" t="inlineStr"/>
     </row>
@@ -34749,7 +34749,7 @@
         </is>
       </c>
       <c r="G428" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="20" t="inlineStr"/>
     </row>
@@ -34785,7 +34785,7 @@
         </is>
       </c>
       <c r="G429" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="20" t="inlineStr"/>
     </row>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="G430" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="20" t="inlineStr"/>
     </row>
@@ -34857,7 +34857,7 @@
         </is>
       </c>
       <c r="G431" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="20" t="inlineStr"/>
     </row>
@@ -34893,7 +34893,7 @@
         </is>
       </c>
       <c r="G432" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="20" t="inlineStr"/>
     </row>
@@ -34929,7 +34929,7 @@
         </is>
       </c>
       <c r="G433" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="20" t="inlineStr"/>
     </row>
@@ -34965,7 +34965,7 @@
         </is>
       </c>
       <c r="G434" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="20" t="inlineStr"/>
     </row>
@@ -35001,7 +35001,7 @@
         </is>
       </c>
       <c r="G435" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="20" t="inlineStr"/>
     </row>
@@ -35037,7 +35037,7 @@
         </is>
       </c>
       <c r="G436" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="20" t="inlineStr"/>
     </row>
@@ -35073,7 +35073,7 @@
         </is>
       </c>
       <c r="G437" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="20" t="inlineStr"/>
     </row>
@@ -35109,7 +35109,7 @@
         </is>
       </c>
       <c r="G438" s="18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H438" s="20" t="inlineStr"/>
     </row>
@@ -35145,7 +35145,7 @@
         </is>
       </c>
       <c r="G439" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="20" t="inlineStr"/>
     </row>
@@ -35181,7 +35181,7 @@
         </is>
       </c>
       <c r="G440" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="20" t="inlineStr"/>
     </row>
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="G441" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="20" t="inlineStr"/>
     </row>
@@ -35253,7 +35253,7 @@
         </is>
       </c>
       <c r="G442" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="20" t="inlineStr"/>
     </row>
@@ -35325,7 +35325,7 @@
         </is>
       </c>
       <c r="G444" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="20" t="inlineStr"/>
     </row>
@@ -35361,7 +35361,7 @@
         </is>
       </c>
       <c r="G445" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="20" t="inlineStr"/>
     </row>
@@ -35397,7 +35397,7 @@
         </is>
       </c>
       <c r="G446" s="18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="20" t="inlineStr"/>
     </row>
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="G448" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="20" t="inlineStr"/>
     </row>
@@ -35505,7 +35505,7 @@
         </is>
       </c>
       <c r="G449" s="18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="20" t="inlineStr"/>
     </row>
@@ -35541,7 +35541,7 @@
         </is>
       </c>
       <c r="G450" s="18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="20" t="inlineStr"/>
     </row>
@@ -35577,7 +35577,7 @@
         </is>
       </c>
       <c r="G451" s="18" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H451" s="20" t="inlineStr"/>
     </row>
@@ -35613,7 +35613,7 @@
         </is>
       </c>
       <c r="G452" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H452" s="20" t="inlineStr"/>
     </row>
@@ -35649,7 +35649,7 @@
         </is>
       </c>
       <c r="G453" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H453" s="20" t="inlineStr"/>
     </row>
@@ -35685,7 +35685,7 @@
         </is>
       </c>
       <c r="G454" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H454" s="20" t="inlineStr"/>
     </row>
@@ -35721,7 +35721,7 @@
         </is>
       </c>
       <c r="G455" s="18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H455" s="20" t="inlineStr"/>
     </row>
@@ -35757,7 +35757,7 @@
         </is>
       </c>
       <c r="G456" s="18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="H456" s="20" t="inlineStr"/>
     </row>
@@ -35973,7 +35973,7 @@
         </is>
       </c>
       <c r="G462" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H462" s="20" t="inlineStr"/>
     </row>
@@ -36009,7 +36009,7 @@
         </is>
       </c>
       <c r="G463" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H463" s="20" t="inlineStr"/>
     </row>
@@ -36045,7 +36045,7 @@
         </is>
       </c>
       <c r="G464" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="20" t="inlineStr"/>
     </row>
@@ -36117,7 +36117,7 @@
         </is>
       </c>
       <c r="G466" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H466" s="20" t="inlineStr"/>
     </row>
@@ -36225,7 +36225,7 @@
         </is>
       </c>
       <c r="G469" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="20" t="inlineStr"/>
     </row>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="G470" s="18" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="20" t="inlineStr"/>
     </row>
@@ -36297,7 +36297,7 @@
         </is>
       </c>
       <c r="G471" s="18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="20" t="inlineStr"/>
     </row>
@@ -36333,7 +36333,7 @@
         </is>
       </c>
       <c r="G472" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="20" t="inlineStr"/>
     </row>
@@ -36405,7 +36405,7 @@
         </is>
       </c>
       <c r="G474" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H474" s="20" t="inlineStr"/>
     </row>
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="G475" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="20" t="inlineStr"/>
     </row>
@@ -36513,7 +36513,7 @@
         </is>
       </c>
       <c r="G477" s="18" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="20" t="inlineStr"/>
     </row>
@@ -36585,7 +36585,7 @@
         </is>
       </c>
       <c r="G479" s="18" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H479" s="20" t="inlineStr"/>
     </row>
@@ -36621,7 +36621,7 @@
         </is>
       </c>
       <c r="G480" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="20" t="inlineStr"/>
     </row>
@@ -36693,7 +36693,7 @@
         </is>
       </c>
       <c r="G482" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="20" t="inlineStr"/>
     </row>
@@ -36729,7 +36729,7 @@
         </is>
       </c>
       <c r="G483" s="18" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H483" s="20" t="inlineStr"/>
     </row>
@@ -36765,7 +36765,7 @@
         </is>
       </c>
       <c r="G484" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H484" s="20" t="inlineStr"/>
     </row>
@@ -36801,7 +36801,7 @@
         </is>
       </c>
       <c r="G485" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="20" t="inlineStr"/>
     </row>
@@ -36873,7 +36873,7 @@
         </is>
       </c>
       <c r="G487" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="20" t="inlineStr"/>
     </row>
@@ -36909,7 +36909,7 @@
         </is>
       </c>
       <c r="G488" s="18" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H488" s="20" t="inlineStr"/>
     </row>
@@ -36945,7 +36945,7 @@
         </is>
       </c>
       <c r="G489" s="18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="20" t="inlineStr"/>
     </row>
@@ -37084,7 +37084,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="H2" s="23" t="inlineStr">
         <is>
@@ -37124,7 +37124,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H3" s="23" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>10.27</v>
+        <v>10.34</v>
       </c>
       <c r="H4" s="23" t="inlineStr"/>
     </row>
@@ -37200,19 +37200,19 @@
         </is>
       </c>
       <c r="G5" s="21" t="n">
-        <v>21.31</v>
+        <v>21.29</v>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37248,19 +37248,19 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>21.95</v>
+        <v>22.05</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37296,19 +37296,19 @@
         </is>
       </c>
       <c r="G7" s="21" t="n">
-        <v>22.01</v>
+        <v>21.96</v>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37344,19 +37344,19 @@
         </is>
       </c>
       <c r="G8" s="21" t="n">
-        <v>22.07</v>
+        <v>22.05</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37392,19 +37392,19 @@
         </is>
       </c>
       <c r="G9" s="21" t="n">
-        <v>22.09</v>
+        <v>22.1</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37440,19 +37440,19 @@
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>22.07</v>
+        <v>22.05</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37488,19 +37488,19 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>22.1</v>
+        <v>22.05</v>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>
@@ -37536,19 +37536,19 @@
         </is>
       </c>
       <c r="G12" s="21" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
-#0 0x56221503644a &lt;unknown&gt;
-#1 0x562214a0e8c9 &lt;unknown&gt;
-#2 0x562214a63f32 &lt;unknown&gt;
-#3 0x562214a64181 &lt;unknown&gt;
-#4 0x562214aaf374 &lt;unknown&gt;
-#5 0x562214aac55d &lt;unknown&gt;
-#6 0x56221</t>
+#0 0x562dedeb044a &lt;unknown&gt;
+#1 0x562ded8888c9 &lt;unknown&gt;
+#2 0x562ded8ddf32 &lt;unknown&gt;
+#3 0x562ded8de181 &lt;unknown&gt;
+#4 0x562ded929374 &lt;unknown&gt;
+#5 0x562ded92655d &lt;unknown&gt;
+#6 0x562de</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -704,7 +704,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-23T14:36:00    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-29T08:41:03    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-28T05:57:11    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-29T06:02:15    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.86s</t>
+          <t>0.89s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.84s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.3s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.49</v>
+        <v>1.18</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>4.1</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.98</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.15</v>
+        <v>21.09</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.1</v>
+        <v>21.09</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>12.07</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>30.17</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.49</v>
+        <v>1.18</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.81</v>
+        <v>4.1</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.98</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.15</v>
+        <v>21.09</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.1</v>
+        <v>21.09</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>12.07</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="G199" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H199" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>30.17</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-29T06:02:15    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-30T05:49:52    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.6s</t>
+          <t>1.56s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.26s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.42s</t>
+          <t>3.35s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.89s</t>
+          <t>0.82s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.17s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>0.07s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.3s</t>
+          <t>1.29s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.18</v>
+        <v>0.46</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3.35</v>
+        <v>2.79</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.66</v>
+        <v>1.06</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.34</v>
+        <v>10.06</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.29</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>22.05</v>
+        <v>21.74</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.96</v>
+        <v>21.78</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>22.05</v>
+        <v>21.83</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>22.1</v>
+        <v>21.83</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.09</v>
+        <v>21.15</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.09</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>22.05</v>
+        <v>21.84</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>22.05</v>
+        <v>21.83</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.32</v>
+        <v>22.01</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>30.17</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.18</v>
+        <v>0.46</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>3.35</v>
+        <v>2.79</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.66</v>
+        <v>1.06</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.34</v>
+        <v>10.06</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.29</v>
+        <v>21.11</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>22.05</v>
+        <v>21.74</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.96</v>
+        <v>21.78</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>22.05</v>
+        <v>21.83</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>22.1</v>
+        <v>21.83</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.09</v>
+        <v>21.15</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.09</v>
+        <v>21.12</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>22.05</v>
+        <v>21.84</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>22.05</v>
+        <v>21.83</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.32</v>
+        <v>22.01</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>30.17</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.6s</t>
+          <t>1.56s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-30T05:49:52    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-07-31T06:21:52    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.56s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.26s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.04s</t>
+          <t>1.05s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.35s</t>
+          <t>3.39s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.32s</t>
+          <t>1.33s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.82s</t>
+          <t>0.89s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.17s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.29s</t>
+          <t>1.31s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.76</v>
+        <v>3.91</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.06</v>
+        <v>10.16</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.1</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.74</v>
+        <v>21.88</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.78</v>
+        <v>21.86</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.9</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.94</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.15</v>
+        <v>21.14</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.18</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.83</v>
+        <v>21.97</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.01</v>
+        <v>22.16</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.76</v>
+        <v>3.91</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.06</v>
+        <v>10.16</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.11</v>
+        <v>21.1</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.74</v>
+        <v>21.88</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.78</v>
+        <v>21.86</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.9</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.83</v>
+        <v>21.94</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.15</v>
+        <v>21.14</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.18</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.83</v>
+        <v>21.97</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.01</v>
+        <v>22.16</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="G261" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H261" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34116,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.56s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-07-31T06:21:52    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-01T06:05:32    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.39s</t>
+          <t>3.4s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.89s</t>
+          <t>0.88s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.47s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.19s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>1.31s</t>
+          <t>1.3s</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.1</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.88</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.86</v>
+        <v>21.77</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.9</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.94</v>
+        <v>21.93</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.14</v>
+        <v>21.18</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.18</v>
+        <v>21.15</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.92</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.97</v>
+        <v>21.92</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.16</v>
+        <v>22.18</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20112,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.1</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.88</v>
+        <v>21.83</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.86</v>
+        <v>21.77</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.9</v>
+        <v>21.88</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.94</v>
+        <v>21.93</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.14</v>
+        <v>21.18</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.18</v>
+        <v>21.15</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.92</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.97</v>
+        <v>21.92</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.16</v>
+        <v>22.18</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23568,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24612,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26232,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H232" s="19" t="inlineStr"/>
     </row>
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H233" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -28032,7 +28032,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28284,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="G255" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H255" s="19" t="inlineStr"/>
     </row>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37032,7 +37032,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-01T06:05:32    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-02T06:06:44    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>1.05s</t>
+          <t>1.04s</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.4s</t>
+          <t>3.39s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.88s</t>
+          <t>0.89s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.46s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.77</v>
+        <v>21.82</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.88</v>
+        <v>21.95</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.93</v>
+        <v>21.94</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.18</v>
+        <v>21.1</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.92</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.92</v>
+        <v>21.94</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.18</v>
+        <v>22.08</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18893,7 +18893,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.83</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.77</v>
+        <v>21.82</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.88</v>
+        <v>21.95</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.93</v>
+        <v>21.94</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.18</v>
+        <v>21.1</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.92</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.92</v>
+        <v>21.94</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.18</v>
+        <v>22.08</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25332,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="G198" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H198" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="G207" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H207" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26772,7 +26772,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26844,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27312,7 +27312,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="G226" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="19" t="inlineStr"/>
     </row>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27744,7 +27744,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -27780,7 +27780,7 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H238" s="19" t="inlineStr"/>
     </row>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -27996,7 +27996,7 @@
         </is>
       </c>
       <c r="G244" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H244" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28500,7 +28500,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H258" s="19" t="inlineStr"/>
     </row>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34512,7 +34512,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36960,7 +36960,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -693,7 +693,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-04T05:57:37    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-05T05:56:54    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.27s</t>
+          <t>1.28s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>0.85s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.53s</t>
+          <t>1.49s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.83s</t>
+          <t>0.84s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>1.25</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.14</v>
+        <v>21.09</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.73</v>
+        <v>21.78</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.08</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.08</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>21.96</v>
+        <v>22.02</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11059,7 +11059,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11419,7 +11419,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11563,7 +11563,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11635,7 +11635,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11959,7 +11959,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12391,7 +12391,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13039,7 +13039,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13327,7 +13327,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13363,7 +13363,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13723,7 +13723,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13939,7 +13939,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14227,7 +14227,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14731,7 +14731,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14911,7 +14911,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -15019,7 +15019,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15055,7 +15055,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15199,7 +15199,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15379,7 +15379,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15415,7 +15415,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15811,7 +15811,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15991,7 +15991,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16135,7 +16135,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16171,7 +16171,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16279,7 +16279,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16351,7 +16351,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16423,7 +16423,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16639,7 +16639,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16675,7 +16675,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17251,7 +17251,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17755,7 +17755,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17791,7 +17791,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17827,7 +17827,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17863,7 +17863,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17899,7 +17899,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17971,7 +17971,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18115,7 +18115,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18475,45 +18475,54 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
-      <c r="A482" s="17" t="inlineStr">
+      <c r="A482" s="20" t="inlineStr">
         <is>
           <t>TC_PERF_021</t>
         </is>
       </c>
-      <c r="B482" s="17" t="inlineStr">
+      <c r="B482" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C482" s="17" t="inlineStr">
+      <c r="C482" s="20" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D482" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E482" s="18" t="inlineStr">
+      <c r="D482" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E482" s="21" t="inlineStr">
         <is>
           <t>Performance smoke test #21</t>
         </is>
       </c>
-      <c r="F482" s="17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G482" s="17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H482" s="19" t="inlineStr"/>
+      <c r="F482" s="20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G482" s="20" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="H482" s="22" t="inlineStr">
+        <is>
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
+  (Session info: chrome=150.0.7871.128)
+Stacktrace:
+#0 0x55de0734e44a &lt;unknown&gt;
+#1 0x55de06d268c9 &lt;unknown&gt;
+#2 0x55de06d0e35a &lt;unkno</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
@@ -18547,7 +18556,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18583,7 +18592,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18619,7 +18628,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18655,7 +18664,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18691,54 +18700,45 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
     <row r="488" ht="16" customHeight="1">
-      <c r="A488" s="20" t="inlineStr">
+      <c r="A488" s="17" t="inlineStr">
         <is>
           <t>TC_PERF_027</t>
         </is>
       </c>
-      <c r="B488" s="20" t="inlineStr">
+      <c r="B488" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C488" s="20" t="inlineStr">
+      <c r="C488" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D488" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E488" s="21" t="inlineStr">
+      <c r="D488" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E488" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #27</t>
         </is>
       </c>
-      <c r="F488" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G488" s="20" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="H488" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.002
-  (Session info: chrome=150.0.7871.128)
-Stacktrace:
-#0 0x55829685c44a &lt;unknown&gt;
-#1 0x5582962348c9 &lt;unknown&gt;
-#2 0x55829621c35a &lt;unkno</t>
-        </is>
-      </c>
+      <c r="F488" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G488" s="17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H488" s="19" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
@@ -18844,7 +18844,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18880,7 +18880,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18916,7 +18916,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18988,7 +18988,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19024,7 +19024,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19168,7 +19168,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19343,7 +19343,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19451,7 +19451,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19523,7 +19523,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19559,7 +19559,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19739,7 +19739,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19775,7 +19775,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19811,7 +19811,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19847,7 +19847,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19883,7 +19883,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19919,7 +19919,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19955,7 +19955,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19991,7 +19991,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20063,7 +20063,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20135,7 +20135,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20171,7 +20171,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20243,7 +20243,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.61</v>
+        <v>1.25</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20315,7 +20315,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20675,7 +20675,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20747,7 +20747,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20819,7 +20819,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20891,7 +20891,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20927,7 +20927,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.14</v>
+        <v>21.09</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20999,7 +20999,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.73</v>
+        <v>21.78</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21143,7 +21143,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21179,7 +21179,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.08</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21215,7 +21215,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.12</v>
+        <v>21.08</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.85</v>
+        <v>21.83</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21323,7 +21323,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>21.96</v>
+        <v>22.02</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21359,7 +21359,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21395,7 +21395,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21503,7 +21503,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21647,7 +21647,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21863,7 +21863,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21935,7 +21935,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22043,7 +22043,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22115,7 +22115,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22187,7 +22187,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22223,7 +22223,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22295,7 +22295,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22367,7 +22367,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22439,7 +22439,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22475,7 +22475,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22511,7 +22511,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22583,7 +22583,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22619,7 +22619,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22727,7 +22727,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22763,7 +22763,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22799,7 +22799,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22871,7 +22871,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22907,7 +22907,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22943,7 +22943,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22979,7 +22979,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23087,7 +23087,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23123,7 +23123,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23159,7 +23159,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23195,7 +23195,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23231,7 +23231,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23267,7 +23267,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23303,7 +23303,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23339,7 +23339,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23375,7 +23375,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23411,7 +23411,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23447,7 +23447,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23483,7 +23483,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23519,7 +23519,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23555,7 +23555,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23591,7 +23591,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23771,7 +23771,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23807,7 +23807,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23915,7 +23915,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23951,7 +23951,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23987,7 +23987,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24023,7 +24023,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24059,7 +24059,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24095,7 +24095,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24131,7 +24131,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24203,7 +24203,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24239,7 +24239,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24275,7 +24275,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24347,7 +24347,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24383,7 +24383,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24419,7 +24419,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24455,7 +24455,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24563,7 +24563,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24599,7 +24599,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24635,7 +24635,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24707,7 +24707,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24743,7 +24743,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24779,7 +24779,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24995,7 +24995,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25031,7 +25031,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25067,7 +25067,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25139,7 +25139,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25211,7 +25211,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25247,7 +25247,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25283,7 +25283,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25319,7 +25319,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25787,7 +25787,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25895,7 +25895,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25931,7 +25931,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25967,7 +25967,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26111,7 +26111,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26219,7 +26219,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26291,7 +26291,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26723,7 +26723,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26759,7 +26759,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H209" s="19" t="inlineStr"/>
     </row>
@@ -26867,7 +26867,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26939,7 +26939,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -27011,7 +27011,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27155,7 +27155,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27227,7 +27227,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27335,7 +27335,7 @@
         </is>
       </c>
       <c r="G225" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H225" s="19" t="inlineStr"/>
     </row>
@@ -27407,7 +27407,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27515,7 +27515,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27659,7 +27659,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27731,7 +27731,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27875,7 +27875,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -28055,7 +28055,7 @@
         </is>
       </c>
       <c r="G245" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H245" s="19" t="inlineStr"/>
     </row>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28307,7 +28307,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28343,7 +28343,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28451,7 +28451,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28559,7 +28559,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28667,7 +28667,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28703,7 +28703,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28775,7 +28775,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28811,7 +28811,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28991,7 +28991,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29063,7 +29063,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29099,7 +29099,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29207,7 +29207,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29279,7 +29279,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29315,7 +29315,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29387,7 +29387,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29459,7 +29459,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29495,7 +29495,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29603,7 +29603,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29639,7 +29639,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29711,7 +29711,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29747,7 +29747,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29783,7 +29783,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29819,7 +29819,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29891,7 +29891,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29999,7 +29999,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30035,7 +30035,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30071,7 +30071,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30143,7 +30143,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30287,7 +30287,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30359,7 +30359,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30395,7 +30395,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30431,7 +30431,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30503,7 +30503,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30539,7 +30539,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30575,7 +30575,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30647,7 +30647,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30683,7 +30683,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30827,7 +30827,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30971,7 +30971,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -31043,7 +31043,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31079,7 +31079,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31115,7 +31115,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31187,7 +31187,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31259,7 +31259,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31295,7 +31295,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31331,7 +31331,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31403,7 +31403,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31547,7 +31547,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31619,7 +31619,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31691,7 +31691,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31727,7 +31727,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31799,7 +31799,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31943,7 +31943,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -32015,7 +32015,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32051,7 +32051,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32195,7 +32195,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32303,7 +32303,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32339,7 +32339,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32375,7 +32375,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32447,7 +32447,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32519,7 +32519,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32555,7 +32555,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32807,7 +32807,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32879,7 +32879,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32915,7 +32915,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32987,7 +32987,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33023,7 +33023,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33095,7 +33095,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33131,7 +33131,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33167,7 +33167,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33203,7 +33203,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33239,7 +33239,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33275,7 +33275,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33311,7 +33311,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33419,7 +33419,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33455,7 +33455,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33491,7 +33491,7 @@
         </is>
       </c>
       <c r="G396" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H396" s="19" t="inlineStr"/>
     </row>
@@ -33527,7 +33527,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33563,7 +33563,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33671,7 +33671,7 @@
         </is>
       </c>
       <c r="G401" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H401" s="19" t="inlineStr"/>
     </row>
@@ -33743,7 +33743,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33779,7 +33779,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33887,7 +33887,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33923,7 +33923,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33995,7 +33995,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34067,7 +34067,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34139,7 +34139,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34175,7 +34175,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34211,7 +34211,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34247,7 +34247,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34355,7 +34355,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34427,7 +34427,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34499,7 +34499,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34535,7 +34535,7 @@
         </is>
       </c>
       <c r="G425" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H425" s="19" t="inlineStr"/>
     </row>
@@ -34571,7 +34571,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34679,7 +34679,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34715,7 +34715,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34751,7 +34751,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -35111,7 +35111,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35147,7 +35147,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35327,7 +35327,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35363,7 +35363,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35579,7 +35579,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35651,7 +35651,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35723,7 +35723,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35795,7 +35795,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35867,7 +35867,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35903,7 +35903,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35939,7 +35939,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35975,7 +35975,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -36011,7 +36011,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36047,7 +36047,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36083,7 +36083,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36119,7 +36119,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36155,7 +36155,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36191,7 +36191,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36335,7 +36335,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36371,7 +36371,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36407,7 +36407,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36443,7 +36443,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36515,7 +36515,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36551,14 +36551,14 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_021</t>
+          <t>TC_PERF_022</t>
         </is>
       </c>
       <c r="B482" s="17" t="inlineStr">
@@ -36578,7 +36578,7 @@
       </c>
       <c r="E482" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #21</t>
+          <t>Performance smoke test #22</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
@@ -36594,7 +36594,7 @@
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_022</t>
+          <t>TC_PERF_023</t>
         </is>
       </c>
       <c r="B483" s="17" t="inlineStr">
@@ -36614,7 +36614,7 @@
       </c>
       <c r="E483" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #22</t>
+          <t>Performance smoke test #23</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
@@ -36623,14 +36623,14 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_023</t>
+          <t>TC_PERF_024</t>
         </is>
       </c>
       <c r="B484" s="17" t="inlineStr">
@@ -36650,7 +36650,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #23</t>
+          <t>Performance smoke test #24</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
@@ -36666,7 +36666,7 @@
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_024</t>
+          <t>TC_PERF_025</t>
         </is>
       </c>
       <c r="B485" s="17" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #24</t>
+          <t>Performance smoke test #25</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
@@ -36695,14 +36695,14 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_025</t>
+          <t>TC_PERF_026</t>
         </is>
       </c>
       <c r="B486" s="17" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="E486" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #25</t>
+          <t>Performance smoke test #26</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
@@ -36731,14 +36731,14 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_026</t>
+          <t>TC_PERF_027</t>
         </is>
       </c>
       <c r="B487" s="17" t="inlineStr">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="E487" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #26</t>
+          <t>Performance smoke test #27</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
@@ -36767,7 +36767,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36875,7 +36875,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36911,7 +36911,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36947,7 +36947,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36983,7 +36983,7 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
@@ -37019,7 +37019,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -37091,7 +37091,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37199,7 +37199,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37309,7 +37309,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>TC_PERF_027</t>
+          <t>TC_PERF_021</t>
         </is>
       </c>
       <c r="B2" s="20" t="inlineStr">
@@ -37329,7 +37329,7 @@
       </c>
       <c r="E2" s="21" t="inlineStr">
         <is>
-          <t>Performance smoke test #27</t>
+          <t>Performance smoke test #21</t>
         </is>
       </c>
       <c r="F2" s="20" t="inlineStr">
@@ -37338,16 +37338,16 @@
         </is>
       </c>
       <c r="G2" s="20" t="n">
-        <v>30.14</v>
+        <v>30.13</v>
       </c>
       <c r="H2" s="22" t="inlineStr">
         <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.002
+          <t>Message: timeout: Timed out receiving message from renderer: -0.001
   (Session info: chrome=150.0.7871.128)
 Stacktrace:
-#0 0x55829685c44a &lt;unknown&gt;
-#1 0x5582962348c9 &lt;unknown&gt;
-#2 0x55829621c35a &lt;unkno</t>
+#0 0x55de0734e44a &lt;unknown&gt;
+#1 0x55de06d268c9 &lt;unknown&gt;
+#2 0x55de06d0e35a &lt;unkno</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Results'!$A$1:$H$501</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Passed Tests'!$A$1:$H$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failed Tests'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -156,11 +156,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -205,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,15 +259,6 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -288,10 +274,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-05T05:56:54    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-06T05:58:20    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -737,22 +723,22 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.63s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -889,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.36s</t>
+          <t>3.4s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -920,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.33s</t>
+          <t>1.34s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -951,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.19s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -982,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.85s</t>
+          <t>0.88s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -1013,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.49s</t>
+          <t>1.48s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1063,19 +1049,19 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.84s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1231,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.79</v>
+        <v>1.45</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1267,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1303,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1339,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1375,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1411,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1447,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1483,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1519,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1555,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1591,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1627,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1663,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1699,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1735,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1771,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1807,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1843,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1879,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1915,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1951,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1987,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2023,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2059,7 +2045,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -2095,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2167,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2203,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2239,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2275,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2311,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2347,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2383,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2419,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2455,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2491,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2527,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2563,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2599,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2635,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2671,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2707,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2743,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2815,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2851,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.09</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2887,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.76</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2923,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.78</v>
+        <v>21.76</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2959,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2995,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.84</v>
+        <v>21.87</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3031,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3067,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3103,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.08</v>
+        <v>21.12</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3139,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.08</v>
+        <v>21.16</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3175,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3211,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3247,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.02</v>
+        <v>22.14</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3283,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3319,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3391,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3427,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3463,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3499,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3571,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3607,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3643,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3679,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3715,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3751,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3787,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3823,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3859,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3895,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3931,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3967,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -4003,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4039,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4075,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4111,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4147,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4183,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4219,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4255,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4291,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4327,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4363,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4399,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4435,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4471,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4507,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4543,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4579,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4615,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4651,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4687,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4723,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4759,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4795,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4831,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4867,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4939,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4975,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -5011,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5047,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5083,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5119,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5155,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5191,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5227,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5263,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5299,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5371,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5407,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5443,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5479,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5515,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5551,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5587,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5623,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5659,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5695,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5731,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5767,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5803,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5839,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5875,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5947,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5983,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6019,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6055,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6091,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6127,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6163,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6199,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6235,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6271,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6343,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6379,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6415,7 +6401,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -6451,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6559,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6595,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6703,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6739,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6775,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6955,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6991,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7027,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7063,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7099,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7135,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7171,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7279,7 +7265,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -7351,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7423,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7459,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7495,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7567,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7675,7 +7661,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -7711,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7747,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7783,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7819,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7855,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7891,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7927,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -8035,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8071,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8107,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8179,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8251,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8431,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8467,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8647,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8791,7 +8777,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -8863,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8899,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8935,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8971,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -9007,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9151,7 +9137,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -9187,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9331,7 +9317,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -9403,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9439,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9583,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9655,7 +9641,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -9799,7 +9785,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -10159,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10231,7 +10217,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -10267,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10375,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10411,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10483,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10591,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10663,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10771,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10807,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10843,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10879,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10915,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10951,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -11059,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11095,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11131,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11203,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11275,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11347,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11419,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11455,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11491,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11527,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11563,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11599,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11635,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11671,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11851,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11887,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11923,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11995,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12031,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12067,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12103,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12139,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12175,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12283,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12319,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12427,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12499,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12607,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12643,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12679,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12715,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12751,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12787,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12823,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12859,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12895,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12931,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12967,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -13003,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13039,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13075,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13147,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13183,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13255,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13291,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13327,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13363,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13399,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13435,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13471,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13507,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13543,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13579,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13615,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13651,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13687,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13723,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13759,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13795,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13831,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13867,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13903,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13939,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13975,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -14011,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14047,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14119,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14191,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14335,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14371,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14407,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14515,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14551,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14587,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14623,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14659,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14695,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14731,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14767,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14803,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14839,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14875,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14911,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14983,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15055,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15091,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15127,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15163,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15271,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15307,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15343,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15379,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15487,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15559,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15631,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15667,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15703,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15739,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15775,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15811,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15847,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15883,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15919,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15955,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15991,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16027,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16063,7 +16049,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -16099,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16135,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16171,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16243,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16279,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16315,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16351,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16387,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16423,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16495,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16531,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16567,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16603,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16675,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16711,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16747,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16783,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16819,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16855,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16891,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16927,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16963,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16999,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17107,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17179,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17215,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17251,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17287,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17323,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17359,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17395,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17431,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17467,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17539,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17575,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17611,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17683,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17755,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17791,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17827,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17863,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17899,7 +17885,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -17935,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17971,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -18043,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18079,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18115,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18151,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18187,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18223,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18259,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18295,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18403,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18439,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18475,54 +18461,45 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
-      <c r="A482" s="20" t="inlineStr">
+      <c r="A482" s="17" t="inlineStr">
         <is>
           <t>TC_PERF_021</t>
         </is>
       </c>
-      <c r="B482" s="20" t="inlineStr">
+      <c r="B482" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C482" s="20" t="inlineStr">
+      <c r="C482" s="17" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D482" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E482" s="21" t="inlineStr">
+      <c r="D482" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E482" s="18" t="inlineStr">
         <is>
           <t>Performance smoke test #21</t>
         </is>
       </c>
-      <c r="F482" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G482" s="20" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="H482" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=150.0.7871.128)
-Stacktrace:
-#0 0x55de0734e44a &lt;unknown&gt;
-#1 0x55de06d268c9 &lt;unknown&gt;
-#2 0x55de06d0e35a &lt;unkno</t>
-        </is>
-      </c>
+      <c r="F482" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G482" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H482" s="19" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
@@ -18556,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18628,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18664,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18700,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18736,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18772,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18808,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18844,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18880,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18952,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -18988,7 +18965,7 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
@@ -19024,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19060,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19132,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19204,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19220,7 +19197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H500"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19307,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>0.79</v>
+        <v>1.45</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19343,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19379,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19415,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19451,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19487,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19523,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19559,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19595,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19631,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19667,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19703,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19739,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19775,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19811,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19847,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19883,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19919,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19955,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19991,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20027,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20063,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20099,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20135,7 +20112,7 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="19" t="inlineStr"/>
     </row>
@@ -20171,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20243,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20279,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20315,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20351,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20387,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20423,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20459,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20495,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20531,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20567,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20603,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20639,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20675,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20711,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20747,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20783,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20819,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20891,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20927,7 +20904,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.09</v>
+        <v>21.15</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -20963,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.76</v>
+        <v>21.81</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20999,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.78</v>
+        <v>21.76</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21035,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21071,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.84</v>
+        <v>21.87</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21107,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21143,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21179,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.08</v>
+        <v>21.12</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21215,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.08</v>
+        <v>21.16</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21251,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.86</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21287,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21323,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.02</v>
+        <v>22.14</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21359,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21395,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21467,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21503,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21539,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21575,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21647,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21683,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21719,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21755,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21791,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21827,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21863,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21899,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21935,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21971,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -22007,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22043,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22079,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22115,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22151,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22187,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22223,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22259,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22295,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22331,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22367,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22403,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22439,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22475,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22511,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22547,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22583,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22619,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22655,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22691,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22727,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22763,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22799,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22835,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22871,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22907,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22943,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -23015,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23051,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23087,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23123,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23159,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23195,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23231,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23267,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23303,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23339,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23375,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23447,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23483,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23519,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23555,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23591,7 +23568,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -23627,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23663,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23699,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23735,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23771,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23807,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23843,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23879,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23915,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23951,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -24023,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24059,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24095,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24131,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24167,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24203,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24239,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24275,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24311,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24347,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24419,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24455,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24491,7 +24468,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H146" s="19" t="inlineStr"/>
     </row>
@@ -24527,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24635,7 +24612,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -24671,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24779,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24815,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24851,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -25031,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25067,7 +25044,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -25103,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25139,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25175,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25211,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25247,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25355,7 +25332,7 @@
         </is>
       </c>
       <c r="G170" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H170" s="19" t="inlineStr"/>
     </row>
@@ -25427,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25499,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25535,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25571,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25643,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25751,7 +25728,7 @@
         </is>
       </c>
       <c r="G181" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H181" s="19" t="inlineStr"/>
     </row>
@@ -25787,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25823,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25859,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25895,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25931,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25967,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -26003,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26111,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26147,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26183,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26255,7 +26232,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -26327,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26507,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26543,7 +26520,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -26723,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26867,7 +26844,7 @@
         </is>
       </c>
       <c r="G212" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H212" s="19" t="inlineStr"/>
     </row>
@@ -26939,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26975,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -27011,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27047,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27083,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27227,7 +27204,7 @@
         </is>
       </c>
       <c r="G222" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H222" s="19" t="inlineStr"/>
     </row>
@@ -27263,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27407,7 +27384,7 @@
         </is>
       </c>
       <c r="G227" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H227" s="19" t="inlineStr"/>
     </row>
@@ -27479,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27515,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27659,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27731,7 +27708,7 @@
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="19" t="inlineStr"/>
     </row>
@@ -27875,7 +27852,7 @@
         </is>
       </c>
       <c r="G240" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H240" s="19" t="inlineStr"/>
     </row>
@@ -28235,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28307,7 +28284,7 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H252" s="19" t="inlineStr"/>
     </row>
@@ -28343,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28451,7 +28428,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28487,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28559,7 +28536,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -28667,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28739,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28847,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28883,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28919,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28955,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28991,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29027,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29135,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29171,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29207,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29279,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29351,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29423,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29495,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29531,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29567,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29603,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29639,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29675,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29711,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29747,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29927,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29963,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29999,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30071,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30107,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30143,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30179,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30215,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30251,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30359,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30395,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30503,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30575,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30683,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30719,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30755,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30791,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30827,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30863,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30899,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30935,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30971,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -31007,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31043,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31079,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31115,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31151,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31223,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31259,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31331,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31367,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31403,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31439,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31475,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31511,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31547,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31583,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31619,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31655,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31691,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31727,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31763,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31799,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31835,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31871,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31907,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31943,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31979,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -32015,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32051,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32087,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32123,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32195,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32267,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32411,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32447,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32483,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32591,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32627,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32663,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32699,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32735,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32771,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32807,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32843,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32879,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32915,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32951,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32987,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33059,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33131,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33167,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33203,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33239,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33347,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33383,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33419,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33455,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33563,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33635,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33707,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33743,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33779,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33815,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33851,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33887,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33923,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33959,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33995,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34031,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34067,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34103,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34139,7 +34116,7 @@
         </is>
       </c>
       <c r="G414" s="17" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="H414" s="19" t="inlineStr"/>
     </row>
@@ -34175,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34211,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34247,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34319,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34355,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34391,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34427,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34463,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34499,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34571,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34607,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34643,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34679,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34751,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34787,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34823,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34859,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34895,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34931,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34967,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -35003,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35039,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35075,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35183,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35255,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35291,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35327,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35363,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35399,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35435,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35471,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35507,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35543,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35615,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35651,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35687,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35759,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35831,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35867,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35903,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35939,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35975,7 +35952,7 @@
         </is>
       </c>
       <c r="G465" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H465" s="19" t="inlineStr"/>
     </row>
@@ -36011,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36047,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36119,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36155,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36191,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36227,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36263,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36299,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36335,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36371,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36479,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36515,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36551,14 +36528,14 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
     <row r="482" ht="16" customHeight="1">
       <c r="A482" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_022</t>
+          <t>TC_PERF_021</t>
         </is>
       </c>
       <c r="B482" s="17" t="inlineStr">
@@ -36578,7 +36555,7 @@
       </c>
       <c r="E482" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #22</t>
+          <t>Performance smoke test #21</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
@@ -36587,14 +36564,14 @@
         </is>
       </c>
       <c r="G482" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H482" s="19" t="inlineStr"/>
     </row>
     <row r="483" ht="16" customHeight="1">
       <c r="A483" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_023</t>
+          <t>TC_PERF_022</t>
         </is>
       </c>
       <c r="B483" s="17" t="inlineStr">
@@ -36614,7 +36591,7 @@
       </c>
       <c r="E483" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #23</t>
+          <t>Performance smoke test #22</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
@@ -36623,14 +36600,14 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
     <row r="484" ht="16" customHeight="1">
       <c r="A484" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_024</t>
+          <t>TC_PERF_023</t>
         </is>
       </c>
       <c r="B484" s="17" t="inlineStr">
@@ -36650,7 +36627,7 @@
       </c>
       <c r="E484" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #24</t>
+          <t>Performance smoke test #23</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
@@ -36659,14 +36636,14 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
     <row r="485" ht="16" customHeight="1">
       <c r="A485" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_025</t>
+          <t>TC_PERF_024</t>
         </is>
       </c>
       <c r="B485" s="17" t="inlineStr">
@@ -36686,7 +36663,7 @@
       </c>
       <c r="E485" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #25</t>
+          <t>Performance smoke test #24</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
@@ -36695,14 +36672,14 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
     <row r="486" ht="16" customHeight="1">
       <c r="A486" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_026</t>
+          <t>TC_PERF_025</t>
         </is>
       </c>
       <c r="B486" s="17" t="inlineStr">
@@ -36722,7 +36699,7 @@
       </c>
       <c r="E486" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #26</t>
+          <t>Performance smoke test #25</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
@@ -36731,14 +36708,14 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
     <row r="487" ht="16" customHeight="1">
       <c r="A487" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_027</t>
+          <t>TC_PERF_026</t>
         </is>
       </c>
       <c r="B487" s="17" t="inlineStr">
@@ -36758,7 +36735,7 @@
       </c>
       <c r="E487" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #27</t>
+          <t>Performance smoke test #26</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
@@ -36767,14 +36744,14 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
     <row r="488" ht="16" customHeight="1">
       <c r="A488" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_028</t>
+          <t>TC_PERF_027</t>
         </is>
       </c>
       <c r="B488" s="17" t="inlineStr">
@@ -36794,7 +36771,7 @@
       </c>
       <c r="E488" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #28</t>
+          <t>Performance smoke test #27</t>
         </is>
       </c>
       <c r="F488" s="17" t="inlineStr">
@@ -36803,14 +36780,14 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
     <row r="489" ht="16" customHeight="1">
       <c r="A489" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_029</t>
+          <t>TC_PERF_028</t>
         </is>
       </c>
       <c r="B489" s="17" t="inlineStr">
@@ -36830,7 +36807,7 @@
       </c>
       <c r="E489" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #29</t>
+          <t>Performance smoke test #28</t>
         </is>
       </c>
       <c r="F489" s="17" t="inlineStr">
@@ -36839,14 +36816,14 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
     <row r="490" ht="16" customHeight="1">
       <c r="A490" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_030</t>
+          <t>TC_PERF_029</t>
         </is>
       </c>
       <c r="B490" s="17" t="inlineStr">
@@ -36866,7 +36843,7 @@
       </c>
       <c r="E490" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #30</t>
+          <t>Performance smoke test #29</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
@@ -36875,14 +36852,14 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
     <row r="491" ht="16" customHeight="1">
       <c r="A491" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_031</t>
+          <t>TC_PERF_030</t>
         </is>
       </c>
       <c r="B491" s="17" t="inlineStr">
@@ -36902,7 +36879,7 @@
       </c>
       <c r="E491" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #31</t>
+          <t>Performance smoke test #30</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
@@ -36911,14 +36888,14 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
     <row r="492" ht="16" customHeight="1">
       <c r="A492" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_032</t>
+          <t>TC_PERF_031</t>
         </is>
       </c>
       <c r="B492" s="17" t="inlineStr">
@@ -36938,7 +36915,7 @@
       </c>
       <c r="E492" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #32</t>
+          <t>Performance smoke test #31</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
@@ -36947,14 +36924,14 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
     <row r="493" ht="16" customHeight="1">
       <c r="A493" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_033</t>
+          <t>TC_PERF_032</t>
         </is>
       </c>
       <c r="B493" s="17" t="inlineStr">
@@ -36974,7 +36951,7 @@
       </c>
       <c r="E493" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #33</t>
+          <t>Performance smoke test #32</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
@@ -36983,14 +36960,14 @@
         </is>
       </c>
       <c r="G493" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="19" t="inlineStr"/>
     </row>
     <row r="494" ht="16" customHeight="1">
       <c r="A494" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_034</t>
+          <t>TC_PERF_033</t>
         </is>
       </c>
       <c r="B494" s="17" t="inlineStr">
@@ -37010,7 +36987,7 @@
       </c>
       <c r="E494" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #34</t>
+          <t>Performance smoke test #33</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
@@ -37019,14 +36996,14 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
     <row r="495" ht="16" customHeight="1">
       <c r="A495" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_035</t>
+          <t>TC_PERF_034</t>
         </is>
       </c>
       <c r="B495" s="17" t="inlineStr">
@@ -37046,7 +37023,7 @@
       </c>
       <c r="E495" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #35</t>
+          <t>Performance smoke test #34</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
@@ -37055,14 +37032,14 @@
         </is>
       </c>
       <c r="G495" s="17" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H495" s="19" t="inlineStr"/>
     </row>
     <row r="496" ht="16" customHeight="1">
       <c r="A496" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_036</t>
+          <t>TC_PERF_035</t>
         </is>
       </c>
       <c r="B496" s="17" t="inlineStr">
@@ -37082,7 +37059,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #36</t>
+          <t>Performance smoke test #35</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
@@ -37091,14 +37068,14 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
     <row r="497" ht="16" customHeight="1">
       <c r="A497" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_037</t>
+          <t>TC_PERF_036</t>
         </is>
       </c>
       <c r="B497" s="17" t="inlineStr">
@@ -37118,7 +37095,7 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #37</t>
+          <t>Performance smoke test #36</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
@@ -37127,14 +37104,14 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
     <row r="498" ht="16" customHeight="1">
       <c r="A498" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_038</t>
+          <t>TC_PERF_037</t>
         </is>
       </c>
       <c r="B498" s="17" t="inlineStr">
@@ -37154,7 +37131,7 @@
       </c>
       <c r="E498" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #38</t>
+          <t>Performance smoke test #37</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
@@ -37170,7 +37147,7 @@
     <row r="499" ht="16" customHeight="1">
       <c r="A499" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_039</t>
+          <t>TC_PERF_038</t>
         </is>
       </c>
       <c r="B499" s="17" t="inlineStr">
@@ -37190,7 +37167,7 @@
       </c>
       <c r="E499" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #39</t>
+          <t>Performance smoke test #38</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
@@ -37199,14 +37176,14 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
     <row r="500" ht="16" customHeight="1">
       <c r="A500" s="17" t="inlineStr">
         <is>
-          <t>TC_PERF_040</t>
+          <t>TC_PERF_039</t>
         </is>
       </c>
       <c r="B500" s="17" t="inlineStr">
@@ -37226,7 +37203,7 @@
       </c>
       <c r="E500" s="18" t="inlineStr">
         <is>
-          <t>Performance smoke test #40</t>
+          <t>Performance smoke test #39</t>
         </is>
       </c>
       <c r="F500" s="17" t="inlineStr">
@@ -37239,8 +37216,44 @@
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
+    <row r="501" ht="16" customHeight="1">
+      <c r="A501" s="17" t="inlineStr">
+        <is>
+          <t>TC_PERF_040</t>
+        </is>
+      </c>
+      <c r="B501" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C501" s="17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D501" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E501" s="18" t="inlineStr">
+        <is>
+          <t>Performance smoke test #40</t>
+        </is>
+      </c>
+      <c r="F501" s="17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G501" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H501" s="19" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H500"/>
+  <autoFilter ref="A1:H501"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37251,7 +37264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37306,53 +37319,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>TC_PERF_021</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>Performance smoke test #21</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G2" s="20" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
-        <is>
-          <t>Message: timeout: Timed out receiving message from renderer: -0.001
-  (Session info: chrome=150.0.7871.128)
-Stacktrace:
-#0 0x55de0734e44a &lt;unknown&gt;
-#1 0x55de06d268c9 &lt;unknown&gt;
-#2 0x55de06d0e35a &lt;unkno</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37374,34 +37342,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Pass %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
@@ -37422,7 +37390,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
@@ -37443,7 +37411,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
@@ -37464,7 +37432,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
@@ -37485,7 +37453,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Form Validation</t>
         </is>
@@ -37506,7 +37474,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
@@ -37527,7 +37495,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
@@ -37548,7 +37516,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
@@ -37557,19 +37525,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Responsive Design</t>
         </is>
@@ -37590,7 +37558,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
@@ -37611,7 +37579,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Session Security</t>
         </is>
@@ -37632,7 +37600,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>UI Validation</t>
         </is>
@@ -37673,216 +37641,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>400+</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>99.8%</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>≥ 95%</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Failed Tests</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="B4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>≤ 5%</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Avg Execution Time</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>1.63s</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>1.58s</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>≤ 3.0s</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Test Coverage (Pages)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>19 routes / 14 page objects</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>All routes</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Automation Framework</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Selenium 4.18 + Python 3.11</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Load Testing</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>k6 — 100 VUs × 60s</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>CI/CD Pipeline</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>GitHub Actions</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Report Format</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Excel + HTML + JSON</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-06T05:58:20    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-07T05:05:02    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>1.28s</t>
+          <t>1.27s</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.4s</t>
+          <t>3.38s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>1.34s</t>
+          <t>1.32s</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.19s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.88s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.48s</t>
+          <t>1.46s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.08s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.09</v>
+        <v>10.15</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.81</v>
+        <v>21.82</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.76</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.84</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.87</v>
+        <v>21.89</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.87</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10793,7 +10793,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -13673,7 +13673,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -13709,7 +13709,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13961,7 +13961,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -14501,7 +14501,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -14681,7 +14681,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14789,7 +14789,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15473,7 +15473,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15761,7 +15761,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -16661,7 +16661,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16769,7 +16769,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17021,7 +17021,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17237,7 +17237,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17705,7 +17705,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -17741,7 +17741,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -18245,7 +18245,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -18281,7 +18281,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18821,7 +18821,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19145,7 +19145,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19752,7 +19752,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20436,7 +20436,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.09</v>
+        <v>10.15</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.81</v>
+        <v>21.82</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.76</v>
+        <v>21.81</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.89</v>
+        <v>21.84</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.87</v>
+        <v>21.89</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.86</v>
+        <v>21.83</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.87</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.14</v>
+        <v>22.11</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22200,7 +22200,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22488,7 +22488,7 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H91" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22920,7 +22920,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23280,7 +23280,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="G123" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H123" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="G143" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H143" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24648,7 +24648,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -24720,7 +24720,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24900,7 +24900,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25188,7 +25188,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25440,7 +25440,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="G174" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H174" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26088,7 +26088,7 @@
         </is>
       </c>
       <c r="G191" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H191" s="19" t="inlineStr"/>
     </row>
@@ -26124,7 +26124,7 @@
         </is>
       </c>
       <c r="G192" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H192" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H196" s="19" t="inlineStr"/>
     </row>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="G197" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H197" s="19" t="inlineStr"/>
     </row>
@@ -26412,7 +26412,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -26628,7 +26628,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H229" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -28464,7 +28464,7 @@
         </is>
       </c>
       <c r="G257" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H257" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="G264" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H264" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28824,7 +28824,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="G268" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H268" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29004,7 +29004,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="H272" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="G274" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H274" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29184,7 +29184,7 @@
         </is>
       </c>
       <c r="G277" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H277" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="19" t="inlineStr"/>
     </row>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="G281" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H281" s="19" t="inlineStr"/>
     </row>
@@ -29364,7 +29364,7 @@
         </is>
       </c>
       <c r="G282" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H282" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H286" s="19" t="inlineStr"/>
     </row>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H287" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="G289" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H289" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="G292" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H292" s="19" t="inlineStr"/>
     </row>
@@ -29760,7 +29760,7 @@
         </is>
       </c>
       <c r="G293" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H293" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29904,7 +29904,7 @@
         </is>
       </c>
       <c r="G297" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H297" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30012,7 +30012,7 @@
         </is>
       </c>
       <c r="G300" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H300" s="19" t="inlineStr"/>
     </row>
@@ -30048,7 +30048,7 @@
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H301" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
         </is>
       </c>
       <c r="G303" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H303" s="19" t="inlineStr"/>
     </row>
@@ -30156,7 +30156,7 @@
         </is>
       </c>
       <c r="G304" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H304" s="19" t="inlineStr"/>
     </row>
@@ -30192,7 +30192,7 @@
         </is>
       </c>
       <c r="G305" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H305" s="19" t="inlineStr"/>
     </row>
@@ -30228,7 +30228,7 @@
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H306" s="19" t="inlineStr"/>
     </row>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="G308" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H308" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="G310" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H310" s="19" t="inlineStr"/>
     </row>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="G311" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H311" s="19" t="inlineStr"/>
     </row>
@@ -30444,7 +30444,7 @@
         </is>
       </c>
       <c r="G312" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H312" s="19" t="inlineStr"/>
     </row>
@@ -30480,7 +30480,7 @@
         </is>
       </c>
       <c r="G313" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H313" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
         </is>
       </c>
       <c r="G315" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H315" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="G323" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H323" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="G333" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H333" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31416,7 +31416,7 @@
         </is>
       </c>
       <c r="G339" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H339" s="19" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
         </is>
       </c>
       <c r="G340" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H340" s="19" t="inlineStr"/>
     </row>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="G341" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H341" s="19" t="inlineStr"/>
     </row>
@@ -31524,7 +31524,7 @@
         </is>
       </c>
       <c r="G342" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H342" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
         </is>
       </c>
       <c r="G344" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H344" s="19" t="inlineStr"/>
     </row>
@@ -31632,7 +31632,7 @@
         </is>
       </c>
       <c r="G345" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H345" s="19" t="inlineStr"/>
     </row>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="G346" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H346" s="19" t="inlineStr"/>
     </row>
@@ -31704,7 +31704,7 @@
         </is>
       </c>
       <c r="G347" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H347" s="19" t="inlineStr"/>
     </row>
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="G348" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H348" s="19" t="inlineStr"/>
     </row>
@@ -31776,7 +31776,7 @@
         </is>
       </c>
       <c r="G349" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H349" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31848,7 +31848,7 @@
         </is>
       </c>
       <c r="G351" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H351" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31956,7 +31956,7 @@
         </is>
       </c>
       <c r="G354" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H354" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
         </is>
       </c>
       <c r="G356" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H356" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="G359" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H359" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="G363" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H363" s="19" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
         </is>
       </c>
       <c r="G365" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H365" s="19" t="inlineStr"/>
     </row>
@@ -32388,7 +32388,7 @@
         </is>
       </c>
       <c r="G366" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H366" s="19" t="inlineStr"/>
     </row>
@@ -32460,7 +32460,7 @@
         </is>
       </c>
       <c r="G368" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H368" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="G370" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H370" s="19" t="inlineStr"/>
     </row>
@@ -32568,7 +32568,7 @@
         </is>
       </c>
       <c r="G371" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H371" s="19" t="inlineStr"/>
     </row>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G372" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H372" s="19" t="inlineStr"/>
     </row>
@@ -32640,7 +32640,7 @@
         </is>
       </c>
       <c r="G373" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H373" s="19" t="inlineStr"/>
     </row>
@@ -32712,7 +32712,7 @@
         </is>
       </c>
       <c r="G375" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H375" s="19" t="inlineStr"/>
     </row>
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="G376" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H376" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32856,7 +32856,7 @@
         </is>
       </c>
       <c r="G379" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H379" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="G383" s="17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H383" s="19" t="inlineStr"/>
     </row>
@@ -33036,7 +33036,7 @@
         </is>
       </c>
       <c r="G384" s="17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H384" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="G389" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H389" s="19" t="inlineStr"/>
     </row>
@@ -33252,7 +33252,7 @@
         </is>
       </c>
       <c r="G390" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H390" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="G398" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H398" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="G400" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H400" s="19" t="inlineStr"/>
     </row>
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="G402" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H402" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33828,7 +33828,7 @@
         </is>
       </c>
       <c r="G406" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H406" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33900,7 +33900,7 @@
         </is>
       </c>
       <c r="G408" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H408" s="19" t="inlineStr"/>
     </row>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="G409" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H409" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34044,7 +34044,7 @@
         </is>
       </c>
       <c r="G412" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H412" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="G416" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H416" s="19" t="inlineStr"/>
     </row>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="G417" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H417" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
         </is>
       </c>
       <c r="G419" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H419" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34368,7 +34368,7 @@
         </is>
       </c>
       <c r="G421" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H421" s="19" t="inlineStr"/>
     </row>
@@ -34404,7 +34404,7 @@
         </is>
       </c>
       <c r="G422" s="17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H422" s="19" t="inlineStr"/>
     </row>
@@ -34440,7 +34440,7 @@
         </is>
       </c>
       <c r="G423" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H423" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34548,7 +34548,7 @@
         </is>
       </c>
       <c r="G426" s="17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H426" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34620,7 +34620,7 @@
         </is>
       </c>
       <c r="G428" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H428" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34692,7 +34692,7 @@
         </is>
       </c>
       <c r="G430" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H430" s="19" t="inlineStr"/>
     </row>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="G431" s="17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H431" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34836,7 +34836,7 @@
         </is>
       </c>
       <c r="G434" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H434" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34908,7 +34908,7 @@
         </is>
       </c>
       <c r="G436" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H436" s="19" t="inlineStr"/>
     </row>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="G437" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H437" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35088,7 +35088,7 @@
         </is>
       </c>
       <c r="G441" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H441" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="G443" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H443" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35232,7 +35232,7 @@
         </is>
       </c>
       <c r="G445" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H445" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35304,7 +35304,7 @@
         </is>
       </c>
       <c r="G447" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H447" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="G449" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H449" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G460" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H460" s="19" t="inlineStr"/>
     </row>
@@ -35808,7 +35808,7 @@
         </is>
       </c>
       <c r="G461" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H461" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="G463" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H463" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36096,7 +36096,7 @@
         </is>
       </c>
       <c r="G469" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H469" s="19" t="inlineStr"/>
     </row>
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="G470" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H470" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36204,7 +36204,7 @@
         </is>
       </c>
       <c r="G472" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H472" s="19" t="inlineStr"/>
     </row>
@@ -36312,7 +36312,7 @@
         </is>
       </c>
       <c r="G475" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H475" s="19" t="inlineStr"/>
     </row>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="G476" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H476" s="19" t="inlineStr"/>
     </row>
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="G477" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H477" s="19" t="inlineStr"/>
     </row>
@@ -36420,7 +36420,7 @@
         </is>
       </c>
       <c r="G478" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H478" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36888,7 +36888,7 @@
         </is>
       </c>
       <c r="G491" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H491" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37140,7 +37140,7 @@
         </is>
       </c>
       <c r="G498" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H498" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37212,7 +37212,7 @@
         </is>
       </c>
       <c r="G500" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H500" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-07T05:05:02    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-08T04:21:51    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.38s</t>
+          <t>3.39s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.17s</t>
+          <t>1.18s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.87s</t>
+          <t>0.9s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.46s</t>
+          <t>1.49s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.18s</t>
+          <t>2.19s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.09s</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.15</v>
+        <v>10.19</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.82</v>
+        <v>21.87</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.81</v>
+        <v>21.83</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.84</v>
+        <v>21.92</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.14</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.87</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -12269,7 +12269,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -12593,7 +12593,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -12701,7 +12701,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -12953,7 +12953,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -13061,7 +13061,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -13493,7 +13493,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -13853,7 +13853,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -15005,7 +15005,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -15077,7 +15077,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -15293,7 +15293,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -15329,7 +15329,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -15437,7 +15437,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -15797,7 +15797,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -16985,7 +16985,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -17273,7 +17273,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -17345,7 +17345,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -17381,7 +17381,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -17453,7 +17453,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -17669,7 +17669,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -18101,7 +18101,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -18461,7 +18461,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -18713,7 +18713,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -18785,7 +18785,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -19037,7 +19037,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -19181,7 +19181,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -19284,7 +19284,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -19320,7 +19320,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -19428,7 +19428,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -19464,7 +19464,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -19608,7 +19608,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -20040,7 +20040,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -20148,7 +20148,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -20220,7 +20220,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -20292,7 +20292,7 @@
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
     </row>
@@ -20328,7 +20328,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -20400,7 +20400,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -20472,7 +20472,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -20508,7 +20508,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -20544,7 +20544,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
     </row>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -20652,7 +20652,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.15</v>
+        <v>10.19</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -20868,7 +20868,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.82</v>
+        <v>21.87</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.81</v>
+        <v>21.83</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.84</v>
+        <v>21.92</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -21120,7 +21120,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.12</v>
+        <v>21.14</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>21.16</v>
+        <v>21.13</v>
       </c>
       <c r="H55" s="19" t="inlineStr"/>
     </row>
@@ -21228,7 +21228,7 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>21.83</v>
+        <v>21.87</v>
       </c>
       <c r="H56" s="19" t="inlineStr"/>
     </row>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.87</v>
+        <v>21.89</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -21372,7 +21372,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -21408,7 +21408,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -21444,7 +21444,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" s="19" t="inlineStr"/>
     </row>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="G64" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H64" s="19" t="inlineStr"/>
     </row>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -21660,7 +21660,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -21768,7 +21768,7 @@
         </is>
       </c>
       <c r="G71" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H71" s="19" t="inlineStr"/>
     </row>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H77" s="19" t="inlineStr"/>
     </row>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -22056,7 +22056,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="G80" s="17" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H80" s="19" t="inlineStr"/>
     </row>
@@ -22128,7 +22128,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -22380,7 +22380,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -22452,7 +22452,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H90" s="19" t="inlineStr"/>
     </row>
@@ -22524,7 +22524,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -22560,7 +22560,7 @@
         </is>
       </c>
       <c r="G93" s="17" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H93" s="19" t="inlineStr"/>
     </row>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -22632,7 +22632,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -22668,7 +22668,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -22704,7 +22704,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -22740,7 +22740,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -22884,7 +22884,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -23028,7 +23028,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -23244,7 +23244,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -23352,7 +23352,7 @@
         </is>
       </c>
       <c r="G115" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H115" s="19" t="inlineStr"/>
     </row>
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -23424,7 +23424,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -23496,7 +23496,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -23532,7 +23532,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -23964,7 +23964,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -24000,7 +24000,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -24036,7 +24036,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -24144,7 +24144,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -24216,7 +24216,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -24252,7 +24252,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -24324,7 +24324,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="G144" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H144" s="19" t="inlineStr"/>
     </row>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="G149" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H149" s="19" t="inlineStr"/>
     </row>
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -24792,7 +24792,7 @@
         </is>
       </c>
       <c r="G155" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H155" s="19" t="inlineStr"/>
     </row>
@@ -24828,7 +24828,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -24864,7 +24864,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -25008,7 +25008,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -25080,7 +25080,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="19" t="inlineStr"/>
     </row>
@@ -25260,7 +25260,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H168" s="19" t="inlineStr"/>
     </row>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -25368,7 +25368,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -25512,7 +25512,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -25656,7 +25656,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -25764,7 +25764,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -25872,7 +25872,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="G186" s="17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H186" s="19" t="inlineStr"/>
     </row>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H188" s="19" t="inlineStr"/>
     </row>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="G193" s="17" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="H193" s="19" t="inlineStr"/>
     </row>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -26448,7 +26448,7 @@
         </is>
       </c>
       <c r="G201" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H201" s="19" t="inlineStr"/>
     </row>
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="G211" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H211" s="19" t="inlineStr"/>
     </row>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="G214" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H214" s="19" t="inlineStr"/>
     </row>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="19" t="inlineStr"/>
     </row>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H217" s="19" t="inlineStr"/>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -27240,7 +27240,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="G228" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H228" s="19" t="inlineStr"/>
     </row>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H230" s="19" t="inlineStr"/>
     </row>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H234" s="19" t="inlineStr"/>
     </row>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -27816,7 +27816,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -27924,7 +27924,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="G246" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="19" t="inlineStr"/>
     </row>
@@ -28104,7 +28104,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -28140,7 +28140,7 @@
         </is>
       </c>
       <c r="G248" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H248" s="19" t="inlineStr"/>
     </row>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -28356,7 +28356,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -28644,7 +28644,7 @@
         </is>
       </c>
       <c r="G262" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H262" s="19" t="inlineStr"/>
     </row>
@@ -28680,7 +28680,7 @@
         </is>
       </c>
       <c r="G263" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H263" s="19" t="inlineStr"/>
     </row>
@@ -28752,7 +28752,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -28788,7 +28788,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="G270" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H270" s="19" t="inlineStr"/>
     </row>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="G271" s="17" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="H271" s="19" t="inlineStr"/>
     </row>
@@ -29040,7 +29040,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H273" s="19" t="inlineStr"/>
     </row>
@@ -29112,7 +29112,7 @@
         </is>
       </c>
       <c r="G275" s="17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="H275" s="19" t="inlineStr"/>
     </row>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="G276" s="17" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="H276" s="19" t="inlineStr"/>
     </row>
@@ -29220,7 +29220,7 @@
         </is>
       </c>
       <c r="G278" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H278" s="19" t="inlineStr"/>
     </row>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H279" s="19" t="inlineStr"/>
     </row>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="G283" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H283" s="19" t="inlineStr"/>
     </row>
@@ -29436,7 +29436,7 @@
         </is>
       </c>
       <c r="G284" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H284" s="19" t="inlineStr"/>
     </row>
@@ -29472,7 +29472,7 @@
         </is>
       </c>
       <c r="G285" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H285" s="19" t="inlineStr"/>
     </row>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="G288" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H288" s="19" t="inlineStr"/>
     </row>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="G290" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="19" t="inlineStr"/>
     </row>
@@ -29688,7 +29688,7 @@
         </is>
       </c>
       <c r="G291" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H291" s="19" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="G294" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H294" s="19" t="inlineStr"/>
     </row>
@@ -29832,7 +29832,7 @@
         </is>
       </c>
       <c r="G295" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H295" s="19" t="inlineStr"/>
     </row>
@@ -29868,7 +29868,7 @@
         </is>
       </c>
       <c r="G296" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H296" s="19" t="inlineStr"/>
     </row>
@@ -29940,7 +29940,7 @@
         </is>
       </c>
       <c r="G298" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H298" s="19" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="G299" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H299" s="19" t="inlineStr"/>
     </row>
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="G302" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H302" s="19" t="inlineStr"/>
     </row>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="G307" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H307" s="19" t="inlineStr"/>
     </row>
@@ -30336,7 +30336,7 @@
         </is>
       </c>
       <c r="G309" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H309" s="19" t="inlineStr"/>
     </row>
@@ -30516,7 +30516,7 @@
         </is>
       </c>
       <c r="G314" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H314" s="19" t="inlineStr"/>
     </row>
@@ -30588,7 +30588,7 @@
         </is>
       </c>
       <c r="G316" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H316" s="19" t="inlineStr"/>
     </row>
@@ -30624,7 +30624,7 @@
         </is>
       </c>
       <c r="G317" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H317" s="19" t="inlineStr"/>
     </row>
@@ -30660,7 +30660,7 @@
         </is>
       </c>
       <c r="G318" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H318" s="19" t="inlineStr"/>
     </row>
@@ -30696,7 +30696,7 @@
         </is>
       </c>
       <c r="G319" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H319" s="19" t="inlineStr"/>
     </row>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="G320" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H320" s="19" t="inlineStr"/>
     </row>
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="G321" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H321" s="19" t="inlineStr"/>
     </row>
@@ -30804,7 +30804,7 @@
         </is>
       </c>
       <c r="G322" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H322" s="19" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="G324" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H324" s="19" t="inlineStr"/>
     </row>
@@ -30912,7 +30912,7 @@
         </is>
       </c>
       <c r="G325" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H325" s="19" t="inlineStr"/>
     </row>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="G326" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H326" s="19" t="inlineStr"/>
     </row>
@@ -30984,7 +30984,7 @@
         </is>
       </c>
       <c r="G327" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H327" s="19" t="inlineStr"/>
     </row>
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="G328" s="17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="H328" s="19" t="inlineStr"/>
     </row>
@@ -31056,7 +31056,7 @@
         </is>
       </c>
       <c r="G329" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H329" s="19" t="inlineStr"/>
     </row>
@@ -31092,7 +31092,7 @@
         </is>
       </c>
       <c r="G330" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H330" s="19" t="inlineStr"/>
     </row>
@@ -31128,7 +31128,7 @@
         </is>
       </c>
       <c r="G331" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H331" s="19" t="inlineStr"/>
     </row>
@@ -31164,7 +31164,7 @@
         </is>
       </c>
       <c r="G332" s="17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="H332" s="19" t="inlineStr"/>
     </row>
@@ -31236,7 +31236,7 @@
         </is>
       </c>
       <c r="G334" s="17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="H334" s="19" t="inlineStr"/>
     </row>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="G335" s="17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="H335" s="19" t="inlineStr"/>
     </row>
@@ -31308,7 +31308,7 @@
         </is>
       </c>
       <c r="G336" s="17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="H336" s="19" t="inlineStr"/>
     </row>
@@ -31344,7 +31344,7 @@
         </is>
       </c>
       <c r="G337" s="17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="H337" s="19" t="inlineStr"/>
     </row>
@@ -31380,7 +31380,7 @@
         </is>
       </c>
       <c r="G338" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H338" s="19" t="inlineStr"/>
     </row>
@@ -31560,7 +31560,7 @@
         </is>
       </c>
       <c r="G343" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H343" s="19" t="inlineStr"/>
     </row>
@@ -31812,7 +31812,7 @@
         </is>
       </c>
       <c r="G350" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H350" s="19" t="inlineStr"/>
     </row>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="G352" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H352" s="19" t="inlineStr"/>
     </row>
@@ -31920,7 +31920,7 @@
         </is>
       </c>
       <c r="G353" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H353" s="19" t="inlineStr"/>
     </row>
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="G355" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H355" s="19" t="inlineStr"/>
     </row>
@@ -32064,7 +32064,7 @@
         </is>
       </c>
       <c r="G357" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H357" s="19" t="inlineStr"/>
     </row>
@@ -32100,7 +32100,7 @@
         </is>
       </c>
       <c r="G358" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H358" s="19" t="inlineStr"/>
     </row>
@@ -32172,7 +32172,7 @@
         </is>
       </c>
       <c r="G360" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H360" s="19" t="inlineStr"/>
     </row>
@@ -32208,7 +32208,7 @@
         </is>
       </c>
       <c r="G361" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H361" s="19" t="inlineStr"/>
     </row>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="G362" s="17" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="H362" s="19" t="inlineStr"/>
     </row>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="G364" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H364" s="19" t="inlineStr"/>
     </row>
@@ -32424,7 +32424,7 @@
         </is>
       </c>
       <c r="G367" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H367" s="19" t="inlineStr"/>
     </row>
@@ -32496,7 +32496,7 @@
         </is>
       </c>
       <c r="G369" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H369" s="19" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
         </is>
       </c>
       <c r="G374" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H374" s="19" t="inlineStr"/>
     </row>
@@ -32784,7 +32784,7 @@
         </is>
       </c>
       <c r="G377" s="17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H377" s="19" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
         </is>
       </c>
       <c r="G378" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H378" s="19" t="inlineStr"/>
     </row>
@@ -32892,7 +32892,7 @@
         </is>
       </c>
       <c r="G380" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H380" s="19" t="inlineStr"/>
     </row>
@@ -32928,7 +32928,7 @@
         </is>
       </c>
       <c r="G381" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H381" s="19" t="inlineStr"/>
     </row>
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="G382" s="17" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="H382" s="19" t="inlineStr"/>
     </row>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="G385" s="17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="H385" s="19" t="inlineStr"/>
     </row>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="G386" s="17" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="H386" s="19" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
         </is>
       </c>
       <c r="G387" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H387" s="19" t="inlineStr"/>
     </row>
@@ -33180,7 +33180,7 @@
         </is>
       </c>
       <c r="G388" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H388" s="19" t="inlineStr"/>
     </row>
@@ -33288,7 +33288,7 @@
         </is>
       </c>
       <c r="G391" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H391" s="19" t="inlineStr"/>
     </row>
@@ -33324,7 +33324,7 @@
         </is>
       </c>
       <c r="G392" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H392" s="19" t="inlineStr"/>
     </row>
@@ -33360,7 +33360,7 @@
         </is>
       </c>
       <c r="G393" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H393" s="19" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G394" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H394" s="19" t="inlineStr"/>
     </row>
@@ -33432,7 +33432,7 @@
         </is>
       </c>
       <c r="G395" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H395" s="19" t="inlineStr"/>
     </row>
@@ -33504,7 +33504,7 @@
         </is>
       </c>
       <c r="G397" s="17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="H397" s="19" t="inlineStr"/>
     </row>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="G399" s="17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="H399" s="19" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
         </is>
       </c>
       <c r="G403" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H403" s="19" t="inlineStr"/>
     </row>
@@ -33756,7 +33756,7 @@
         </is>
       </c>
       <c r="G404" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H404" s="19" t="inlineStr"/>
     </row>
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="G405" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H405" s="19" t="inlineStr"/>
     </row>
@@ -33864,7 +33864,7 @@
         </is>
       </c>
       <c r="G407" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H407" s="19" t="inlineStr"/>
     </row>
@@ -33972,7 +33972,7 @@
         </is>
       </c>
       <c r="G410" s="17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H410" s="19" t="inlineStr"/>
     </row>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="G411" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H411" s="19" t="inlineStr"/>
     </row>
@@ -34080,7 +34080,7 @@
         </is>
       </c>
       <c r="G413" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H413" s="19" t="inlineStr"/>
     </row>
@@ -34152,7 +34152,7 @@
         </is>
       </c>
       <c r="G415" s="17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="H415" s="19" t="inlineStr"/>
     </row>
@@ -34260,7 +34260,7 @@
         </is>
       </c>
       <c r="G418" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H418" s="19" t="inlineStr"/>
     </row>
@@ -34332,7 +34332,7 @@
         </is>
       </c>
       <c r="G420" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H420" s="19" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="G424" s="17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H424" s="19" t="inlineStr"/>
     </row>
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G427" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H427" s="19" t="inlineStr"/>
     </row>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="G429" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H429" s="19" t="inlineStr"/>
     </row>
@@ -34764,7 +34764,7 @@
         </is>
       </c>
       <c r="G432" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H432" s="19" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,7 @@
         </is>
       </c>
       <c r="G433" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H433" s="19" t="inlineStr"/>
     </row>
@@ -34872,7 +34872,7 @@
         </is>
       </c>
       <c r="G435" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H435" s="19" t="inlineStr"/>
     </row>
@@ -34980,7 +34980,7 @@
         </is>
       </c>
       <c r="G438" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H438" s="19" t="inlineStr"/>
     </row>
@@ -35016,7 +35016,7 @@
         </is>
       </c>
       <c r="G439" s="17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H439" s="19" t="inlineStr"/>
     </row>
@@ -35052,7 +35052,7 @@
         </is>
       </c>
       <c r="G440" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H440" s="19" t="inlineStr"/>
     </row>
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G442" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H442" s="19" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
         </is>
       </c>
       <c r="G444" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H444" s="19" t="inlineStr"/>
     </row>
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="G446" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H446" s="19" t="inlineStr"/>
     </row>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="G448" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H448" s="19" t="inlineStr"/>
     </row>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="G450" s="17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H450" s="19" t="inlineStr"/>
     </row>
@@ -35448,7 +35448,7 @@
         </is>
       </c>
       <c r="G451" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H451" s="19" t="inlineStr"/>
     </row>
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="G452" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H452" s="19" t="inlineStr"/>
     </row>
@@ -35520,7 +35520,7 @@
         </is>
       </c>
       <c r="G453" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H453" s="19" t="inlineStr"/>
     </row>
@@ -35556,7 +35556,7 @@
         </is>
       </c>
       <c r="G454" s="17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H454" s="19" t="inlineStr"/>
     </row>
@@ -35592,7 +35592,7 @@
         </is>
       </c>
       <c r="G455" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H455" s="19" t="inlineStr"/>
     </row>
@@ -35628,7 +35628,7 @@
         </is>
       </c>
       <c r="G456" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H456" s="19" t="inlineStr"/>
     </row>
@@ -35664,7 +35664,7 @@
         </is>
       </c>
       <c r="G457" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H457" s="19" t="inlineStr"/>
     </row>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="G458" s="17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="H458" s="19" t="inlineStr"/>
     </row>
@@ -35736,7 +35736,7 @@
         </is>
       </c>
       <c r="G459" s="17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="H459" s="19" t="inlineStr"/>
     </row>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="G462" s="17" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="H462" s="19" t="inlineStr"/>
     </row>
@@ -35916,7 +35916,7 @@
         </is>
       </c>
       <c r="G464" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H464" s="19" t="inlineStr"/>
     </row>
@@ -35988,7 +35988,7 @@
         </is>
       </c>
       <c r="G466" s="17" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H466" s="19" t="inlineStr"/>
     </row>
@@ -36024,7 +36024,7 @@
         </is>
       </c>
       <c r="G467" s="17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H467" s="19" t="inlineStr"/>
     </row>
@@ -36060,7 +36060,7 @@
         </is>
       </c>
       <c r="G468" s="17" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H468" s="19" t="inlineStr"/>
     </row>
@@ -36168,7 +36168,7 @@
         </is>
       </c>
       <c r="G471" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H471" s="19" t="inlineStr"/>
     </row>
@@ -36240,7 +36240,7 @@
         </is>
       </c>
       <c r="G473" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H473" s="19" t="inlineStr"/>
     </row>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="G474" s="17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H474" s="19" t="inlineStr"/>
     </row>
@@ -36456,7 +36456,7 @@
         </is>
       </c>
       <c r="G479" s="17" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="H479" s="19" t="inlineStr"/>
     </row>
@@ -36492,7 +36492,7 @@
         </is>
       </c>
       <c r="G480" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H480" s="19" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="G481" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H481" s="19" t="inlineStr"/>
     </row>
@@ -36600,7 +36600,7 @@
         </is>
       </c>
       <c r="G483" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H483" s="19" t="inlineStr"/>
     </row>
@@ -36636,7 +36636,7 @@
         </is>
       </c>
       <c r="G484" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H484" s="19" t="inlineStr"/>
     </row>
@@ -36672,7 +36672,7 @@
         </is>
       </c>
       <c r="G485" s="17" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H485" s="19" t="inlineStr"/>
     </row>
@@ -36708,7 +36708,7 @@
         </is>
       </c>
       <c r="G486" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H486" s="19" t="inlineStr"/>
     </row>
@@ -36744,7 +36744,7 @@
         </is>
       </c>
       <c r="G487" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H487" s="19" t="inlineStr"/>
     </row>
@@ -36780,7 +36780,7 @@
         </is>
       </c>
       <c r="G488" s="17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H488" s="19" t="inlineStr"/>
     </row>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="G489" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H489" s="19" t="inlineStr"/>
     </row>
@@ -36852,7 +36852,7 @@
         </is>
       </c>
       <c r="G490" s="17" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H490" s="19" t="inlineStr"/>
     </row>
@@ -36924,7 +36924,7 @@
         </is>
       </c>
       <c r="G492" s="17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H492" s="19" t="inlineStr"/>
     </row>
@@ -36996,7 +36996,7 @@
         </is>
       </c>
       <c r="G494" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H494" s="19" t="inlineStr"/>
     </row>
@@ -37068,7 +37068,7 @@
         </is>
       </c>
       <c r="G496" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H496" s="19" t="inlineStr"/>
     </row>
@@ -37104,7 +37104,7 @@
         </is>
       </c>
       <c r="G497" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H497" s="19" t="inlineStr"/>
     </row>
@@ -37176,7 +37176,7 @@
         </is>
       </c>
       <c r="G499" s="17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H499" s="19" t="inlineStr"/>
     </row>
@@ -37248,7 +37248,7 @@
         </is>
       </c>
       <c r="G501" s="17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H501" s="19" t="inlineStr"/>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>1.57s</t>
+          <t>1.58s</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">

--- a/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
+++ b/Test Results/Excel/TrustRoute_Automation_Report_LATEST.xlsx
@@ -679,7 +679,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Run Date: 2026-08-08T04:21:51    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
+          <t>Run Date: 2026-08-09T04:28:22    |    Target: https://rhema5.github.io/trustroute-PDD/    |    Environment: GitHub Actions CI</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>1.58s</t>
+          <t>1.57s</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>3.39s</t>
+          <t>3.38s</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>1.18s</t>
+          <t>1.17s</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>0.9s</t>
+          <t>0.87s</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>1.49s</t>
+          <t>1.47s</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>2.19s</t>
+          <t>2.18s</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="G2" s="17" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="H2" s="19" t="inlineStr"/>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G3" s="17" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H3" s="19" t="inlineStr"/>
     </row>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="H4" s="19" t="inlineStr"/>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.33</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="19" t="inlineStr"/>
     </row>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H6" s="19" t="inlineStr"/>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="H7" s="19" t="inlineStr"/>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="H8" s="19" t="inlineStr"/>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="G9" s="17" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="H9" s="19" t="inlineStr"/>
     </row>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H10" s="19" t="inlineStr"/>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="19" t="inlineStr"/>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="H12" s="19" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="19" t="inlineStr"/>
     </row>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="H14" s="19" t="inlineStr"/>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G15" s="17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
     </row>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H21" s="19" t="inlineStr"/>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H22" s="19" t="inlineStr"/>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H23" s="19" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H24" s="19" t="inlineStr"/>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H26" s="19" t="inlineStr"/>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="19" t="inlineStr"/>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
     </row>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
     </row>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
     </row>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
     </row>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
     </row>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="G43" s="17" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H44" s="19" t="inlineStr"/>
     </row>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G45" s="17" t="n">
-        <v>10.19</v>
+        <v>10.11</v>
       </c>
       <c r="H45" s="19" t="inlineStr"/>
     </row>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="G46" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H46" s="19" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="G47" s="17" t="n">
-        <v>21.15</v>
+        <v>21.1</v>
       </c>
       <c r="H47" s="19" t="inlineStr"/>
     </row>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G48" s="17" t="n">
-        <v>21.87</v>
+        <v>21.82</v>
       </c>
       <c r="H48" s="19" t="inlineStr"/>
     </row>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="G49" s="17" t="n">
-        <v>21.83</v>
+        <v>21.76</v>
       </c>
       <c r="H49" s="19" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G50" s="17" t="n">
-        <v>21.92</v>
+        <v>21.9</v>
       </c>
       <c r="H50" s="19" t="inlineStr"/>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="G51" s="17" t="n">
-        <v>21.88</v>
+        <v>21.93</v>
       </c>
       <c r="H51" s="19" t="inlineStr"/>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="G52" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H52" s="19" t="inlineStr"/>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="G53" s="17" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H53" s="19" t="inlineStr"/>
     </row>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="G54" s="17" t="n">
-        <v>21.14</v>
+        <v>21.13</v>
       </c>
       <c r="H54" s="19" t="inlineStr"/>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="G57" s="17" t="n">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="H57" s="19" t="inlineStr"/>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G58" s="17" t="n">
-        <v>22.11</v>
+        <v>22.14</v>
       </c>
       <c r="H58" s="19" t="inlineStr"/>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="G59" s="17" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H59" s="19" t="inlineStr"/>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G60" s="17" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H60" s="19" t="inlineStr"/>
     </row>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="G61" s="17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H61" s="19" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="19" t="inlineStr"/>
     </row>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="G65" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="19" t="inlineStr"/>
     </row>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="G66" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" s="19" t="inlineStr"/>
     </row>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H67" s="19" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="G68" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H68" s="19" t="inlineStr"/>
     </row>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="H69" s="19" t="inlineStr"/>
     </row>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H70" s="19" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="G72" s="17" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H72" s="19" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="G73" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H73" s="19" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="G74" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H74" s="19" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="G75" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H75" s="19" t="inlineStr"/>
     </row>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H76" s="19" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G78" s="17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H78" s="19" t="inlineStr"/>
     </row>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="G79" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H79" s="19" t="inlineStr"/>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G81" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H81" s="19" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="G82" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H82" s="19" t="inlineStr"/>
     </row>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H83" s="19" t="inlineStr"/>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H84" s="19" t="inlineStr"/>
     </row>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="G85" s="17" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H85" s="19" t="inlineStr"/>
     </row>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="G86" s="17" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H86" s="19" t="inlineStr"/>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="G87" s="17" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H87" s="19" t="inlineStr"/>
     </row>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="G88" s="17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H88" s="19" t="inlineStr"/>
     </row>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G89" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H89" s="19" t="inlineStr"/>
     </row>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="G92" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H92" s="19" t="inlineStr"/>
     </row>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="G94" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H94" s="19" t="inlineStr"/>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="G95" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H95" s="19" t="inlineStr"/>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="G96" s="17" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H96" s="19" t="inlineStr"/>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H97" s="19" t="inlineStr"/>
     </row>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H98" s="19" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G99" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" s="19" t="inlineStr"/>
     </row>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="G100" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H100" s="19" t="inlineStr"/>
     </row>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="G101" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H101" s="19" t="inlineStr"/>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="G102" s="17" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H102" s="19" t="inlineStr"/>
     </row>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="G103" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H103" s="19" t="inlineStr"/>
     </row>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="H104" s="19" t="inlineStr"/>
     </row>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H105" s="19" t="inlineStr"/>
     </row>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="G106" s="17" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H106" s="19" t="inlineStr"/>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G107" s="17" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H107" s="19" t="inlineStr"/>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="G108" s="17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H108" s="19" t="inlineStr"/>
     </row>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="G109" s="17" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H109" s="19" t="inlineStr"/>
     </row>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="G110" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H110" s="19" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H111" s="19" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H112" s="19" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="G113" s="17" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="H113" s="19" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="G114" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H114" s="19" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="G116" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H116" s="19" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G117" s="17" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H117" s="19" t="inlineStr"/>
     </row>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H118" s="19" t="inlineStr"/>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H119" s="19" t="inlineStr"/>
     </row>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="G120" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H120" s="19" t="inlineStr"/>
     </row>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="G121" s="17" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H121" s="19" t="inlineStr"/>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="G122" s="17" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="H122" s="19" t="inlineStr"/>
     </row>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="G124" s="17" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="H124" s="19" t="inlineStr"/>
     </row>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="H125" s="19" t="inlineStr"/>
     </row>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="H126" s="19" t="inlineStr"/>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G127" s="17" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="H127" s="19" t="inlineStr"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="G128" s="17" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="H128" s="19" t="inlineStr"/>
     </row>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="G129" s="17" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="H129" s="19" t="inlineStr"/>
     </row>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G130" s="17" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="H130" s="19" t="inlineStr"/>
     </row>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="G131" s="17" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="H131" s="19" t="inlineStr"/>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="19" t="inlineStr"/>
     </row>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="H133" s="19" t="inlineStr"/>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="G134" s="17" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="H134" s="19" t="inlineStr"/>
     </row>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="G135" s="17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H135" s="19" t="inlineStr"/>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="G136" s="17" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="H136" s="19" t="inlineStr"/>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="G137" s="17" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="H137" s="19" t="inlineStr"/>
     </row>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="G138" s="17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H138" s="19" t="inlineStr"/>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H139" s="19" t="inlineStr"/>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="H140" s="19" t="inlineStr"/>
     </row>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="G141" s="17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H141" s="19" t="inlineStr"/>
     </row>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="G142" s="17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="H142" s="19" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="G145" s="17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H145" s="19" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H147" s="19" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="G148" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="19" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="G150" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H150" s="19" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G151" s="17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H151" s="19" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="G152" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H152" s="19" t="inlineStr"/>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H153" s="19" t="inlineStr"/>
     </row>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H154" s="19" t="inlineStr"/>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="G156" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H156" s="19" t="inlineStr"/>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="G157" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H157" s="19" t="inlineStr"/>
     </row>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G158" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H158" s="19" t="inlineStr"/>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="G159" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H159" s="19" t="inlineStr"/>
     </row>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G160" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H160" s="19" t="inlineStr"/>
     </row>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="G161" s="17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="H161" s="19" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="G162" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H162" s="19" t="inlineStr"/>
     </row>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="G163" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H163" s="19" t="inlineStr"/>
     </row>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="G164" s="17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="19" t="inlineStr"/>
     </row>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="G165" s="17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="H165" s="19" t="inlineStr"/>
     </row>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="G166" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H166" s="19" t="inlineStr"/>
     </row>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="G169" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="19" t="inlineStr"/>
     </row>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G171" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H171" s="19" t="inlineStr"/>
     </row>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="G172" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H172" s="19" t="inlineStr"/>
     </row>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="G173" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H173" s="19" t="inlineStr"/>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="G175" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H175" s="19" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G176" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H176" s="19" t="inlineStr"/>
     </row>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="G177" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H177" s="19" t="inlineStr"/>
     </row>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="G178" s="17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H178" s="19" t="inlineStr"/>
     </row>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="G179" s="17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H179" s="19" t="inlineStr"/>
     </row>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="G180" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="19" t="inlineStr"/>
     </row>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="G182" s="17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="H182" s="19" t="inlineStr"/>
     </row>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="G183" s="17" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="H183" s="19" t="inlineStr"/>
     </row>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="G184" s="17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H184" s="19" t="inlineStr"/>
     </row>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="G185" s="17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="H185" s="19" t="inlineStr"/>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="G187" s="17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H187" s="19" t="inlineStr"/>
     </row>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H189" s="19" t="inlineStr"/>
     </row>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="G190" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H190" s="19" t="inlineStr"/>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G194" s="17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H194" s="19" t="inlineStr"/>
     </row>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H195" s="19" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="G200" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H200" s="19" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H202" s="19" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H203" s="19" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="G205" s="17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H205" s="19" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="G206" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="19" t="inlineStr"/>
     </row>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="G208" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H208" s="19" t="inlineStr"/>
     </row>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H210" s="19" t="inlineStr"/>
     </row>
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="G213" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H213" s="19" t="inlineStr"/>
     </row>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="G215" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H215" s="19" t="inlineStr"/>
     </row>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="G218" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="19" t="inlineStr"/>
     </row>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="G219" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H219" s="19" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="G220" s="17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H220" s="19" t="inlineStr"/>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G221" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H221" s="19" t="inlineStr"/>
     </row>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H223" s="19" t="inlineStr"/>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H224" s="19" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H231" s="19" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H235" s="19" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H237" s="19" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G239" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H239" s="19" t="inlineStr"/>
     </row>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="G241" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H241" s="19" t="inlineStr"/>
     </row>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G242" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H242" s="19" t="inlineStr"/>
     </row>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="G243" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H243" s="19" t="inlineStr"/>
     </row>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="G247" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H247" s="19" t="inlineStr"/>
     </row>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="G249" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H249" s="19" t="inlineStr"/>
     </row>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="G250" s="17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="H250" s="19" t="inlineStr"/>
     </row>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G253" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H253" s="19" t="inlineStr"/>
     </row>
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="G254" s="17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H254" s="19" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="G256" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H256" s="19" t="inlineStr"/>
     </row>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H259" s="19" t="inlineStr"/>
     </row>
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="G260" s="17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H260" s="19" t="inlineStr"/>
     </row>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H265" s="19" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H266" s="19" t="inlineStr"/>
     </row>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H267" s="19" t="inlineStr"/>
     </row>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="G269" s="17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H269" s="19" t="inlineStr"/>
     </row>
@@ -10901,